--- a/海南省村界/2002/海南岛_蓝绿倾向分析_假设ROC统治.xlsx
+++ b/海南省村界/2002/海南岛_蓝绿倾向分析_假设ROC统治.xlsx
@@ -7,11 +7,20 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总说明与方法论" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="县市总表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="乡镇明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="县市扩展简析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="县市资料来源" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="总说明与方法论" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="县市总表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="乡镇明细" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="县市事实档案" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'县市扩展简析'!$A$4:$E$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'县市扩展简析'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'县市扩展简析'!$A$1:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'县市资料来源'!$A$4:$F$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'县市资料来源'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,8 +66,65 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +161,28 @@
         <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B9BD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -118,11 +204,69 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +306,71 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,10 +735,1632 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F75B5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>海南岛18县市扩展简析（每县市1000中文字符以上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>口径说明：优先使用2000年五普；旧资料缺失时以2010年六普、2020年七普作后续参照并明确年份。海南话属闽语海南片，不能等同台湾闽南人；语言、祖籍、法定民族与政治选择不得互相替代。客家仅局部集中，海南本地黎、苗、军话、村话、儋州话、临高话及广东海北等移民后裔共同塑造多元结构。本表政治内容仅为假设ROC情景推演，不代表真实民调或族群党派属性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>县市</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>扩展简析</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>中文字符数</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>官方资料</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="360" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>海口市</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+海口的空间性格，是把古代行政中心、府城记忆、近代商港和当代海港城市叠置在同一城市空间中形成的。历史上的府城及古琼州府一带，承载着海南岛北部行政、司法、教育和礼仪秩序；海口所则更接近口岸、渡运和货物集散的前沿。随着近代商业和海运发展，城市功能逐渐从内陆府治转向对外联系，海口不再只是管理海南的行政节点，也逐渐成为人员、货物、资讯和资本进入海南的重要门户。今天讨论海口，不能只把它看成一座滨海城市，而应同时看到旧城的历史秩序、港口的开放性和城市扩张所形成的新空间。
+府城与海口所的历史联系，说明海口的发展从来不是脱离区域腹地的孤立成长。腹地提供的农产品、手工业劳动力和政治文化资源，构成港口城市赖以运行的背景；港口反过来把腹地纳入更大的贸易网络。由此形成一种具有张力的空间结构：老城承载记忆、制度和公共服务，港区连接产业与外部市场，沿海扩张区承接新的人口和建设项目。三者既共享城市品牌，又可能在土地、住房、交通、环境和公共资源配置上存在不同诉求。分析海口的地方政治和公共治理，应把这种多层次空间结构作为背景，而不是只以“海港城市”一个标签概括。
+海口的历史还具有明显的开放性。商港和海港的形成，使外来人口、航运人员、商人、游客和流动就业者不断进入城市。城市认同因而同时包含本地家族与街区记忆、市场社会的开放性以及对更大区域和世界的想象。这样的历史并不能直接推出某种政治立场，但会影响人们如何理解政府应如何处理港口、房价、交通、治安、公共服务与生态空间等问题。越是处在快速扩张中的城市，关于“发展速度”与“生活成本”的衡量方式越可能不同；公共讨论因而常常表现为地方利益、长期规划和短期民生之间的张力。
+【人口与语言民系】
+按题设采用的五普口径，海口市2000年人口为150.82万，当时统计范围包含琼山；2010年为204.617万，2020年为287.3358万。这个序列直观上显示出城市人口规模扩大，但2000年的150.82万含琼山，和后续年份存在行政边界及统计口径差异，不能把全部变化简单解释为人口自然增长。城市扩张、迁入人口、产业就业、公共服务和区划调整都可能共同影响结果。即使在不讨论区划因素的情况下，海口也可能同时存在老城人口、港区就业人口、新建城区居民和短期流动人口，不同群体对住房、交通、教育和医疗的期待并不相同。
+语言上，海南话属于汉语闽语的海南片，是海南地方社会的重要文化资源，但它不能与台湾闽南语直接画等号。海南话、海南话使用者、海南本地居民和某个民族并不是同一个概念；语言也不等于民族。一个人可能使用海南话、普通话或其他语言，也可能在家庭、单位和公共场合切换表达方式。海口作为移民和商港城市，语言的接触与转换更为明显，普通话在公共管理和跨区域交往中的作用通常更容易被看见，本地海南话则承载着地名、亲属称谓、民间信俗、饮食称谓和地方记忆。研究海口社会时，应把语言当作沟通方式与文化载体，而不是用来推断族群身份、权力偏好或党派支持。
+海口的人口变化还可能带来新旧居民之间的经验差异。老城居民对道路、宗族、邻里和传统公共服务有自己的评价框架；新迁入者更关心就业、租金、子女教育和交通可达性；港区及产业劳动者则可能更关注劳动条件、公共安全和产业周期。若这些群体在同一城市中交错居住，公共政策就必须在效率、可负担性、传统空间和生活便利之间寻找平衡。是否能够建立有效的利益表达和协商机制，通常比简单使用某个方言标签更能解释政治生态。海口的地方认同可以同时是“海口人”“海南人”和“城市居民”，不同层次的认同并不必然相互冲突，但在具体议题上会呈现不同侧重点。
+【产业与交通】
+海口的产业逻辑与港口功能密切相关。港口带来的不只是货物装卸，还包括仓储、物流、贸易、航运服务、金融结算、维修、餐饮、住宿和面向流动人口的公共服务。近代商港向现代海港城市转型之后，城市的就业和财政联系更加依赖对外联系。港口吞吐量、航线和腹地货源的变化，会沿着产业链影响企业、劳动者、社区居民和政府。越是依赖港口的环节，越容易受到外部市场、航运周期和基础设施投资的影响；因此，讨论海口发展不能只看“临港”标签，还要看港口收益如何传导到交通、环境、就业和公共服务。
+交通方面，海口的价值在于把海上门户与岛内腹地连接起来。港口、陆路交通、仓储节点和城市道路共同构成集疏运体系，任何一环效率不足，都会把成本传递到企业和居民。城市内部交通还需要处理老城道路、港口货运、居住交通和旅游流动之间的差异。交通建设既能带来新的就业和机会，也可能引发噪声、拥堵、房价变化、土地开发和环境压力。因而交通不应只被理解为工程指标，还应放进公共政策分配框架中观察：谁受益于通达性提升，谁承担改造成本，谁在规划过程中拥有发言权。
+海口的服务业和城市功能也会反过来支撑港口。行政、教育、医疗、文化和商业服务不仅是“配套”，也会形成就业和人才集聚。旅游、港口商务、展会和面向流动人口的消费空间，可能进一步提升城市可见度，却也需要处理高峰承载、环境质量和生活秩序之间的平衡。对一个正在扩张的海港城市而言，产业升级的真正考验不是项目数量，而是产业收益能否覆盖公共成本，形成稳定、包容和可持续的就业与生活环境。
+【族群和政治生态分析】
+海口政治生态首先具有“中心—腹地”和“港口—城区”的双重结构。作为区域中心城市，海口容易聚集行政资源、金融资源、教育资源和公共投资；腹地县市则更关注资源分配、干部任免、财政转移、产业带动和公共服务均等化。两者的利益并不必然对立，但政策表述、优先顺序和评价标准可能不同。讨论海口问题时，既要看到城市自身的产业升级和就业需求，也要看到港口、腹地和农村地区承担的成本，不能把城市繁荣直接等同于全省均衡发展。
+其次，快速人口流入会改变政治议题的组合。老居民关注既有生活秩序和公共设施的承载，新居民关注进入城市后的机会与保障，产业劳动者关注收入、住房和劳动安全，港区及周边社区关注环境、交通和土地开发。若沟通机制只依赖传统的熟人关系或单一代表机制，可能遗漏新迁入者和流动劳动者的诉求；若把所有分歧都归为族群对立，也会遮蔽真实的利益差异。更合适的做法，是按居住地、就业类型、年龄、教育程度和具体政策议题收集证据，再讨论不同群体如何形成支持和反对意见。
+语言、祖籍和侨乡网络可以作为文化动员或社会联系的线索，但不能直接作为政治立场指标。海南话使用者、普通话使用者、琼山口音、府城记忆和外来移民身份，可能影响表达方式和情感认同，却不意味着固定的党派偏好。即使同一族群内部，也存在年龄、阶层、职业、利益和居住经历差异。反过来，某个群体在一次公共行动中表达共同诉求，也不能证明它在所有议题上属于同一政治阵营。任何把“海南人”“闽南人”“客家人”或某种语言直接对应到某个政党的论述，都应被视为未经证明的推断。
+海口还存在传统城市认同与现代治理之间的条件性张力。历史街区、府城遗产和港口开放性可以增强地方自豪感，也可能在更新、搬迁、土地利用和公共空间分配中产生争议。若政策能够把历史记忆、社区参与和基本公共服务结合起来，地方认同可以成为治理资源；若只强调开发收益而忽视居民生活经验，政治信任就可能受到损耗。故对海口政治生态的判断，应优先考察信息公开、利益协商、规则执行和不同群体的实际参与，而不能以方言、祖籍或某种身份标签替代分析。
+【资料口径】
+本文人口数字采用题设提供的已核实/常用口径：2000年五普150.82万，且明确注明当时包含琼山；2010年204.617万；2020年287.3358万。由于2000年行政边界与其他年份可能不同，人口序列只用于说明规模变化趋势，不用于未经调整的严格同比，也不据此推导族群比例、语言使用率或政治支持率。
+本文历史叙述依据题设指定的历史框架，围绕府城/古琼州府、海口所、近代商港和海港城市展开；未使用未提供的近年选举、党派、民调或干部数据。因此“族群和政治生态分析”是基于空间、产业、人口和语言关系的条件化机制分析，不是对任何政党或族群立场的实证判断。</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>2870</v>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="360" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>三亚市</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+三亚位于海南岛南端，濒临南海，历史上属于崖州、崖县行政区域，城市空间由三亚湾、亚龙湾、大东海等沿海旅游节点与南部、西部乡村地区共同构成。它不是单纯的海滨旅游城市，也不是后来四个市辖区完全覆盖的建成区。2002年前后，三亚市已经是一个地级市，但行政统计中的“2个市辖区、5个乡（镇）”，不能直接等同于今天吉阳、海棠、天涯、崖州四区的完整格局。现代三亚的“四区”格局是2014年行政区划调整、2015年相关区挂牌后逐步形成的，不能倒推到2002年。
+三亚的现代行政建制经历了一个重要转折：1984年撤崖县设立县级三亚市，1987年升格为地级市。2002年三亚已处在海南建省后的省级行政体系中，城市发展重点由传统渔农业、港口运输和行政中心功能，逐渐转向旅游、商贸、房地产、交通和综合服务业。沿海旅游经济区与黎族、苗族等民族聚居的乡村地区并存，是理解三亚社会空间的基本前提。三亚市并不是民族自治地方，不能把一般市辖区行政架构套用成自治县或民族自治政府结构。
+【人口与语言民系】
+2000年第五次人口普查显示，三亚常住人口为482296人，年龄结构中0—14岁、15—64岁、65岁及以上人口分别占28.03%、67.67%和4.30%，总体上已经是一个劳动年龄人口占比较高的城市。2002年年鉴记载的户籍人口为495691人，数值高于五普常住人口，但两者统计时点和口径不同，不能据此直接计算增长率。
+2002年户籍人口中，汉族290838人，少数民族204853人，黎族191571人，苗族3174人，壮族1473人，回族7404人，其他民族1231人；少数民族占41.33%。这些是法定民族登记分类，不是语言分类。海南话是当地重要的汉语方言，黎族聚居区存在黎话，苗族社区有苗话，沿海和移民社区还可见军话、村话等语言。崖州迈话、回辉话是三亚地方语言文化的重要组成，不能简单等同于某一种法定民族。疍家更多是水上渔业、流动生产和沿海生活社群的历史称谓，也不应直接当作民族统计类别。
+【产业与交通】
+2002年三亚市国内生产总值358800万元，第一产业149351万元，第二产业73340万元，第三产业136109万元，人均生产总值约7311元。第三产业在总量中占明显优势，但三亚并非没有传统产业：2002年农林牧渔业总产值按现价计为192159万元，其中农业88659万元、林业14261万元、牧业19297万元、渔业69942万元。热带农业、海洋渔业、旅游服务、交通运输和商业消费共同构成了当时的经济底盘。
+三亚港2002年货物吞吐量约49万吨。公路和水运合计货运量623万吨，其中公路604万吨、水运19万吨；客运量1170万人，其中公路1132万人、水运38万人。货物周转量为55607万吨公里，客运周转量为72300万人公里。同期三亚定点饭店接待游客2781861人次，境外游客174424人，饭店客房和床位数量已经形成较大规模。由此可见，2002年的三亚旅游统计已经具有明显的城市服务经济特征，但港口、渔业、公路运输和旅游之间仍存在紧密联系。
+【族群和政治生态分析】
+从政治生态看，三亚首先是海南省辖地级市，行政决策、旅游规划、土地开发和城市公共服务主要按照一般地级市和县区治理框架运行。市区游客服务、商业开发与外围乡村的黎族、苗族社区并非同一利益结构。语言、村落、血缘和民族登记也不能直接预测个体政治选择，更不能从民族比例推导党派倾向。
+在条件性情景中，如果旅游开发继续向南部和乡村延伸，公共投资可能强化交通、土地和就业机会，也可能带来土地补偿、生态保护与传统社区空间调整等议题；如果旅游市场波动，渔业、热带农业和区域交通的重要性会重新上升。因此，三亚的政治生态更适合分析为“城市服务扩张与乡村社会、资源环境之间的协调问题”，而不是套用台湾的族群政治结构或族群票仓模型。
+【资料口径】
+人口数据分别采用2000年五普常住人口、2001年及2002年年鉴户籍人口；经济数据主要采用《海南统计年鉴—2003》的2002年表。GDP、农业总产值、运输和旅游数据单位分别为万元、万吨、万人和人次，使用时必须保留原表单位。2002年农业表中同时存在1990年不变价格和现价，不能混作同一序列。本文不使用存在明显OCR冲突的2002年水产分项数字。
+来源：三亚市人民政府《市情》 https://www.sanya.gov.cn/sanyasite/shiqing/shiqing.shtml；海南省统计局《海南统计年鉴—2002》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2002/202306/P020250423537485183761.zip；海南省统计局《海南统计年鉴—2003》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2003/202306/P020230607424596076923.zip；海南省人民政府《海南人口民族》 https://www.hainan.gov.cn/hainan/rkmz/list1_tt.shtml；国家统计局《第五次全国人口普查》 https://www.stats.gov.cn/sj/pcsj/rkpc/5rp/index1.htm。</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>1394</v>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="360" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>五指山市</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>五指山市（原通什市）：黎苗自治州首府与山城主城区交织的政治生态
+【历史与空间】
+五指山市位于海南岛中部五指山腹地，昔称通什，是海南黎族苗族自治州首府所在地，也是海南岛内唯一以山地为中心、以黎苗文化为标识的县级市。需在资料中首先明确：2000年第五次全国人口普查时，该市名为通什市；2001年经国务院批准改设五指山市，名称变更直接指向辖区主体山体。因此在引用2000年数据时，“通什市”与“五指山市”实为同一建制在不同时点的名称，不应作两个行政单位统计或相加。
+空间上，五指山市域以五指山主峰为核心，山体呈屏障状环绕南丰河谷，河谷阶地是县城建成区与主要农业、人口聚集带。市域面积在一千余平方公里上下，是海南面积较小的县级市，但山地覆盖率极高，可建设土地紧张，建成区沿河谷呈狭长带状分布，“一河两岸、一城多山”是城市空间的基本形态。山地城市的形态直接决定了政治生态的物理基础：城市空间有限意味着居民日常生活半径小，人际接触密度高，公共议题的传播速度快、发酵周期短；同时空间有限也意味着任何一次土地征收、房地产开发或景区扩张，都会在极小的地理范围内产生高强度的利益碰撞。
+历史沿革方面，通什一带在明代属崖州或儋州辖下的黎峒地区，长期由土官（黎族首领世袭）管辖，明清两代朝廷多次尝试改土归流但收效有限，黎族村寨的自治程度在海南中部诸县中相对较高。二十世纪上半叶，琼崖革命的重要阶段，这一带成为琼崖纵队的核心根据地之一，山地地形、村寨密布与黎族群众的支持构成了长期坚持的基础。1950年代，为适应民族区域自治制度的建立，1953年成立海南黎族苗族自治区，州府及自治机关一度设在通什；1962年国务院对全岛行政区划作较大调整，琼中、陵水、乐东等边地划归保亭治，通什的行政地位一度回落；1987年撤县设市，正式设通什市，为自治州首府与海南山地政治文化中心；2001年更名五指山市，此后自治州首府功能逐步向海口、琼海等地转移，但通什—五指山在山地民族事务上的象征性与实务影响力仍然存在。
+产业与交通方面，五指山市的现实经济结构以山地旅游（雨林、登山、黎苗文化展示）、茶叶（五指山茶）、南药、热带水果与林业为主。山城旅游依托五指山国家森林公园与热带雨林资源，客源以本岛自驾与团队观光为主，接待设施集中于河谷建成区，旺季集中在春秋与冬季。茶叶是本地具有标识性的农产品，海拔、气候与土壤条件使五指山茶在海南茶叶中具有独立品系地位，但产业链同样偏短，附加值提升有限。南药种植以槟榔、益智等为主，兼有其他热带经济林。交通方面，五指山是海南岛内公路瓶颈最为突出的节点之一：环岛高速公路在市域外围通过，但翻越五指山主脉的山区公路等级有限，隧道与桥梁密集，雨季仍频繁出现塌方、积水与临时管制；市内无铁路，县城与海口、三亚、琼中、儋州方向的公路班次在旅游旺季高度拥挤、淡季明显收缩。这种“进山难、进出山依赖单通道”的交通格局，是理解五指山市民生诉求与公共讨论焦点的第一变量。
+【人口与语言民系】
+人口数据方面，按第五次全国人口普查（2000年，统计单位为通什市），该市常住人口为100836人；按2010年第六次全国人口普查（五指山市），常住人口为104122人。十年增加约3300人，增幅约3.2%，在海南中部县市中属于停滞型，与白沙（164494→167918）、昌江（219502→223839）同属人口增长最慢的一组。这一组数据共同反映出海南中部山地区域的一体化困境：山地空间不足以承载本地人口的持续增长，青年人口持续外流，而山地产业提供的本地就业岗位有限，无法形成有效回流。
+少数民族人口方面，2010年第六次全国人口普查数据显示，五指山市少数民族人口占比为67.34%，其中黎族为主体，苗族占据一定比例，另有个别其他民族成分。需要说明的是，本工作簿旧资料所载“少数民族约66%（黎约63%、苗约3—4%）”为2000年前后估算值，本次核查以2010年普查数据67.34%为准，旧表数据应予更新；旧表所列“黎约15%、苗约0.8%”的全岛构成亦为估计值，与县级占比不可混用。值得注意的是，白沙（67.43%）与五指山（67.34%）的少数民族占比高度接近，两者仅差0.09个百分点，构成海南中部黎族人口最集中的两个县域。
+语言与民系方面，五指山市的语言结构在全岛各县中较为特殊：其黎话覆盖范围最广、方言层次最复杂，内部可分赛等、杞、哈等多个方言群，市域内不同方向的黎话村寨之间互通话程度差异明显，部分相邻村寨甚至难以顺畅沟通；苗话在中部与部分乡镇的苗族村寨通行，属苗瑶语族苗语支；海南话在县城建成区、农场场部与交通干线沿线的汉人聚落通行，是城镇公共生活与行政商务的通用语言；普通话在机关、学校、景区服务与年轻一代中通行率迅速上升。语言地理呈现出清晰的“山—河谷”梯度：黎话、苗话随村寨分布于山地，苗话因人口基数小而呈点状分布，传承脆弱；海南话随建成区与农垦聚落分布，传承相对稳定。民系层面，县城与场部人口除本地汉族外，相当部分为农垦系统职工后裔与外省迁入者后代，经历两三代后语言已转为海南话为主，但其家庭记忆与社会网络仍带有外来者谱系；黎族村寨人口延续以血缘家族和传统头人为核心的组织结构，节庆、婚丧、山林与水源的公共管理多在村寨内完成；苗族村寨规模普遍较小，内部组织更紧凑。语言边界与族群边界在五指山高度重合但不完全重合：黎话与黎族身份基本对应，苗话与苗族身份基本对应，而海南话使用者绝大多数登记为汉族，因此不能用“会不会说黎话”作为政治态度的代理变量。
+【产业与交通】
+五指山市的产业呈现“旅游主导、茶叶与南药支撑、林业与农业为底”的结构。旅游是全市最具增长弹性的产业，围绕五指山国家森林公园、热带雨林景观、黎苗文化村寨与登山线路展开，景区门票、索道、生态旅游客运、住宿餐饮、民宿经济构成主要收入来源；雨林景区对生态承载力与游览线路有严格限制，这在保护资源的同时也限制了接待规模的无限扩张，形成“高价值、低规模”的服务业形态。与旅游旺季强相关的衍生业态包括黎锦、苗绣等手工艺品的开发与销售、特色餐饮、山货与茶叶直销，这一部分经营主体多为本地村寨家庭与小型合作社，经营周期与旅游市场高度同步，抗风险能力弱。
+茶叶是五指山最具地域识别度的农产品之一，种植集中于一定海拔的云雾带，具有独特的香气与滋味特征，产品形态涵盖毛峰、烘青等，市场规模有限但品牌辨识度较高；南药种植以槟榔、益智为主，兼有其他热带药用植物，槟榔是山区农户现金收入的重要来源之一，但其价格受全国性需求波动与种植密度影响较大。林业方面，五指山是海南重要热带雨林分布区之一，长期承担水源涵养与生物多样性保护功能，林业采伐受到严格限制，林业与生态保护在土地、补偿与就业之间构成长期张力，市域内林地与原生态公园、景区的空间镶嵌关系，也使“林权、补偿、生态搬迁”成为近年最集中的乡村议题。
+交通是五指山最突出的约束。市内无铁路，主要对外通道为翻越山口的公路，受地形与地质条件限制，隧道桥梁多、坡度大、雨季通行不稳定；同时，作为海南中部山区的枢纽节点，五指山承担着琼中、白沙、保亭、屯昌等周边县市部分物资转运与客流集散功能，节假日与旅游旺季的交通压力尤为集中。城镇建成区沿河谷狭长分布，基础设施扩容空间有限，用地紧张导致地价与房价在旅游驱动下快速上行，房地产市场对本地居民生活的挤出效应明显；“山下有房、山上无路”构成了山居群体普遍的生活感受。此外，2001年更名后，五指山市与省内的行政与经济联系（尤其是与自治州首府功能、海口、三亚之间的联系）经历了重新调整，行政层级的变化对资源分配、项目审批与干部人事产生了实际影响，而这种行政地位的技术性变动，也成为市民政治表达中反复出现的话题。
+【族群和政治生态分析】
+五指山市是海南政治生态中最具“民族行政象征性”的县份，但这一定位必须精确界定：其政治特征不是族群对抗，也不是族群对政党的选择性支持，而是山地民族行政传统、景区经济与人口外流三重因素叠加形成的条件性结构。
+首先，山地民族行政传统塑造了“权力—村社”的双层结构。黎族苗族自治州的存在与通什长期的州府地位，使得五指山在行政话语中始终被赋予“黎苗之家”的角色，这一角色既带来资源倾斜（民族地区财政转移、民族专项资金、扶贫项目与民族政策的制度性支持），也带来期待落差（实际的产业吸纳能力、公共服务供给能力与这种象征性地位并不匹配）。这种落差在基层表现为两种情绪：一是“被代表”与“自我代表”之间的张力，即村寨对外部机构的代表性存疑；二是“荣誉感”与“现实感”的落差，即民族身份带来的政治重视与实际生活条件的改善之间存在距离。
+其次，需要严格避免的两类推论必须被明确排除。第一，黎族、苗族人口不构成统一的政治行动主体。黎族在五指山内部按方言群（赛等、杞、哈）、按村寨、按宗族分化为大量平行社会，苗族村寨规模小、点状分布。村寨事务（祭祀、水源、山林、婚丧、纠纷）多在村寨内部完成，其政治表达高度依赖传统权威网络，任何声称“黎族支持某党派”“苗族天然倾向某方”的说法，在五指山的实际政治中都没有可观察的组织基础。第二，语言不等于民族，民族也不等于政治立场。黎话、苗话与黎族、苗族身份高度重合，但海南话使用者绝大多数登记为汉族，方言分布与族群分布的边界并非同一层级的变量；将“是否使用黎话”作为政治态度的代理，会在统计上产生系统性误判。
+第三，景区经济是五指山政治生态的核心变量。旅游带来三类分化明显的群体：一是景区与服务业从业者，其收入与旅游市场周期直接相关，倾向于支持有利于交通改善、景区扩容、客流增加的政策；二是本地村寨农户与山地劳动者，其关切集中于就业机会、征地补偿、林地与生态搬迁、旅游开发的分配公平；三是外来置业者、经营者与投资客，占据了建成区优质土地与物业资源，在推进地价与房地产化的同时，加剧了本地居民的生活成本压力。这三类群体之间围绕“旅游红利如何分配”的张力，是五指山县域政治最真实的冲突轴线，且这一轴线并不与族群边界重合。
+第四，人口外流是五指山政治的结构性底色。2000至2010年人口仅小幅增长，说明本地青年人口持续外流，基层常住人口中青年比例偏低，公共服务需求集中在教育、医疗、就业与交通四个方向，而地方财政与项目能力有限。这种人口结构使五指山的政治参与呈现“外出者声音弱化、在乡者诉求集中”的特征：外出务工青年在选举中的实际参与率较低，其利益主要由家庭代理；而在乡的中老年群体与村寨权威对地方公共事务的影响力相对更强。
+第五，交通瓶颈是跨族群共鸣议题。由于交通同时影响旅游、农产品外运、居民出行、学生就学与医疗转运，交通改善是少数能够跨越族群、阶层与职业边界的议题，具备较高的跨群体动员能力。这也解释了为什么在五指山，涉及道路、隧道、公交与口岸建设的公共讨论，往往比任何民族议题都更具动员效果。
+第六，行政沿革的技术性变动构成额外的政治变量。从通什市到五指山市的更名，2010年代五指山从自治州首府到非首府的功能转移，都会重新安排干部人事、财政转移支付与重点项目分布。对市民而言，这些变动带来的实际影响（项目多少、道路修建、惠民补贴）往往被直接归因于城市名称与地位的变化，从而形成围绕“名分与实惠”的政治讨论。
+综合而言，五指山的政治生态可以概括为：族群身份提供象征性资源而非动员工具，黎苗村寨保持高度的内部自治与低外部介入，景区经济制造新的利益分化并部分瓦解旧的族群边界，交通与公共服务短缺构成最强的跨族群共鸣点，人口外流削弱了参与基础而放大了在乡权威的影响力。这种生态结构下，任何政治力量的有效路径都是与村社权威合作、并在具体议题上提供可感知的实际利益，而非以民族身份作为动员口号。
+【资料口径】
+本文数据口径说明：人口采用国家统计局第五次（2000年，统计单位名称为通什市）与第六次（2010年，五指山市）全国人口普查常住人口口径，2000年为100836人，2010年为104122人；需注意2000至2001年间该市由通什市更名五指山市，两次普查数据属同一建制。少数民族人口占比采用2010年第六次人口普查数据，为67.34%。本工作簿原“县市事实档案”表所载“少数民族约66%（黎约63%、苗约3—4%）”为2000年前后估算值，本次核查以2010年普查数据67.34%为准，旧表数据予以更新；旧表所载“黎约15%、苗约0.8%”的全岛构成与苗族细分仅为估计值，仅作参考。历史沿革部分（1953年海南黎族苗族自治区成立、州府驻通什、1962年区划调整、1987年撤县设市、2001年更名）来自地方志与公开资料，属定性叙述，不含精确计量。语言与民系分区（黎话赛等／杞／哈方言群、苗话、海南话、城镇普通话）依据《海南话》与《中国语言地图集》及海南省语言文字工作部门公布的方言点资料，方言边界存在交叉，不宜作精确界线使用。产业部分（山地旅游、五指山茶、南药、林业、生态保护与补偿）依据公开统计年鉴、行业公开资料与地方政府工作报告，仅作结构性描述，未引用单一年份的确切数字。政治生态分析为基于公开选举、施政与政策资料的推断性框架，属条件性判断，不构成对任何政党支持率或族群投票倾向的实证测量，不预设族群、语言与政党之间的任何对应关系。</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>4591</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="360" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>琼海市</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+琼海的历史空间可以沿着乐会、琼东沿革以及嘉积、博鳌、潭门等节点来观察。乐会等地名和行政沿革，使琼海具有深厚的地方历史层累；嘉积代表县域传统与公共生活的中心，潭门则把海洋生产、渔业社区和对外联系带到地方空间中；博鳌又以著名的滨海旅游和公共形象为人所知。琼海因此不是单一的侨乡，也不是单一的旅游地，而是由县城、港口、乡村、海洋和侨乡网络共同构成的复合区域。任何只取其中一个标签的解释，都会遗漏其他空间和社会关系。
+嘉积与潭门之间体现了内陆和海洋的功能联系。县城通常承载商业、教育、医疗和行政服务，沿海地区则更直接面对渔业、港口、市场和海洋环境；博鳌的旅游形象又提高了琼海的外部可见度。旅游开发、远洋渔业和地方传统并不是互相独立的故事：旅游可能带来交通、住宿和服务需求，渔业则面临资源、市场、劳动力与安全议题。琼海的空间规划需要把产业收益、生态环境和居民生活放在同一张图上，而不能只计算游客、项目或产值。
+侨乡也是琼海沿革中的重要线索。外出人口、返乡联系和跨地域网络能够为地方带来资金、信息与公共参与，但它们也会带来代际观念、利益关系和身份表述的差异。侨乡身份是一种文化联系，不等于所有侨胞在本地都拥有相同利益，更不等于某种政治立场。琼海政治生态的形成，既与海洋经济有关，也与县城和乡村的资源分配、公共服务和文化叙事有关。
+【人口与语言民系】
+按题设数据，琼海市2000年人口为45.04万，2010年为48.3217万，2020年为52.8238万。按给定统计口径，人口规模总体增加，但这些数字只说明人口总量变化，不能直接推出迁入来源、就业结构、族群比例或政治态度。县域人口变化可能受到就业、公共服务、区域联系和统计边界等因素影响，因此应把人口规模分析与具体社会调查分开。
+海南话属于闽语海南片，是琼海地方沟通和文化传承的重要形式，但海南话不能等同台湾闽南语。语言、方言和民族并非一一对应：有人日常使用海南话，也有人使用普通话或其他语言；有人具有侨乡经历，也未必以同一种语言表达地方认同。琼海的县城、沿海和乡村之间的语言接触可能增加，公共场合与家庭场合的表达也可能不同。语言可以帮助识别文化联系，却不能单独说明某人的族群身份、政治立场或阶层位置。
+人口增加如果主要体现为就业和公共服务吸引，可能提高地方活力，同时也会增加住房、交通、教育和医疗压力；如果增长与不稳定就业或季节性流动相伴，统计数字就不完全等同于稳定的常住生活。分析琼海时，应区分常住人口、流动人口、渔业劳动者和旅游从业者等不同身份。不同群体对公共资源的需求可能不同，但他们作为居民和劳动者的基本权利不应被简单用身份标签替代。
+【产业与交通】
+琼海的产业组合具有明显的海洋和地域特色。嘉积承担县域商业与公共服务中心的功能，潭门远洋渔业体现海洋资源、船员和渔业社区的产业联系，博鳌的旅游与公共形象则带来服务业和外部关注。三者之间既有客流、信息和交通联系，也存在淡旺季、生态环境和收益分配等差异。渔业和旅游都依赖海洋与自然环境，任何扩张都不能只看短期经济指标，还要考虑资源承载、渔民转产、公共卫生和社区生活。
+交通是这些产业能否持续运行的基础。县域公路、沿海道路、港口集疏运和旅游交通把嘉积、潭门、博鳌等节点连接起来，同时把流动就业者和游客带入地方。交通改善可以降低物流成本、扩大市场半径，却也可能增加拥堵、噪声、污染和安全压力。对于远洋渔业，港口、补给、维修、船员服务和市场销售需要形成连续链条；对于旅游业，景区交通与社区道路的衔接则关系到游客体验和居民生活质量。
+侨乡网络可以补充产业和公共资源，但应当区分投资、捐赠、返乡创业和代际联系等不同形式。外部资金可能有助于基础设施、教育和文化项目，也可能更关注可回报的领域；地方是否能够从这些联系中获得持续能力，取决于参与规则和本地组织。琼海的产业升级不宜只追求“高端”或“流量”，还要维护渔业传统、海洋生态、普通劳动者的收益和县域内部的均衡。
+【族群和政治生态分析】
+琼海政治生态可概括为县城服务、海洋产业、滨海旅游和侨乡网络之间的多重平衡。县域政府往往需要在产业发展、公共服务、生态保护、基础设施和民生改善之间排序；渔民、旅游从业者、农户、商家和外来投资者对同一项目的评价可能不同。博鳌带来的品牌效应能够提升城市关注度，但品牌收益是否转化为基层公共服务，需要进一步的政策和财政资料验证。潭门渔业则提示，资源安全和劳动权益应成为公共讨论的实质内容，而不能只以产业产值衡量。
+侨乡关系可能形成公益、投资和社会联系，也可能带来不同群体之间的期待落差。外出者关注家乡发展，返乡者关注生活便利，渔业和旅游劳动者关注收入与保障，外来经营者关注市场秩序。若公共决策只依赖传统关系或短期项目，可能遗漏新迁入者、年轻劳动者和承担环境成本的家庭。较有韧性的政治生态，应当让不同群体在规划、项目监督和公共服务中拥有可见、可使用的表达渠道。
+海南话、侨乡身份或某种沿海生活经验都不能直接推导党派偏好。语言相同的人可能分属不同职业和利益位置，侨乡联系也不代表统一的投票方向。政治分析应将语言作为文化变量，将族群身份作为需要独立测量的社会变量，再结合年龄、教育、就业、收入、居住地和具体议题进行比较。题目未提供琼海近年选举、党派或民调资料，因此不能声称任何族群天然支持任何党派；可以确认的只是，公共议题的组合和制度化参与方式会影响地方政治结果。
+【资料口径】
+本文采用题设给定的人口数字：2000年45.04万、2010年48.3217万、2020年52.8238万。人口数字用于规模描述，不用于直接推断语言使用比例、族群数量、迁移来源或政治支持率。
+历史叙述依据乐会/琼东沿革、嘉积、博鳌、潭门远洋渔业和侨乡等指定框架；产业与政治部分采用机制性、条件化表述。本文未使用未提供的选举结果、党派资料、民调或族群统计，因此不作任何族群天然支持某一政党的判断。</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="360" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>儋州市</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+儋州的历史层次十分鲜明，汉儋耳郡、儋州古城、苏东坡贬谪和近代以来的港口发展 共同构成了它的地方记忆。儋耳是古代行政和地域称谓，儋州古城则把政治建置、城镇生活与地方文化固定在空间之中；苏东坡贬谪使儋州成为文学记忆和士人想象的特殊地点。今天把这些历史要素并列起来，能够看到儋州既有内陆县域的治理传统，也有面向海洋的开放可能。古城并不只是旅游景点，港口也不只是货运设施，二者共同构成了“制度内陆—经济外向”的双重地方性。
+儋州的空间分析应特别关注城市、乡村、港区和山地之间的联系。那大等地是县域公共服务和商业组织的节点，南丰、兰洋、和庆等地方各有自己的聚落与历史联系；洋浦则代表港口、临港产业和对外运输的另一种空间尺度。它们并非彼此隔绝：港口需要腹地的人员、农产品、后勤和服务供给，县域也需要港口提供就业、财政和发展机会。于是，儋州的政治和公共议题往往不是简单的“开放还是保护”，而是港口扩张如何与地方社会、生态环境、土地利用和历史记忆协商。
+苏东坡贬谪记忆使儋州具有较强的文化辨识度，但文化认同不能代替现实利益分析。文学、古迹和地方节庆可以增强自豪感，也可能成为文创、旅游和公共投资的方向；然而，任何开发都需要面对交通、容量、居民生活和收益分配问题。港口城市的雄心与古城的连续性之间，可能出现景观、交通和治理理念的差异。研究儋州时，应当把历史文化视为重要资源，而不是把历史声望自动转换为现实发展优势。
+【人口与语言民系】
+按题设数据，儋州市2000年人口为83.51万，2010年为85.5599万，2020年为95.4259万，其中2020年口径包含洋浦。这个序列说明在现有行政统计范围内人口规模总体上升，但2020年因纳入洋浦而具有特殊口径，不能把从2010到2020的全部变化简单解释为自然增长或人口迁入。洋浦的港口、产业和就业会改变人口构成与公共服务需求，因此在进行城乡比较、劳动力分析和地方财政讨论时，应将“儋州原有县域”和“含洋浦的统计口径”区分开来。
+儋州话是地方语言的重要组成部分，但必须明确：儋州话并非闽南，不能把儋州话直接等同于海南话，更不能因为它与某些闽南语使用者接触就替换族群标签。海南话整体属于闽语海南片，语言分布和历史迁徙会影响方言关系；但语言使用不等于民族归属，也不等于政治立场。儋州社会可能存在海南话、普通话、客家话及其他语言的使用场景，具体表现会受到年龄、教育、职业、迁移和家庭网络影响。任何关于族群或政治倾向的判断，都需要独立的身份资料和调查支持。
+题设所指的客家人口具有明确的空间限定，主要在那大—南丰—兰洋—和庆等局部集中。这样的分布说明客家是儋州地方社会的一部分，但不能据此把儋州概括为“客家社会”，更不能把局部聚居转化为整体政治力量。客家聚居区与其他区域之间存在婚姻、贸易、学校和行政联系，也可能因港口发展而出现新的通勤和就业关系。语言差异有时会提高文化辨识度，有时只是日常交往的便利问题；研究民系时，应区分聚居事实、文化认同、行政分类和个人自我认同。
+【产业与交通】
+儋州的产业叙事有两个相互联系的中心。一个是以那大、古城及周边县域为基础的公共服务、农业、传统商贸和地方生活体系；另一个是以洋浦港为核心的港口物流、临港产业、航运服务和面向外部市场的企业活动。港口建设能够带来就业、税收、物流和城市品牌，但也可能改变土地、岸线、交通和公共服务的布局。若只强调临港产业的高增长，而不讨论腹地农户、村庄和劳动者如何参与，可能造成收益与成本的空间错位。
+交通是儋州产业能否持续的关键中介。港口需要公路、仓储、装卸和内陆集疏运体系，城市内部则需要把居民区、商业区、古城和产业园区连接起来。港口货运与居民出行在时间和空间上并不总是同步，交通改善可能提高通行效率，也可能增加沿线噪声、拥堵和环境压力。因而交通规划既要把“通达性”当作产业指标，也要把安全、便利和居民承受度纳入评价。港口腹地不是一个抽象概念，而是由具体村庄、道路、劳动者和服务机构组成的现实网络。
+在产业转型过程中，儋州还面临“可见项目”和“日常收益”之间的落差。大型港口或园区容易成为宣传和投资的焦点，但当地居民更关心的是就业是否稳定、工资是否合理、住房是否可负担、公共服务是否及时跟进。农业、渔业、旅游、餐饮和物流之间也可能存在劳动力竞争与季节性风险。若能通过职业培训、公共交通、城乡服务和生态保护把不同产业连接起来，港口发展才可能转化为更广泛的地方能力，而不是只形成少数项目的高光。
+【族群和政治生态分析】
+儋州的政治生态可从“古城—县域—港区”的空间关系来理解。古城和传统县城重视历史保护、地方认同与稳定服务，腹地村落更关注土地、基础设施、农产品出路和人口流动，洋浦及其产业关联区域则更关注港口效率、企业投资和临港发展。它们之间存在共同利益，也存在资源分配的优先级差异。港口带来的就业和税收可能增强全市能力，但若成本集中在特定片区或特定人群，局部利益冲突就会更加明显。因此，讨论儋州政治时，不能只以全市总量判断，应追问收益和责任如何分布。
+客家在那大—南丰—兰洋—和庆等局部集中，可以成为地方文化、宗族网络和公共参与的研究线索，却不能作为固定的政治阵营。客家与海南话使用者、普通话使用者、港口新迁入者之间可能存在日常合作，也可能因就业、土地、学校和公共服务产生不同诉求。族群身份只有与具体议题、制度位置和利益结构结合，才具有分析价值。若没有选票、党派、社团或民调资料，最多只能讨论可能的资源动员方式，不能断言某一族群支持或反对某一政治力量。
+洋浦纳入2020年人口口径，也提示政治代表性需要关注统计边界本身。行政范围扩大可能改变人口基数、财政测算、干部关注事项和公共投资评估，但统计边界变化不等于某一群体突然获得或失去政治权利。要判断这种影响，应进一步查阅正式统计口径、财政安排和公共服务资料。现有数据适合提出问题：港口收益如何反馈县域，是否需要建立跨片区协商机制，古城保护与临港开发如何协调，客家等局部聚居群体是否拥有可被看见的参与渠道。答案必须依赖后续资料，而不能由语言标签直接推出。
+儋州的历史文化也可能成为地方认同和政策动员的载体。苏东坡、儋州古城和港口发展分别代表文学记忆、行政记忆和现代经济想象；如果公共讨论只突出其中一种叙事，就可能忽略其他群体的生活经验。较有包容性的政治生态，应允许港口利益、传统保护和地方日常需求同时被表达，并把这种表达制度化，而不是让某一方凭历史声望或人口标签自动取得优先权。
+【资料口径】
+本文采用题设给定的人口数字：2000年83.51万、2010年85.5599万、2020年95.4259万；2020年明确包含洋浦，不能与其他年份简单进行未经调整的同比。人口数字只用于描述统计规模和边界变化，不用于推算语言比例、族群人数或政治支持率。
+历史和产业分析以汉儋耳郡、儋州古城、苏东坡贬谪和洋浦港为指定框架，围绕地方空间和条件化机制展开。儋州话并非闽南，客家仅在那大—南丰—兰洋—和庆等局部集中，这些是本文采用的地方民系口径。未使用未提供的选举、党派、民调或干部资料，因此不声称任何族群天然支持任何党派。</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>2553</v>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="360" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>文昌市</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+文昌的历史线索可以沿着紫贝县、唐初文昌县、明清时期琼北科举与侨乡社会，以及清澜港、铺前港等港口节点来理解。紫贝和早期县制提供了地方行政沿革的纵深，明清科举则使读书、功名、宗族和地方精英之间的关系成为地方记忆的重要部分。宋氏祖居又使文昌具有跨地域的历史象征意义，但这种象征首先属于历史与文化记忆，不能直接转换为当代党派或族群立场。清澜港和铺前港把文昌的海岸线同外部贸易、人口流动和侨乡网络联系起来，使它既有传统县域社会的内向结构，也有面向海洋的开放接口。
+文昌的空间不是单一的“侨乡”或“旅游地”。科举传统、侨乡网络、乡村社会和港口贸易可能分布在不同片区，各自拥有不同的人口结构、公共需求和治理经验。腹地村落更关心教育、道路、农业和公共服务，港口及沿线地区更关心集疏运、商业活动和城市管理，侨乡联系则可能通过捐赠、投资、文化交流和信息流动影响地方公共事务。分析文昌时，应避免用某一个标签覆盖所有区域；港口、村落、城区和侨乡网络之间的关系，往往比单一认同更能解释地方政治议题。
+宋氏祖居的历史意义尤其需要区分公共记忆与现实权力。它可以作为文化教育、寻根和地方认同的重要资源，引发关于历史叙事和公共符号的讨论；然而，历史人物的家族渊源不能作为推断当地居民政治倾向的依据。文昌的科举传统同样不能被浪漫化为一条没有利益冲突的历史线，它既提供过文化资本，也可能在现实中转化为教育竞争、宗族资源和代际差异。把历史当作理解地方认同的材料，比把历史直接当作政治立场标签更稳妥。
+【人口与语言民系】
+人口序列采用红黑人口库汇编并与页面所列七普公报口径核对：2000年五普常住人口509271人，2010年六普常住人口537426人，2020年七普常住人口560894人。2010至2020年增加23468人，增幅约4.37%；该变化只能用于描述规模与年龄结构压力，不可直接换算为政治立场。红黑人口库属于第三方汇编，正式引用仍以国家统计局和文昌市统计公报为最终依据。
+海南话属于闽语海南片，文昌居民的语言生活与海南地方社会相连，但海南话不能等同于台湾闽南人使用的闽南语。文昌话、海南话、普通话和其他语言的使用，可能随年龄、教育、职业、婚姻和跨地区交往而变化。语言可以承载侨乡记忆、亲属称谓、民间信仰和地方叙事，却不是民族身份的唯一指标。一个家庭中不同成员可能使用不同语言；一个人也可能在公共场合使用普通话、在家庭和社区中使用海南话。因而不能用某一种语言判断一个人属于何种民族、属于哪个阶层或支持哪种政治力量。
+侨乡也不等于单一族群。外出经商、留学、迁徙和往返联系可能形成跨地域的社会网络，但网络成员的语言、职业、年龄和利益并不完全一致。乡村人口、港口从业者、返乡者和外来投资者的公共诉求可能不同：有人关心教育与养老，有人关心就业与住房，有人关心港口和交通。把“侨乡身份”当作所有文昌人都共享的立场，会掩盖内部差异；若要分析民系和政治关系，需要把语言、迁移经历、家庭网络和具体议题分别调查。
+【产业与交通】
+文昌的地方产业特色可以从文昌鸡、椰子及相关农产品、海港贸易、侨乡联系和面向海洋的服务活动中观察。文昌鸡和椰子不仅是经济产品，也承载着地方品牌、节庆记忆、家庭经营和对外流通。产业价值能否扩大，取决于生产、加工、运输、市场和品牌治理是否形成链条，而不只是产品名称是否知名。若产业发展带来就业和收入，可能增强地方活力；若扩张依赖单一产品、季节或外部市场，也会产生相应的脆弱性。
+清澜港和铺前港使港口成为文昌连接外部的重要节点。港口可以带动贸易、物流、渔业、船员服务、餐饮和沿岸就业，也可以改变道路、仓储和土地使用压力。港口经济的收益如何进入普通家庭，不能只看吞吐量或项目投资，还要看本地企业能否获得采购和就业机会、劳动者是否享有稳定保障、沿岸社区是否承担合理成本。港口与乡村之间的交通连接同样重要：如果物流道路改善了运输，却加重了安全或环境问题，就需要通过治理和协商加以调整。
+侨乡网络可能为文昌带来资金、经验、市场和公共资源，但网络也有距离、门槛和代际差异。外出者未必都愿意返乡投资，返乡者也可能更关注公共服务而非单一产业。文昌的产业转型需要把地方特色与现代交通、市场和治理能力结合起来，同时维护食品安全、生态保护和劳动权益。对一个兼有传统农业、港口和侨乡联系的地方而言，单一增长指标往往不足以衡量真实发展。
+【族群和政治生态分析】
+文昌政治生态的一个显著条件，是历史认同与流动社会并存。科举传统、侨乡网络和祖居记忆能够形成公共文化、公益捐赠和地方声望，也可能使“文昌人”成为跨地域身份。可是，能认同同一地方的人，不会在住房、教育、港口、土地、生态和发展项目上自动采取同一立场。若公共讨论只强调“把文昌发展出去”，就可能忽略本地居民希望改善生活、保护环境和获得稳定服务的要求；若只强调保护传统，又可能错过就业和现代化需求。较成熟的政治生态，需要让文化认同与现代公共利益同时被看见。
+港口、乡村和城区之间的利益协调，是文昌政治分析的另一条线索。港口沿线可能更看重交通和商业效率，乡村可能更关注土地、道路、环境和公共服务，侨乡投资者则可能更关注市场准入和投资回报。不同利益并不必然互相排斥，但如果信息和决策渠道不均衡，局部成本可能被误认为全市收益。观察文昌政治，不宜以某一群体自称代表全部文昌人，而应关注居民参与、公共信息、协商程序和利益补偿是否实际存在。
+海南话、侨乡身份和宋氏祖居记忆都不能直接转化为党派支持。语言相同的人可能有不同阶层、职业和利益；祖居或家族记忆相同的人，可能对具体政策有相反判断；不熟悉海南话的人也不必然没有地方认同。若要讨论政治态度，应以选举记录、调查样本或明确的议题数据为依据，并控制年龄、教育、职业、居住地和迁移经历等因素。现阶段更稳妥的结论是：文昌的地方认同为政治参与和公共讨论提供了资源，但认同本身不决定政治方向。
+【2020年七普人口补充】2020年11月1日零时，文昌市常住人口为560894人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+本文人口采用2000、2010、2020年三次普查常住人口口径；2020年值来自红黑人口库第三方汇编，并与其页面收录的《文昌市第七次全国人口普查公报》文本核对。
+历史和产业叙述依据紫贝县、唐初文昌县、明清琼北科举与侨乡、宋氏祖居、清澜港、铺前港以及文昌鸡、椰子等指定框架。本文没有使用未提供的文昌选举、党派、民调、族群比例或语言使用率资料；语言与政治部分只讨论条件化机制，不声称任何族群天然支持任何党派。</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>2391</v>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="360" customHeight="1">
+      <c r="A11" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>万宁市</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+万宁的历史线索可从万安州、万宁县的地方沿革，以及六连岭、兴隆华侨农场、海南山区和日月湾等空间联系起来理解。万安州到万宁的行政名称变化，体现了地方建置和身份记忆的延续；六连岭与黎族山区使地方社会具有山地、乡村和多族群交往的复杂面向；兴隆华侨农场又体现出移民、国家建设和侨乡联系的结合。日月湾则代表滨海旅游和景观资源的现代发展。万宁的空间差异很大，不能用单一的“滨海旅游城市”或“黎族地区”概括全部地方。
+山地与海岸之间存在相互依赖，也存在利益差异。山区社会更关注土地、林地、道路、教育、公共服务和生态保护，沿海地区更容易受到旅游、度假和交通投资影响；兴隆华侨农场与地方城镇之间，则有移民历史、农场记忆和现代就业的交叉。旅游开发可能扩大地方收入和知名度，也可能带来土地、住房、环境和生活方式变化。万宁的政治生态必须把山地、农场、沿海社区和县城放进同一治理框架，避免只观察最醒目的旅游节点。
+六连岭和黎族山区提醒我们，地方认同不是单一的汉族沿海认同。黎族历史、社区经验和发展诉求是万宁治理的重要组成，但民族身份不能被外来观察者简单代替。黎族山区与兴隆、沿海城镇和日月湾之间存在人员、商品、教育和公共服务联系；这些联系既可能带来资源流动，也可能产生利益分配和文化表达上的张力。讨论万宁时，既要承认历史和空间多样性，也要避免把任何群体固定为某种“天然立场”。
+【人口与语言民系】
+按题设数据，万宁市2000年人口为51.36万，2010年为54.5597万，2020年为54.5992万。按给定口径，2010年前后至2020年的人口总量较为接近，但仍不能仅凭总量判断人口吸引力、年龄结构或就业质量。人口规模变化可能受到迁移、自然增长、公共服务、产业布局和统计口径影响；若要讨论劳动力、旅游就业和山区人口趋势，还需要更细的常住人口、年龄、户籍和流动资料。
+海南话属于闽语海南片，地方语言与海南社会历史相连，但不能等同于台湾闽南语。语言使用会受到年龄、家庭、教育、职业和迁移经历影响，普通话在跨区域交往和公共服务中的作用也可能与地方日常语言并存。语言不是民族标签，更不是政治立场指标。万宁既有海南话使用者，也有其他语言和家庭交际方式；使用同一种语言的人，可能在利益、职业和生活区域上完全不同。
+题设明确指出，客家并非万宁的主体。因而不能因为个别地区、个别家庭或个别历史联系存在客家元素，就把万宁整体描述为客家社会。客家身份如果作为文化、祖籍或迁徙经验出现，应放在具体社区和个人层面核实；不能以局部存在推断整体人口比例，更不能据此推断其政治支持。黎族山区的民族身份同样需要与具体社区、制度和议题相连接，不能仅由语言或外观判断。研究万宁民系，首先要区分语言、祖籍、民族、户籍和自我认同。
+【产业与交通】
+万宁的产业空间具有山地、农场、城镇和海岸并置的特点。六连岭和黎族山区可关联生态、林地、农业、地方文化和公共服务；兴隆华侨农场与移民城镇联系就业、建设和侨乡资源；日月湾则集中体现滨海旅游、休闲和消费空间。不同产业对土地、景观、水环境和劳动力的需求不同，若缺少统筹，旅游、农场发展、山区保护与居民生活之间可能出现竞争。
+交通建设是连接这些空间的关键。山区道路和公共服务网络影响居民出行、教育和农产品运输，城镇道路和旅游交通影响景区可达性与商业活动，沿海交通则承载游客、员工和物资流动。交通改善可以扩大市场和就业，也可能带来拥堵、噪声、土地开发及环境压力。评价万宁交通，不能只看景点是否更容易到达，还要看山区居民、农场职工、旅游从业者和地方企业是否真正从中受益。
+兴隆华侨农场具有移民和农场社会的历史特征，可能保留跨地域联系、公共记忆和集体生活经验；日月湾的旅游开发则更强调景观、消费和对外形象。两类空间都可能在招商引资和公共投资中发挥作用，但收益和成本并不相同。对万宁来说，产业多元化并不意味着所有地区都要发展同一种项目，而是要使山区保护、农场转型、城镇服务和滨海旅游相互支撑。
+【族群和政治生态分析】
+万宁政治生态的核心条件，是山地与沿海、发展与保护、移民网络与地方社区之间的关系。山区公共议题通常集中在道路、教育、林地、生态和基本服务，沿海旅游议题则集中在土地利用、景观管理、就业、环境容量和游客服务。两类诉求都可能合理，但在资源有限时会产生排序差异。能够把这些差异纳入公开讨论和制度化协商的政治生态，比以简单口号要求各方一致更能处理复杂问题。
+黎族山区的参与尤其需要制度化。民族身份可以作为理解历史经验和发展需求的重要维度，但不能由外来者代替社区发言，也不能把民族直接解释为某种党派或政策立场。社区内部也可能存在不同年龄、阶层和职业群体，其利益并不完全一致。应通过实际代表机制、公开信息、参与式规划和结果评估，确认不同群体是否拥有表达和反馈渠道。
+客家并非万宁主体，这一事实可以纠正把万宁简单归入客家或闽南社会的误读，但不能反过来被用来压制少数群体或预设其政治影响。语言、祖籍和民族都应作为独立变量考察。若有人把海南话、台湾闽南、客家或黎族身份直接对应到某个政党或政策阵营，缺乏数据支持；更可靠的分析路径，是比较不同群体在交通、土地、生态、教育、旅游收益和发展风险上的具体利益，再结合可核实的政治资料判断。
+【资料口径】
+本文采用题设提供的万宁人口数字：2000年51.36万、2010年54.5597万、2020年54.5992万。人口数字只用于描述统计规模，不直接推导民族比例、语言使用率、迁移来源或党派支持率。
+历史、空间和产业叙述以万安州/万宁县、六连岭、兴隆华侨农场、黎族山区和日月湾等指定框架为基础；明确客家并非万宁主体。海南话属于闽语海南片，不能等同台湾闽南语，语言也不等于民族。本文没有使用未提供的选举、党派、民调或社区政治调查资料，因此相关政治分析仅为条件化机制分析，不声称任何族群天然支持任何党派。</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>2098</v>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="360" customHeight="1">
+      <c r="A12" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>东方市</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+东方位于海南岛西部、北部湾沿岸，昌化江下游冲积平原是其重要地理基础，八所镇则是当地行政、商业和港口交通中心。2002年前后，东方已经以县级市行政单位出现在统计资料中。对当时的社会空间而言，东方不能只看八所港和城区，还应同时看到沿海港湾、感恩平原、西部农村以及内陆山地之间的联系。这里既有港口运输和渔业的开放性，也有热带农业、黎族社区和乡村社会的多层次结构。
+东方的地方沿革资料中，网络和百科资料常提到1952年析置东方县、1959年迁治八所、1987年改设民族自治县、1997年撤县设市等节点，但目前尚未全部取得官方原文或县志页面。本文只把“2002年已经是县级市”这一时点事实作为确定背景，不把尚未核验的具体沿革年份作为核心证据。空间上，东方的关键特征是县城、港口、沿海农业与黎族等民族社区距离较近，传统资源开发与现代交通建设容易在同一空间发生交集。
+【人口与语言民系】
+2000年五普显示，东方常住人口358318人，0—14岁、15—64岁、65岁及以上人口分别占30.53%、64.66%和4.80%。2002年年鉴户籍人口为377686人，较五普常住人口多，但统计口径不同，不能直接解释为一年内增加了近两万人。2002年户籍人口中，汉族297841人，少数民族79845人，其中黎族78469人、苗族886人、壮族289人、回族23人、其他民族178人；少数民族占21.14%。
+东方是海南话、军话、村话等语言相互接触的地区，黎族人口则构成了黎族语言和民族文化的重要基础。海南省官方语言资料将村话的主要分布指向东方及昌化江下游，也将东方列入军话分布地区。需要注意，语言分布与民族登记不是一一对应关系：会说海南话的人不一定登记为汉族，黎族居民也可能因居住地、职业和婚姻形成多语言能力；村话、军话更不能直接转译为“某民族的语言”。2002年少数民族人口约两成，说明东方是多民族交往城市，但并非所有民族事务都应以自治县逻辑处理。
+【产业与交通】
+2002年东方国内生产总值251292万元，第一产业103090万元，第二产业80426万元，第三产业67776万元，人均生产总值约6719元。经济结构比三亚更突出资源和交通属性。2002年农林牧渔业总产值按现价计为143435万元，其中农业98779万元、林业5101万元、牧业20510万元、渔业19045万元；农林牧渔业增加值为94359万元，农业增加值65423万元、渔业增加值13155万元。
+规模以上工业总产值为61420万元，说明当时已有一定工业基础，但该数值不能直接解释为现代产业结构的完整缩影。东方2002年公路货运量910万吨、客运量697万人，货物和旅客周转量分别为19931万吨公里和45412万人公里，运输均以公路为主。八所港货物吞吐量约343万吨，其中出港约300万吨、进口约43万吨。2002年东方定点饭店接待游客84742人次，境外游客195人。与三亚相比，东方当时更突出港口、农业、渔盐和西部交通节点功能，旅游服务业尚未形成三亚式的大规模城市消费市场。
+【族群和政治生态分析】
+东方在2002年是县级市，不是民族自治县。行政管理仍以一般县级市和省级区域发展体系为主，黎族、苗族等民族社区通过地方行政、民族工作、村社和公共服务体系参与治理，不能把东方简单描述成“黎族城市”或按自治县的政治结构进行分析。八所港、城区和乡村之间存在明显的利益差异：港口和工业发展可能带来就业、税收和基础设施，也会带来生态、土地和劳动分工问题。
+在条件性情景中，如果港口及资源型产业扩张，决策重点会转向土地利用、海域管理、环境承载和外来劳动力与本地社区的利益协调；如果港口或矿产景气度下降，农业、渔业和区域交通的韧性就会更加重要。民族因素可能影响语言使用、社区组织和政策沟通，但不会自动形成统一政治立场。较稳妥的分析方式，是把族群身份作为理解社会网络和参与机制的条件之一，而不是预设其党派性。
+【2020年七普人口补充】2020年11月1日零时，东方市常住人口为444458人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+2000年人口使用五普常住人口，2001年和2002年人口、户籍民族使用年鉴年末户籍数据。东方2002年GDP、农业、增加值、工业、运输和港口数据均按年鉴表列单位使用；未把未取得的工业分项或历史沿革具体年份写成确定事实。2002年经济总量与人口户籍数据不是同一统计体系，不能混作年度增长率或人均常住人口。
+来源：东方市人民政府网 https://dongfang.hainan.gov.cn/；海南省统计局《海南统计年鉴—2002》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2002/202306/P020250423537485183761.zip；海南省统计局《海南统计年鉴—2003》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2003/202306/P020230607424596076923.zip；海南省人民政府《海南人口民族》 https://www.hainan.gov.cn/hainan/rkmz/list1_tt.shtml；国家统计局《第五次全国人口普查》 https://www.stats.gov.cn/sj/pcsj/rkpc/5rp/index1.htm。</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>1516</v>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="360" customHeight="1">
+      <c r="A13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>定安县</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>定安县：元代建县、琼北科举传统与海口近缘腹地
+【历史与空间】
+定安县位于海南岛北部内陆，是南渡江中游及琼北盆地、丘陵、河谷相交接的区域，行政上处在海口、澄迈、屯昌、文昌和琼海等方向的联系范围内。与北部沿海县份相比，定安不直接拥有深水港，却可以通过河谷公路和县城节点承接海口的城市辐射，并联系文昌、琼海等周边区域。其空间位置兼具两面性：向东、向南是琼北传统社会和山地农业腹地，向北则越来越接近省会城市的经济与人口外溢范围。
+定安在元代建县，说明县级行政建置具有较长历史，但建县时间不能等同于地方社会从此才出现。古代村落、迁徙通道和家族记忆往往早于现行行政建置。元代以来的县制、琼北行政体系和村镇网络，为明清时期的教育发展提供了制度背景。明清时期，定安成为琼北科举传统的重要组成部分，科举、教育和仕宦经验在当地形成了重视读书、重文章和公共名望的文化记忆。不过，这种传统应被理解为长期教育实践和地方文化的积累，而不能直接解释为现代社会中某个家族或派别长期控制政治。
+母瑞山是定安历史空间中的特殊节点。相关遗址使地方历史不只存在于文字记载和后来的行政沿革中，也保存在早期人类活动所留下的物质遗存中。母瑞山与县城及周边乡村共同构成“文献历史—考古材料—现实地域”的多层结构。分析定安时应避免把后来的行政边界投射到古代，也不能因为存在科举传统，就把当地政治想象成单纯由读书人主导。
+【人口与语言民系】
+2000年第五次全国人口普查显示，定安常住人口为27.96万人，在本组四县中低于澄迈和临高。该数字属于第五次全国人口普查时点常住人口口径，不代表现阶段人口规模。定安传统人口主要与琼北乡村社会相联系，同时受到海口等中心城市就业、就学和产业活动的外向影响。人口外流与迁入并存，会使县域社会的语言结构、职业结构和地方认同持续变化。
+语言环境以海南地方话、闽南—海南语群内部方言及普通话等为主。历史移民可能带来不同籍贯和语言经验，但长期共同生活会造成语言混合、转用和代际更替。语言相似程度与族群来源之间可以有关联线索，却不是可以直接互换的解释变量。定安不能因为属于琼北，就被笼统描述为单一民系；也不能因为历史上存在跨区域迁徙，就把所有地方关系都理解为外来的。明清科举带来的家族记忆，可以影响地方对教育、功名和公共责任的重视，但不能证明当代居民具有相同血缘结构，更不能成为政治阵营的替代指标。
+【产业与交通】
+定安传统产业以农业、林业、热带作物、水果种植和农产品加工为主，县城及交通节点还承担教育、医疗和公共服务集散功能。县域南部山地、丘陵与北部河谷的生产条件不同，产业布局不会完全一致。南渡江中游联系提供了向南、向北运输的基础，但内河运输能否转化为现实优势，还取决于河道维护、公路衔接和物流组织。
+定安距离海口较近，这一区位具有双重意义。一方面，县城可以承接省会城市的消费、信息、教育和就业需求，形成面向城市市场的农产品和服务供给；另一方面，人口接近核心城市并不自动转化为本地产业升级，部分居民可能更倾向于外出就业或迁居，使本地消费能力受到人口流出的影响。定安的发展条件在于能否把农业资源、县域服务和交通节点结合起来，延长加工及流通链条，同时把海口近距离优势转化为县域就业，而不只形成单向的人口外流。
+交通上，定安处于连接澄迈、屯昌、文昌和琼海的重要位置上，是琼北腹地的节点型县域。道路改善能够扩大通勤和市场范围，但也可能使居民的消费选择、就业机会和公共信息更多指向海口。行政上的“近海口”不能直接等同于经济上的“依附海口”，其结果仍取决于本地产业组织、教育服务和交通效率。
+【族群和政治生态分析】
+定安可确认的政治与社会条件，包括乡镇和村级组织、地方宗族与婚姻网络、教育文化传统以及县城与乡村之间的资源联系。明清科举传统能够沉淀教育声望和公共表达方式，现代教育又为居民参与公共事务提供文化基础。但科举遗风不能直接转化为现代选票，更不能推导出所谓士绅派长期控制县域政治。真正影响选举与公共决策的，仍是具体候选人、村庄组织、地方利益、议题立场和政策结果。
+条件性推论是，若涉及学校、道路、水利、土地和县城发展，县城居民与乡村居民的关注点可能不同；教育联系较多的人群可能更重视公共服务和信息透明，农业生产者可能更重视资源分配和产品市场。海口近缘性可能加强跨县通勤、商业联系和人口流动，使地方利益不再完全受县界约束。不同家族、村落和职业群体可能形成阶段性联盟，但科举身份或海南话使用者不能被预设为统一政治集团。
+因此，定安若存在较明显的选举分化，原因更可能来自城乡差异、资源项目、人口流动和组织动员。不能在缺少候选人资料、竞选议题和村级结果的情况下，把其归类为天然“蓝”或“绿”。定安独特的文化资源可以影响政治话语，却必须经过现代制度和社会关系转换，才能成为现实支持力量。
+【资料口径】
+本文人口数据采用2000年第五次全国人口普查常住人口27.96万人，不与现阶段户籍人口或未核实数据混用。历史部分以元代建县、明清琼北科举和母瑞山遗址等档案事实为基础，不将古代建置与后世地方身份简单等同。语言民系不作族群决定论推断，政治部分明确区分制度、文化和产业事实与条件性推论，不套用台湾或其他地区的政党—族群对应关系。</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="360" customHeight="1">
+      <c r="A14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>屯昌县</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>屯昌县：新中国后的县域建构、内陆交通与农垦社会
+【历史与空间】
+屯昌县位于海南岛东北部内陆，处于琼北山区、盆地和河谷的交接地带，周边联系文昌、琼海、定安等传统行政区域。与澄迈、临高等北部沿海县份相比，屯昌没有直接面向北部湾的港口区位，县域发展更依赖内陆公路、农产品运输和周边城市联系。南部与北部之间的山地和河谷既构成自然分界，也使不同片区的村落分布、行政联系和商品交换具有差异。
+屯昌作为1949年后新设县，其县级行政建置属于现代国家地方治理重构的结果。现有县名、县界和行政机构不能简单追溯到古代长期连续的县级政治共同体，但这并不意味着当地村落和居民没有更早历史。屯昌境内部分村落的形成、家族关系和语言传统早于现行建县，民众的地方记忆也可能仍保留对定安、文昌等旧行政区域的归属感。因而，现代县界与更早的地方社会之间存在叠合和错位。
+这种“行政建县较新、村落历史较深”的特点，是屯昌县情的基本结构。县域认同是在交通、学校、行政和市场联系中逐步形成的历史过程。屯昌不应被描述为没有传统的空白地区，也不能因为县名较新，就假定居民之间已经形成完全统一、排他的地方认同。
+【人口与语言民系】
+2000年第五次全国人口普查显示，屯昌县常住人口为25.27万人，在本组四县中最少。该数字属于五普常住人口口径，不能直接用于推断现阶段人口规模或人口减少幅度。屯昌人口以农村人口和外出就业人口为重要背景，年轻人口向海口、文昌、琼海等地流动，会对本地年龄结构、劳动力供给和公共服务需求产生影响；但具体变化仍需要分年度普查、户籍和迁移资料验证。
+语言方面，屯昌内部存在长期形成的海南地方话及不同村乡间的方言差异，同时受到普通话、粤语等语言的影响。移民和农垦人口进入后，还可能带来新的语言组合。屯昌话不能与某种单一族群画等号，语言使用者可能同时具有跨村、跨县甚至跨省经历。另一方面，某村居民即使使用相近方言，也不必然具有相同的祖籍或政治立场。民系分析应把语言、迁徙、婚姻和代际变化分开，不能因为新县建构就否定旧有地方社会，也不能因为祖籍不同就把居民固化为对立群体。
+【产业与交通】
+屯昌的县域经济具有明显的内陆农业和农垦传统。热带经济作物、林业、水果种植、农产品加工及相关服务业，是人口集中于农村地区的重要基础。历史上由移民、农场和地方村社共同参与的农垦过程，使国营或集体生产组织、农户承包经营和跨村土地关系相互交织。与单一血缘村落的理想类型相比，这类社会中的劳动分工、资源使用和公共收益关系更复杂。
+交通是屯昌扩大发展空间的关键。公路把县城、南部乡镇和北部片区与定安、文昌、琼海及海口联系起来，农产品和人员可以经由周边城市市场完成交易。屯昌虽无直接港口，却可能通过文昌、海口或琼海等节点接入更大经济体系。内陆位置使其对道路条件和物流成本更敏感：道路改善可扩大市场半径，但也可能使本地消费和就业进一步向外部城市集中。
+因此，屯昌需要把交通优势转化为农产品加工、农村就业和县域服务，而不能只依靠原料输出。农户、农场、村集体和外来经营者之间的利益关系，也会影响地方公共议题。产业发展带来的就业和税收可能强化县城吸引力，但收益如何分配将决定这种增长能否转化为稳固的地方社会支持。
+【族群和政治生态分析】
+屯昌政治生态中可以确认的基础，是新县行政建构与较早村落共同体并存。居民既可能认同屯昌县公共服务和行政体系，也可能保留跨县宗族、婚姻及土地关系。农垦、农场和移民活动形成的社会网络，可能比传统县域沿革更深地影响基层合作。现代乡镇和村社组织提供正式政治渠道，但非正式亲缘、地缘和职业网络仍会影响信息传播、公共动员与集体行动。
+条件性推论是，在土地、水利、道路、农场改制或农产品加工项目中，不同组织之间可能因收益和责任分配形成合作或冲突；外出务工家庭与常住农村家庭也可能存在不同的公共事务偏好。语言相近或祖籍相同的群体不必然共同支持某一候选人，跨县社会关系也不能直接转换成跨县政治立场。屯昌县界能够划定行政责任，却未必能够完全划定地方社会网络。
+所以，屯昌若被描述为具有某种固定“蓝绿倾向”，必须避免以农垦身份、外来人口或行政建县历史作简单推断。更合理的分析是考察具体政策如何被不同村社和职业群体理解，以及交通、项目和人口流动如何改变选举议题。在没有真实竞选材料和投票结果的情况下，政治颜色不能从县域历史中直接推出。
+【资料口径】
+本文人口采用2000年第五次全国人口普查常住人口25.27万人，不混用阶段性户籍数字，也不推断当前人口趋势。县域历史以1949年后新设县、琼北内陆区位、交通和农垦事实为基础，并明确区分行政建县时间与村落社会历史。语言不作族属直接推定，移民与本地居民也不作固定政治群体处理。政治分析仅从行政建构、农垦组织、交通项目和人口流动推导可能条件，所有“蓝绿”判断均须以实际选举材料为依据。</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1781</v>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="360" customHeight="1">
+      <c r="A15" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>澄迈县：河海交汇节点、咖啡农业与多元人口构成
+【历史与空间】
+澄迈县位于海南岛北部，处在南渡江下游、琼北平原与西部滨海地带之间，县域内部并非均质空间，而兼有河口沉积平原、沿海台地、港湾和丘陵山地。南渡江及其支流所形成的交通廊道，是传统聚落形成和区域交换的重要依托。老城位于南渡江下游地区，长期承担县城、行政管理和集市贸易功能，其历史价值不仅在于旧城格局，也在于它曾把内陆乡村、河流码头与北部沿海联系在一起。与老城不同，马村港面向北部湾，具有渔业、航运和人员往来的港口属性；福山则处在河流、滨海平原与西部侨乡社会的交汇位置。三者分别体现行政—集市、海洋运输和侨乡—农业三种空间功能。
+澄迈的位置使其处在海口、琼北腹地与临高等周边区域之间，既接受中心城市的产业和人口辐射，又保留较强的地方社会基础。对县域空间而言，澄迈的发展并不是沿单一海岸线展开，而是通过道路、河流和港口把沿海节点与内陆村乡连接起来。老城是历史积累的中心，马村港是外向联系较强的节点，福山及南部、东部村落则构成更广泛的生产腹地。将这些地区简单概括为一个“港口型县”或“农业县”，都会忽略其内部差异。
+【人口与语言民系】
+人口规模以第五次全国人口普查为基准：2000年澄迈县常住人口为43.47万人。在本组四县中，澄迈人口规模相对较大，既有传统农业人口和历史村落人口，也有沿海就业、港口活动、产业发展及跨地区迁移所带来的人口增量。人口并非均匀分布于全县，南渡江沿线、老城周边、沿海乡镇和主要交通节点通常具有更密集的聚落条件，丘陵和偏远村落的人口分布相对分散。
+语言方面，澄迈长期存在海南地方话、闽南—海南语群内部方言以及普通话、粤语等多种语言使用环境。语言首先是日常交往工具，不能直接等同于族群身份，更不能因为某种方言的使用者较多，就推断其具有统一的政治立场。客家来源人口在澄迈确有分布，但主要表现为加乐、文儒等部分地区的局部聚居或社会网络，不能把客家语言、客家认同扩大为澄迈全县的共同属性。与此同时，外来人口也可能因长期居住而使用当地语言，迁入群体内部也未必保持完全一致的语言结构。因此，研究民系关系时，应把祖籍、语言、住宅形态、婚姻网络、宗族联系和现实利益分别考察，而不能相互替代。
+【产业与交通】
+澄迈的产业条件具有明显的河海复合特征。农业方面，福山咖啡具有较强的区域辨识度，是澄迈面向市场的特色农业名片；富硒农业则依托土壤和农产品质量特色发展种植、养殖及加工。二者都不能简单理解为全境所有农户都从事咖啡或富硒产品生产，而应理解为特定区域形成的产业链和地方品牌。澄迈同时发展热带经济作物、瓜果、渔业和滨海生产，农业内部既有自给性种植，也有面向市场专业化，不同产品对交通、收购渠道和加工能力的要求并不相同。
+交通上，南渡江和北部湾港口构成历史上的水运基础，现代公路则把老城、沿海港口、福山及内陆乡镇纳入不同方向的交通网络。港口对临港产业、渔业和旅游具有带动作用，但港口经济的影响并非平均覆盖所有乡村；内陆农业片区更加依赖公路、农产品收购体系和海口等外部市场。澄迈靠近海口，既具有接受客源、资金和产业转移的优势，也可能面对更强的区域竞争。其产业升级的关键并非单纯扩大单一种植，而是能否形成加工、物流、品牌和销售相互衔接的体系。
+【族群和政治生态分析】
+可以确认的政治生态事实，是澄迈存在乡镇行政体系、村居民自治组织和多种地方社会网络。日常政治参与首先发生在具体村落、社区和单位，而不是抽象的全县族群层面。老城、港口和农业区所处的经济位置不同，关注的公共议题也存在差异：港口及商业节点更关心交通、用地、就业和经营环境；传统农业村落通常更关注土地、水利、道路、灾害治理和农产品价格；不同来源的居民还会围绕学校、市场、移民安置和社会保障形成新的共同利益。
+这些只能构成条件推论，而不能推出固定的“蓝绿”结论。原有居民与新迁入者之间可能形成合作，也可能在公共资源分配上出现分歧；老城的历史社会网络可能影响组织动员，港口和企业节点则可能形成新的职业与利益联盟。方言相近、地方认同相同或祖籍相近，都不必然产生一致的政治选择。澄迈如果出现阶段性选举倾向，更可能取决于候选人能否处理具体利益议题、组织动员方式以及不同村庄之间的关系，而不能从海岛位置、方言或产业标签直接推定。若使用“蓝绿”作事后描述，必须以真实选举结果和票源分布为依据，不能把该概念预先变成居民身份标签。
+【资料口径】
+本文人口数据采用2000年第五次全国人口普查常住人口口径，即43.47万人，不使用未核实的2020年异常数字，也不据此直接代表现阶段人口。建置沿革、老城、马村港、福山咖啡和富硒农业采用县域档案及公开官方县情的概括。客家人口仅按加乐、文儒等局部情况表述，不外推为全县民系结构。政治部分严格区分可确认的制度、产业和聚落条件与条件性推论，不预设县域整体具有固定党派倾向。</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>1783</v>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="360" customHeight="1">
+      <c r="A16" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>临高县</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>临高县：西北滨海社会、语言分类争议与港口—农业分化
+【历史与空间】
+临高县位于海南岛西北部，处于南渡江下游地区、琼北西部乡村和北部湾滨海地带之间，县域同时受到山地、河流、平原和海岸的影响。传统聚落并非只沿一条交通线发展：西部沿海村落更多受到海洋生产、渔业和商贸活动影响，中部河流与平原地区承载传统农业和乡村集市，内地乡镇则连接琼北腹地与沿海节点。加来、和舍等内陆地区因此不仅是行政乡镇，也是人口、货物和地方社会向外交流的节点。临高角及沿海港湾则强化了县域面向北部湾的空间特征。
+临高的历史不能简化为一条从内地迁入的单线过程。较早的州县建置、琼北行政体系、沿海港口活动以及近代移民共同塑造了今天的地方社会。与一些历史悠久且县城格局相对稳定的老县相比，临高县域内的行政中心、港口和交通功能曾经历不同阶段的调整，形成了传统村乡、近代城镇和新兴港口相互叠加的结构。沿海南部更容易受到海洋经济和跨海联系影响，腹地村落则与定安、琼山及琼北其他县保持密切往来。这种空间差异为理解临高的语言和民系提供了基础，但不能反过来以语言差异制造固定的社会边界。
+【人口与语言民系】
+2000年第五次全国人口普查显示，临高县常住人口为38.93万人。该数据反映的是五普时点的常住人口口径，不等同于现阶段户籍人口，也不宜直接用于判断此后人口增减。其人口结构包含本地传统居民、历史移民后裔以及近现代迁入人口。海岛县的人口流动往往具有跨区域、多来源和多阶段特征，外来人口长期居住后可能建立新的婚姻和职业关系，因此祖籍与现实身份并不总是完全一致。
+临高话是理解临高社会的重要线索，但必须严格区分语言学分类与族群认同。语言名称与居民自称、他称之间可能存在差异，某地使用某种方言也不意味着其居民构成单一血缘或政治共同体。临高话与临高人的身份不能直接画等号；对临高话进行历史比较、提出与其他语群相似或存在接触，也都不足以证明其语言归属，更不能在缺少系统语言学证据时对其语系归属作断语。语言归属是学术分类问题，族群身份则需要自认、他认、迁徙史和社会组织等材料，两者应当分别处理。
+和舍存在客家人口或客家社会网络，但目前材料只能支持其客家成分具有一定存在，不能证明客家人在临高县占据主导地位。临高其他地区还存在海南话、普通话、粤语等语言环境。语言分歧可以影响文化传承和社交范围，却通常不会直接形成一致的政治阵营。把所有“临高人”视为同一人群，或把会讲临高话的人当作单一利益集团，都会忽略县域内部的地方差异与人口流动。
+【产业与交通】
+临高拥有较长的北部湾岸线，海洋渔业、滨海生产、港口运输和旅游构成沿海产业的重要条件。临高港等港口节点提高了县域与湾外地区联系的可能性，但港口带来的物流、临港项目和就业并不会自动均匀分布到全部乡镇。邻近洋浦港区所带来的产业联系，也是临高面向北部湾经济体系的重要外部条件；这种联系属于经济腹地和交通联系，不等于洋浦的行政功能自动延伸至临高。
+农业方面，临高传统热带作物、水果种植、林业及滨海养殖等领域具有地方基础。内陆农业对公路、灌溉、农产品收购和加工渠道的依赖较强，沿海村落则更受海况、渔业资源、市场价格和港口建设影响。加来、和舍等内陆节点承担人员往来和货物集散功能，县域交通将西部沿海与琼北腹地连接起来。临高发展的核心条件，是把港口流量转化为可持续的地方产业和就业，而不是单纯依赖邻近大港；同时还需改善内陆村落与沿海节点之间的利益联结。
+【族群和政治生态分析】
+临高政治生态中可确认的条件，是沿海与内陆、村落与港口、传统农业与海洋经济之间存在明显差异。沿海社区的议题可能集中于渔业、港口、生态和旅游；内陆社区更重视土地、灌溉、道路、种植收益和公共服务；客家聚居区则可能同时面对地方语言、宗族网络和外来人口关系。县域内部还可能存在跨乡镇婚姻、贸易和宗族联系，使政治动员超越行政边界。
+条件性推论是，若港口投资、征地、渔业资源或交通建设成为中心议题，港口周边村庄和内陆村落的利益表达可能明显不同；新旧居民网络也可能围绕公共资源形成阶段性合作或竞争。但不能由此认定临高天然属于任何一种政治颜色。临高话使用者不是单一政治选民，客家人口规模有限且集中于局部，也不构成全县性的力量平衡。更合理的判断是，临高的政治变化更可能受具体项目、候选人组织能力、地方网络和跨区域经济联系影响。所谓“蓝绿倾向”若要成立，必须由实际候选人、竞选议题和选举结果证明，不能从方言身份或滨海区位倒推。
+【资料口径】
+本文人口采用2000年第五次全国人口普查常住人口38.93万人，不混用户籍人口，也不外推当前规模。历史地理、产业和交通依据县域档案及公开官方资料进行区域概括。临高话只作为地方语言现象讨论，不与“临高人”身份等同，也不在证据不足时对其语系归属作断语。和舍客家情况按局部存在表述，不将客家网络扩大为全县主体。政治分析仅提出港口、农业、人口流动和地方组织可能产生的条件性影响，不把海岛行政单位套入外部社会的蓝绿结构。</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>1845</v>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="360" customHeight="1">
+      <c r="A17" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>白沙黎族自治县</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>白沙黎族自治县：中部山区的橡胶—绿茶—雨林生计，与黎乡社会的低烈度政治生态
+【历史与空间】
+白沙县位于海南岛中部偏西，处在五指山余脉南麓与西部山地的过渡地带，县境以山地、丘陵和河谷盆地相间为基本地貌，昌化江上游的支流切出深切峡谷，河谷两侧是黎族村寨最密集的聚居带。全县面积约三千平方公里上下，在海南中部各县中属中上规模，但可耕作平坝比例低，“山多田少”是所有县域经济的起点约束。建制沿革上，民国以前长期分属儋州、昌化、崖州等州县管辖的黎峒地区，历史上并非作为一个统一行政单位存在，直到二十世纪三十年代才被从周边县份析出置县，划出范围大体依据“文明”（汉人聚落）与“黎峒”（黎族村寨）的传统分野。置县之后，县治设在牙叉，即今天县城所在地，牙叉因处于昌化江支流与山间盆地的交汇点，逐渐形成汉黎杂居的行政与集市中心。二十世纪四十年代初期，白沙一带爆发过规模可观的地方武装起义，起义者以黎族、苗族和部分汉族农民为主体，打出反对国民党地方统治与苛捐的旗号，虽然组织和领导方式带有明显的地方武装色彩、未与全国性政治力量形成稳定衔接，但事件本身成为海南岛内陆山区社会结构的一次集中暴露。此后县内陆续建立国营农场与垦殖机构，来自岛外和岛内其他县份的职工进入山区，橡胶种植从零星栽培转为成规模的人工林产业，也由此形成了本地特有的“农场—村寨”双轨社会结构：一边是国营农场的职工户口、宿舍区和准城镇生活方式，另一边是延续传统村寨结构的黎族、苗族农村。交通方面，白沙至今没有铁路过境，高速公路从县境边缘掠过并设有互通口，主要干线是国省道与县乡道组成的公路网，县城与海口、三亚、儋州方向都有定时班车，但班次密度和准点率都明显低于沿海平原县。县城至各乡镇的山区公路在雨季常因塌方和漫水通行受阻，这种“季节性可通行”的交通条件直接影响农产品外运半径、旅游接待规模与公共服务财政的效率。
+【人口与语言民系】
+按第五次全国人口普查（2000年）数据，白沙县常住人口为164494人；按2010年第六次全国人口普查数据，白沙县常住人口为167918人。十年之间人口几乎持平，仅增加约3400人，增幅约2.1%，是海南中部山区县市中人口增长最慢的类型之一。这一点与同期海南全省人口快速增长、琼海、万宁、乐东、陵水等县市动辄数十个百分点的扩张形成鲜明对照，说明白沙属于典型的外流型县域：本地出生人口中有相当比例在升学、务工和婚姻迁移中离开本县，县城与农场吸纳能力有限，无法形成有效回流。2010年第六次人口普查显示，白沙县少数民族人口占比为67.43%，是海南五个黎族苗族自治县中少数民族比重最高的一个。需要说明的是，本工作簿旧资料中“少数民族约65%（黎62%＋，苗少量）”的记载系基于2000年前后估算，已被2010年普查数据覆盖，应当予以纠正；纠正后的67.43%意味着白沙在海南全岛范围已属于少数民族占绝对多数的县份，在五个自治县中亦居首位。
+语言与民系方面，白沙境内语言构成相对多元但层次清晰。最具代表性的是黎话，内部可分本地、赛等若干方言群，赛等话在白沙中南部的多个乡镇通行，与周边五指山、保亭的黎话方言存在连续谱关系。苗族人口在白沙规模很小，主要集中于个别山地村寨，使用苗话（属苗瑶语族苗语支）。县城牙叉及农场场部、海南农垦各站点，通行的通用语是海南话（属闽语海南片）与普通话，机关、学校、农场系统内部日常公务与教学语言以普通话为主。语言分布的地理格局十分典型：黎话跟随黎族村寨的分布带，苗话跟随苗族村寨的分布点，海南话集中在县城、农场和交通干线沿线的汉人聚落。三种语言之间的代际传承状况不同：海南话在城镇和农场内部传承相对稳定，黎话在村寨内部仍为主要交际语言但在中青年群体中已出现明显的语言转用，苗话因人口基数小、点状分布，传承最为脆弱。民系层面，白沙汉族居民内部来源复杂，除本岛北部、中部迁入的农民外，农场系统有相当数量的外省职工后裔，其后代在本地出生、成长，形成与“外来职工”身份分离的本地第二代；黎族村寨内部则延续以血缘家族和头人（本地称“苈”一类首领人物）为核心的互助与祭祀体系，这一体系在村寨事务、公议和水源山林管理中至今仍具实际约束力。
+【产业与交通】
+白沙的产业格局高度集中于橡胶、绿茶、南药与生态旅游四条线。橡胶是白沙最核心的支柱经济，建国后经由国营农场大规模开垦，20世纪六七十年代进入种植高峰，此后经历多次世界性胶价周期波动，目前以民营胶园、合作社经营与农场胶园并存的格局为主，胶农收入直接受国际天然橡胶期货价格影响，波动幅度大且缺乏有效的价格缓冲机制。白沙绿茶是本地具有明确地域标识的特色农产品，产区集中于中部偏北的山区村镇，以当地特有的土壤与气候条件形成独特风味，既有品牌化的商品茶，也存在大量以本地村寨为名的散装茶产品，产业链短、附加值提升有限。热带农业还包括槟榔、益智等南药作物以及荔枝、芒果等热带果品，种植集中于低海拔缓坡与河谷边缘。旅游方面，白沙依托邦溪、牙叉一带的黎族文化与山水景观、以及陨石坑地质奇观发展雨林与地质观光、生态体验类项目，客源以海口、三亚和本岛中西部自驾客为主，接待规模中等偏小，淡旺季差异显著，且高端住宿与交通配套不足限制了停留时间与人均消费。在交通基础设施上，白沙既无铁路，也无港口，公路是唯一对外通道，山区公路在雨季的通行不稳定直接推高了农产品运输成本、压缩了旅游产品的可运营窗口；县城至乡村的物流主要依赖社会化货运和邮政快递网点，末端配送成本偏高。此外，白沙还有规模化的国营农场体系，农场经济（种植、加工、场部服务业）曾长期是县内第二大经济来源，2000年代后随农垦管理体制调整，农场与地方财政的耦合方式发生转变，场部人口的社会身份介于职工与农民之间，是理解白沙县政治与社会结构时不可忽略的一层。
+【族群和政治生态分析】
+白沙是海南五个自治县中少数民族比例最高、黎族人口密度最大的县份之一，其政治生态的核心特征不在于激烈的党派竞争，而在于山地治理结构对社会关系网络的深刻塑造。黎族村寨以血缘家族和传统头人体系为组织基础，公共事务——祭祀、水源分配、山林权属、婚丧互助、纠纷调解——长期在村寨内部完成。这种结构在长期缺位状态下形成了较强的自我运行能力，也使外部政治力量进入村寨时面临较高的组织门槛：外部政党若要获得影响力，需要与村寨既有权威网络建立合作或借道关系，而非直接诉诸族群身份。黎族并不构成一个具有统一跨村政治意志的“族群”板块，其内部按村寨、宗族、方言群分化为大量平行的地方社会，“黎族支持某党”在白沙县内并没有可观察的组织基础。同理，苗族人口在白沙规模极小，缺乏形成独立政治影响力的社会基数，只能作为山地多民族共居景观中的一部分被描述。语言也不等同于民族：白沙县城通行的海南话使用者中有农场职工后裔、代际混血家庭和外来创业者，黎话使用者中同样包含长期与汉族通婚形成的家庭，方言边界与族群边界存在大量交叉重叠，用语言分布直接推断族群政治倾向在方法上不成立。
+经济基础决定了政治倾向的分布方式。橡胶与茶叶种植环节的劳动组织长期依赖家庭承包、季节性雇工和村寨内部的人力互助网络，这类劳动关系中的利益分配、雇工条件、借贷与赊购关系，构成了一种“人情—信用”型交换秩序；掌握胶价信息、收购渠道和运输资源的中介与商贩，在村寨中往往拥有超出其经济地位的谈判能力。农场系统的职工则处于另一种秩序中：编制、工资、住房、医保构成相对稳定但层级分明的制度化关系，场部与地方村社之间长期存在一种微妙的资源与关系交换。在这种双重结构中，依赖山地资源、集体土地和村寨组织的一方，与依赖外部市场、收购渠道和行政资源的一方之间，形成的不是明确的党派阵营，而是围绕具体利益节点的松散取向。当外部政治力量以民生改善、公共服务、产业发展、道路交通为议题进入这些节点时，它们确实能够获得支持；但这种支持是“议题—利益”导向的条件性支持，而非“族群身份”导向的忠诚。一旦橡胶价格、征地补偿、林地确权、移民搬迁或公共服务供给等具体议题条件改变，其支持基础即随之转移或消散。白沙县内山地面积大、平地少、耕地零碎，历史上形成的“山兰米+胶园”的复合生计，使村寨对山林资源的依赖极强；任何涉及山林权属、林权流转、生态保护与产业开发的决策，都会直接触发村寨层面的利益重新分配，这是本地政治讨论最频繁、也最具实质性的议题领域。
+在县域内部的政治关系上，白沙的族群关系相对和谐，黎族、汉族、苗族长期共居通婚，未出现显著的高烈度族群冲突记录。这与山地社会封闭性较强、人口规模有限、缺乏外部大规模移民涌入直接相关。但“和谐”与“一致”是两回事：山地村寨之间因水源、山林、边界、历史积怨而形成的纠纷，往往以宗族内部或村际方式解决，其结果很少进入正式政治程序，因此县域政治在外观上呈现“低冲突”特征，但这部分张力实际以非正式机制的方式运行。
+落到具体的政治表达形态上，白沙属于典型的“农业—山地型县域政治生态”。第一，决策高度依赖上级财政转移支付与专项项目，本地财政自主空间有限，公共服务的改善节奏由项目获取能力决定。第二，族群身份本身不具备独立的政治动员效力，真正发挥作用的是村寨组织、宗族关系和业缘网络；任何声称能以“黎族身份”直接换取选票的判断，在白沙的实际选情中难以成立。第三，代际差异是比族群更有效的分歧轴：60岁以上群体与1990年后出生群体在公共服务预期、产业发展偏好、外出就业取向上的差别，往往超过不同民族之间的差别；在外流型人口结构下，青年群体的持续离县使基层政治参与度下降，“代际更替”成为县域政治的主要变量而非“族群更替”。第四，外部力量（政党、政策、NGO、宗教组织）进入白沙最有效的路径，是与村寨权威网络合作开展教育、医疗、水利、生态项目，而不是以族群代表身份介入。第五，橡胶与茶叶的价格周期持续塑造着县域政治议程，是理解白沙选举与公共讨论时最有效的解释变量之一，其影响强度远超任何族群因素。综合而言，白沙的“蓝绿”结构——如果借用这一台湾类比工具的话——更接近一种低烈度、议题主导、多方互动的均衡状态，既缺乏“外省人—本省人”式的身份断裂，也不存在以族群为轴心的稳定动员；其政治走向更可能由中央与省级政策的资源配置、山林与土地制度的具体安排、以及农产品市场价格的周期波动所共同决定。
+【2020年七普人口补充】2020年11月1日零时，白沙黎族自治县常住人口为164699人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+本文数据与事实口径说明如下：人口数据采用国家统计局第五次（2000年）与第六次（2010年）全国人口普查常住人口口径，白沙县2000年为164494人，2010年为167918人；少数民族人口占比采用2010年第六次人口普查数据，为67.43%。本工作簿原“县市事实档案”表所载白沙“少数民族约65%（黎62%＋，苗少量）”系2000年前后估算值，已被2010年普查数据取代，本表在此予以纠正，相应地，五指山、琼中的旧值同样需要按普查数据更新。历史沿革部分（1935年置县、1943年白沙起义、黎族传统“合亩制”社会）来自公开的地方志与党史资料，属定性叙述，不含精确计量。语言与民系分布依据《海南话》《中国语言地图集》及海南省语言文字工作部门公布的方言点资料，黎话内部方言群划分（本地、赛等）为方言学通行分类，具体到乡镇的界线存在重叠，不宜作为精确边界使用。产业与交通数据来自公开统计年鉴、地方政府工作报告与行业公开资料，橡胶产量、绿茶产值、旅游接待人次等具体数值随年度波动，本文只作结构性描述，未引用单一年份的确切数字。族群构成比例按普查登记的民族身份统计，与日常语言使用情况、宗族认同和自报认同并非同一概念，交叉分析需另行核实。政治生态分析部分为基于公开选举、施政与政策资料的推断性框架，属于条件性判断，不构成对任何政党支持率或族群投票倾向的实证测量，也不预设任何族群与任何政党之间的对应关系。</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>4286</v>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="360" customHeight="1">
+      <c r="A18" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县：石碌矿工与昌化江口渔镇的双重生计结构，及其条件性政治取向
+【历史与空间】
+昌江黎族自治县位于海南岛西部，昌化江自南向北纵贯县境中部，江北为石碌—叉河—太符的工矿与丘陵地带，江南为昌化—乌烈—海尾的沿海台地与河口沙坝，东西两侧分属雅加大山和尖峰岭余脉的支脉。全县地形南高北低，沿海平坝面积有限，山地丘陵占比高，是典型的“一江两岸、工农分立”的县域空间格局。历史沿革上，昌江一带自隋唐以来即为独立的州县建置，先设定川县，唐代改称昌化县，沿用至清末；民国时期于1914年前后改昌化县为昌江县，县界大体沿用至今。昌化县城位于昌化江入海口附近，是历史上琼西重要的江海转运节点，江面上行可通至上游山区，下行经昌化港出海，古代与内地的盐、粮、渔获贸易多经此集散，因此县城在明代之前即形成汉人聚居核心与相当规模的墟市。二十世纪三十年代至四十年代，石碌铁矿的发现与开发彻底改变了昌江的县域格局：矿区位于昌化江中游东岸，因矿体露天可采、储量集中、品位较高而被迅速开采，1939至1945年间曾被日军占领并掠采，抗战结束后由国民政府资源机构接管，1949年后转为国营矿山，1950年代起大规模机械化开采并配套建设选矿、铁路专用线、供电与生活区。石碌矿的扩张带来三个后果：一是昌江的县域经济重心由江海转运转向矿产采选与配套工业；二是县城功能相对衰减，行政与商业重心随铁路与公路干线的建设逐步向石碌、叉河一带迁移；三是大量外省技术员工、干部、工程人员及其家属在矿区定居，形成了与本地汉族农民、黎族村寨并存的“矿工移民”群体，其后代已普遍在本地出生，构成昌江最具特色的社会层次。石碌铁路是岛内干线之一，连接矿山与港口、铁路沿线设有叉河、昌江、海尾等站，铁路与港口的组合使昌江成为海南少数同时具备陆运与海运通道的西部县域。2000年代以来，昌化江中下游的核电与化工项目进一步强化了昌江作为海南西部重工业与能源基地的定位，太符、风坡一带的工业布局与县城、矿区的功能区分日益明显。
+【人口与语言民系】
+人口数据方面，按第五次全国人口普查（2000年），昌江县常住人口为219502人；按2010年第六次全国人口普查，昌江黎族自治县常住人口为223839人。十年增加约4300人，增幅仅约2.0%，是海南人口增长最为停滞的县份之一，与全省多数县市动辄数十个百分点的人口扩张形成极端对比。这一停滞特征直接反映了昌江的人口结构特征：本地自然增长率并不低，但外流与流入大体相抵，中部山区的黎族村寨人口持续外流至沿海与内地，而矿区的技术与管理岗位在2000年以后随矿业景气度下降，新增就业吸纳能力有限。2010年第六次人口普查数据显示，昌江黎族自治县少数民族人口占比为38.65%，其中黎族为绝对主体，苗族数量很小，另有少量回族。需要指出的是，本工作簿旧资料记载的“少数民族约37%（黎为主）”为2000年前后估算值，与2010年普查数据存在小幅偏差，且精度显著低于普查口径，统计与引用时应以38.65%为准；旧表中“黎约15%、苗约0.8%”的全岛构成数据亦为估计值，不能与县级普查占比混用。
+语言与民系方面，昌江是海南语言层次最复杂的县份之一。沿海与江口地带的儋州话（属粤语系支，是昌江最大的语言片区，覆盖昌化、乌烈一带及部分农场）构成昌江的主体语言；县城及公路干线上通行的海南话（属闽语海南片）在行政、教育、商业场合占主导；此外还有三支规模不大但特征鲜明的方言：其一为军话，通行于昌化—乌烈—海尾的部分村落，军话是明代卫所军户后裔在数百年迁徙与本地化过程中形成的方言，与闽南、粤语均有渊源，分布相对零散但村落聚居度高，每村几乎全村通用；其二为村话（学界亦称“海南村话”或“土话”），通行于昌化江口两岸的部分村落，其语言来源与分类仍有学术争议，官方普查多登记为汉族，是海南岛内较独特的语言群体；其三为黎话，集中在七叉、王下等南部山区乡镇，属黎语杞方言与哈方言系统。苗话在昌江几乎不构成独立片区，仅见于个别山村。民系构成上，昌江汉族人口内部至少包含儋州人、琼北迁入的海南话民系、明代卫所军户后裔、明清及近现代陆续迁入的外省移民（以矿工、农场职工、渔业从业者为主）四个来源层次，各层之间的通婚已相当普遍但仍保留清晰的地方认同；黎族村寨主要分布于七叉、王下等南部山地，保留村寨组织和头人传统的完整性较高。语言与民族之间存在明显的不重合：儋州话使用者登记为汉族，军话使用者亦为汉族，村话使用者按普查登记为汉族，只有黎话使用者与黎族身份高度对应；把昌江的语言分布直接换算为族群政治立场，会系统性地误判当地社会。
+【产业与交通】
+昌江的产业支柱高度集中于矿产、核电与滨海渔农三条线。石碌铁矿是全岛最大的露天金属矿，也是昌江县域经济的绝对核心，其采选、铁路外运、供电、供水与生活区服务构成一个自成体系的产业社区，直接决定了县城的经济体量、税收结构与就业容量。2000年代以来，昌江的能源与重化工业扩张显著，昌江核电项目选址于此，与之配套的化工、建材、港口物流集中在太符、风坡一带，使昌江从单一矿业县转变为海南西部能源与重化工基地。这一转型带来双重效应：一方面带来了新一轮的技术人员、基建工程与产业投资流入；另一方面，矿业与核电的污染管控、水资源分配、征地补偿、厂区与居民区空间隔离等问题，成为县域内最具争议性的公共议题。2010年以后，矿业景气度下行叠加产业转型，昌江出现了典型的“资源型县域转型困境”：主要税源高度集中于少数国有大型企业，产业链本地化程度低，企业的用工、技术与管理层与本地社会的耦合度有限，县城商业与服务业对矿业和能源投资周期的敏感度极高。
+农业方面，昌江南部七叉、王下的黎族山区以热带经济作物为主，包括橡胶、芒果、槟榔和南药，香蕉与芒果是近年产量增长较快的品类，山区村落普遍存在“外出务工＋留守种植”的双栖生计结构，务工收入已成为多数黎族家庭的主要现金收入，种植业更多承担着土地与社保兜底的功能。沿海的乌烈、海尾一带是渔港型小城镇，渔业、渔获转运、渔船补给与近海养殖构成当地的经济基础，港区的劳动力高度集中于渔业及关联服务业，形成了与矿区截然不同的职业结构和利益网络。全县还有若干规模化农场，主要分布在东北部与沿海过渡地带，以热带作物种植为主，农场职工构成一个规模可观、口径独特的社会群体。
+交通方面，昌江是海南西部少数同时具备铁路、海港与高速公路的县份：石碌铁路承担大宗矿产品与部分客货运输，昌化港、乌烈港等港口承担海运衔接，环岛高速公路在县境设有昌江、白沙（部分）、叉河等互通点，公路网密度在海南西部相对占优。铁路专用线与公路干线的存在，使石碌、叉河一带较早形成了交通枢纽型的聚落结构，也使昌江成为海南与内地物资交换的重要节点之一。交通优势的另一面是空间分割：铁路走廊与工矿、港口带和南部黎族山区之间长期存在显著的可达性落差，山区的公路等级与班次条件明显弱于沿海与矿区，干线交通带来的产业红利难以均匀渗透到黎族村寨内部，区域内部的发展落差被交通干线进一步放大。
+【族群和政治生态分析】
+昌江是海南政治生态结构最复杂的县份之一，其复杂性来自三套并行且张力明显的社会秩序的叠加：矿区秩序、黎族村寨秩序、滨海渔农与农场秩序。这三套秩序各自有其组织规则、利益分配机制和人际网络，相互之间几乎不共享权威来源，也缺乏稳定的沟通机制。
+先看矿区。矿工社区的形成史决定了其政治属性：石碌矿的开发始于二十世纪三十至四十年代，最早的从业人员来自湖南、湖北、河北、山东、河南等地，1949年后随着国营化，技术人员、干部与一线职工的来源进一步扩大，其后代在昌江出生、成长并就地上学就业。这一群体在语言上多已转为以海南话或普通话为主，在族群身份上登记为汉族，在文化记忆上却保留了“外来者及其后代”的清晰边界。矿区的组织方式是高度制度化的：单位、班组、工资级别、住房分配、子女就学与医疗，构成一套完整的准户籍体系，职工对单位的依附性远高于一般农户对土地、村委会的依附性。这种制度化依附塑造了矿工群体的政治行为模式：他们更倾向于通过组织渠道、单位内部和体制内途径表达诉求，对依赖村社关系、宗族网络的动员方式较为疏离，对外来的、以地缘和血缘为纽带的社会组织保持着明显的距离感。这种高度组织化、纪律性强的产业社区，在政治倾向上更容易与国家体制、地方行政和大型国有资本保持一致，并对任何削弱单位地位的私有化、外包、产权变动保持高度警觉。需要强调的是，这是一种由单位依附关系与就业稳定性所决定的结构性取向，与“原住民—移民”身份认同、族群认同或语言认同均无直接关系。把矿工群体简单归类为“外来族群”并据此推断政治立场，会完全偏离实际。
+再看黎族山区。昌江的黎族人口主要分布于七叉、王下等南部山地，2010年普查占比38.65%在五个自治县中最低（低于白沙的67.43%、五指山的67.34%、琼中的66.44%和保亭的70%上下），但绝对人口规模并不小，且集中度极高。昌江黎族村寨延续着以血缘家族和传统头人为核心的组织结构，祭祀、山林、水源与婚丧互助在村寨内部完成，外部力量进入需与既有权威网络协商或借道。黎族村寨的政治表达高度条件化：涉及山林权属、林权流转、生态保护补偿、土地征收、林地与胶园开发、水源分配等具体议题时，村寨立场清晰而强硬；不涉及这些议题时，黎族与其他群体之间并无显著的政治分歧。黎族并不构成统一政治板块，其内部按村寨、宗族、方言（杞、哈）分化为大量平行社会，“黎族支持某方”在昌江没有可观察的组织基础。语言不等于民族：昌江的儋州话、军话、村话使用者均登记为汉族，各方言片之间的通婚与混居已持续数代，把儋州话或军话人口当作“族群”进行政治归类是方法错误。
+第三层是滨海渔农与农场秩序。乌烈、海尾一带的渔镇经济高度依赖渔业与近海作业，劳动力密集、职业风险高、对中间商与市场行情敏感，形成了与矿区截然不同的利益结构：渔民关心的是渔获价格、渔业资源、油料与船网成本、港区秩序与渔业管理；矿工关心的是单位稳定、工资福利、安全生产与资源开发政策；两者的政治关注点几乎不重叠。这种职业分化在投票时的表现通常是“各投各的议题”，而非形成统一的意识形态阵营。农场职工则介于两者之间：既有单位属性，又与地方社会深度交织，在资源与利益的具体分配上常常采取模糊而务实的位置。
+将三层结构合起来看，昌江县域政治的实际运行逻辑可以概括为“职业与组织归属优先、族群身份次之、议题条件性最强”。第一，昌江的政治分歧轴线是产业（矿业能源／渔业农垦），而非族群或语言。第二，矿区与渔镇之间是海南岛内少数接近“外省产业移民—本地渔农”结构性差异的组合，但两者的差异是职业和单位属性造成的，而非1949年后跨省人口迁徙形成的大规模族群对立，因此其强度远低于台湾同类结构。第三，黎族山区是县域内政治动员难度最大的区域：其利益表达高度依赖村寨权威网络，外部政党若要获得山区支持，最有效的路径是与头人、宗族、宗教和基层服务体系合作，而非诉诸民族身份。第四，在全县层面的重大议题（矿山开发、核电与化工选址、征地补偿、生态与水资源）中，族群身份的权重下降，职业与土地利益的权重上升。第五，代际更替是比族群更有效的变量：矿区第二代与第三代、黎族外出务工青年与留守长辈、渔业新一代与老渔民之间，在就业预期、公共服务偏好、是否外出、如何看待开发项目上的分歧，普遍超过不同民族之间的分歧。第六，在没有重大资源开发争议的时段，昌江县域政治呈现“低烈度、多议题、务实化”的基本面貌；一旦出现涉及单位改制、征地或生态补偿的争议，冲突的强度与速度都会迅速上升，但其冲突轴线依然是利益而非身份。
+至于“族群天然支持某党派”或“语言就是民族标识”这类推论，在昌江尤其站不住脚：这里同时存在儋州话、海南话、军话、村话、黎话五种语言对应两个登记民族，加上四层来源的汉族民系，如果把语言或“民系”直接当作政治立场代理变量，得到的结论必然是相互矛盾的。昌江的政治生态更接近一种“工业小镇＋山地村社＋渔港”三重叠加的、议题驱动的有限动员结构。
+【2020年七普人口补充】2020年11月1日零时，昌江黎族自治县常住人口为232124人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+本文数据口径说明：人口采用国家统计局第五次（2000年）与第六次（2010年）全国人口普查常住人口口径，昌江2000年219502人，2010年223839人；少数民族人口占比采用2010年第六次人口普查数据，为38.65%。本工作簿原“县市事实档案”表所载“少数民族约37%（黎为主）”系2000年前后估算，精度低于普查口径，本表予以更正为38.65%，旧表黎族内部构成（约62%等）亦为估计值，仅作参考。历史沿革部分（隋定川、唐昌化、1914年改昌江县、1939—1945年日军掠采石碌铁矿）来自地方志与公开党史资料，为定性叙述。语言分区（儋州话、海南话、军话、村话、黎话）依据《海南话》与《中国语言地图集》及海南省语言文字工作部门公布的方言点资料，各方言的乡镇级边界存在交叉，不宜作精确界线使用；需特别注意儋州话、军话、村话使用者按普查登记为汉族，仅黎话与黎族身份高度对应。产业部分（石碌铁矿、昌江核电、渔业、热带作物）依据公开统计年鉴、行业公开资料与地方政府工作报告，本文仅作结构性描述，未引用单一年份的确切产值数字。政治生态分析为基于公开选举、施政与政策资料的推断性框架，属条件性判断，不构成对任何政党支持率或族群投票倾向的实证测量，亦不预设族群与政党的对应关系。</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>4796</v>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="360" customHeight="1">
+      <c r="A19" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>乐东黎族自治县</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+乐东黎族自治县位于海南岛西南部，地形由中部、西部山地丘陵和东南沿海平原组成，黎族村寨、热带农业区、渔港和盐业空间并存。2002年统计资料以“乐东县”简称列入，行政性质是海南省的黎族自治县，下辖16个乡（镇）。因此，乐东与东方市、三亚市不能作为同一种行政单位比较：前者是民族自治县，后者分别是县级市和地级市。
+乐东的地方社会长期与五指山、南渡江和昌化江流域的黎族历史、山地农业和沿海渔业相联系。1987年自治县建制确立后，黎族人口和民族身份成为县域治理的重要社会背景，但这不意味着县内所有居民都采用同一种语言，也不意味着自治制度只处理黎族事务。现代公路、产业园区、旅游和盐业、渔业开发把原本相对分散的村落和市场连接起来，同时也改变了资源分配和人口流动方式。
+【人口与语言民系】
+2000年五普常住人口为447382人，年龄结构为0—14岁31.12%、15—64岁63.85%、65岁及以上5.03%。2002年户籍人口为461752人。2002年户籍人口中，汉族285997人，少数民族175755人，其中黎族171213人、苗族2852人、壮族1543人、回族20人、其他民族127人；少数民族占38.06%。这说明乐东是一个黎族人口高度集中、同时存在汉、苗等民族共同生活的县域，但“黎族自治县”首先是行政建制和民族区域自治制度名称，不等于全体居民都拥有同一种语言或政治立场。
+语言方面，黎话是黎族社区的重要语言，沿海和汉族聚居区常见海南话，苗族聚居地存在苗话；部分区域还可能因迁徙、婚姻和交通形成语言混合。方言分布不能仅由民族比例反推，法定民族统计也不能说明某一种语言覆盖多少人。语言在村社认同、家庭交往、市场交易和公共传播中的作用可能不同，研究时必须把语言、族群和行政类别分别处理。
+【产业与交通】
+2002年乐东国内生产总值197336万元，第一产业127931万元，第二产业11369万元，第三产业58036万元。三次产业数据说明，当时乐东经济具有明显的农业和资源型特征。农林牧渔业总产值按现价计为176950万元，其中农业101529万元、林业19990万元、牧业27792万元、渔业27639万元；农林牧渔业增加值为109711万元，农业增加值61961万元、林业12587万元、牧业11315万元、渔业17848万元。渔业、热带农业、林业、盐业和沿海资源开发共同构成县域经济基础。
+2002年规模以上工业总产值为8281万元，明显低于东方和三亚。公路货运量459万吨，客运量488万人，货物周转量29377万吨公里，客运周转量26972万人公里，运输主要依赖公路。乐东拥有沿海港湾和盐业、渔业条件，但年鉴中未列出的港口吞吐或旅游指标不能解释为零，只能说明本表没有提供相应统计。产业转型若要避免只依赖单一资源，需要同时改善公路、冷链、加工、旅游和县域公共服务。
+【族群和政治生态分析】
+乐东作为民族自治县，制度上有民族区域自治的合法性，但政治生态仍是多族群、多村落和多利益主体共同构成的基层治理环境。黎族人口占比较高，意味着一批公共政策需要通过村寨组织、学校、宗教文化活动、双语服务和基层协商才能落地；并不意味自治机构只代表黎族，也不意味着民族身份可以直接转换为某种党派偏好。
+在条件性情景中，如果盐业、渔业、农业园区或旅游项目扩张，可能出现土地、资源、生态补偿和收益分配问题；如果外部投资不足，则需要依靠本地农业加工、乡村旅游和交通改善来增强韧性。自治县制度的实际效果，应通过财政转移、公共服务供给、民族语言使用、社区参与和利益分配来观察，而不是仅凭“黎族自治县”名称推断社会一致性。乐东也不应套用台湾的族群分区、县市自治或族群政党结构。
+【2020年七普人口补充】2020年11月1日零时，乐东黎族自治县常住人口为464435人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+2000年人口为五普常住人口，2001—2002年为户籍人口及户籍民族。GDP和农业数据使用2003年鉴所载2002年表；农业现价与1990年不变价格不能混用。运输数据以公路为主，缺失港口、旅游或工业细项不补零。2002年经济表存在OCR识别差异，正文只保留已通过表头和分项和核对的数据。
+来源：乐东黎族自治县人民政府网 https://ledong.hainan.gov.cn/；海南省统计局《海南统计年鉴—2002》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2002/202306/P020250423537485183761.zip；海南省统计局《海南统计年鉴—2003》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2003/202306/P020230607424596076923.zip；海南省人民政府《海南人口民族》 https://www.hainan.gov.cn/hainan/rkmz/list1_tt.shtml；国家民委《黎族—历史沿革》 https://www.neac.gov.cn/seac/ztzl/lz/lsyg.shtml；国家统计局《第五次全国人口普查》 https://www.stats.gov.cn/sj/pcsj/rkpc/5rp/index1.htm。</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>1448</v>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="360" customHeight="1">
+      <c r="A20" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>陵水黎族自治县</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>【历史与空间】
+陵水黎族自治县位于海南岛东南部，南面濒临南海，北部和西北部与山区、黎族村落及热带作物区相连，东南沿海分布着港湾、渔村和旅游空间。陵水与三亚相邻，但2002年仍是海南省直辖的黎族自治县，不是三亚市的一个区。县域内部既有沿海平原、港口和旅游开发，也有山地、黎族社区和传统农业，政治生态不能只用“邻近三亚”概括。
+陵水县政府官方历史沿革资料记载：1950年4月29日陵水全境解放；1958年与崖县、保亭县合并为崖县；1961年恢复陵水县建置并隶海南黎族苗族自治州；1987年成立陵水黎族自治县；1988年海南建省后隶海南省。这个过程说明，2002年的陵水既具有县级地方社会历史，也处在海南省级行政和旅游开发加速的背景下。县域空间中的沿海社区、黎族山地村落和国营农林场，不能简单合并成同质化的“陵水社会”。
+【人口与语言民系】
+2000年五普显示，陵水常住人口303272人，0—14岁、15—64岁、65岁及以上人口分别占29.62%、64.22%和6.16%。2002年户籍人口为327658人。2002年户籍民族中，汉族144223人，少数民族183435人，其中黎族181944人、苗族693人、壮族571人、回族23人、其他民族204人；少数民族占55.98%，四地中比例最高。55.98%是户籍登记比例，不等于所有居民在日常政治参与中以黎族身份行事。
+语言结构具有明显的多样性。黎族社区使用黎话，沿海汉族和城镇社区常见海南话，苗族社区有苗话；陵水沿海还可见疍家话及水上渔业社群的语言痕迹。海南省官方资料将疍家话列为陵水、三亚、昌江、海口等沿海地区语言现象之一。疍家首先是一个历史形成的水上渔业和社区身份称谓，不是可以与汉族、黎族、苗族直接并列的法定民族分类；回辉话也主要对应三亚地方语言与社区，不应移植为陵水所有疍家居民的统一语言。
+【产业与交通】
+2002年陵水农林牧渔业总产值按现价计为130176万元，其中农业58551万元、林业10095万元、牧业9605万元、渔业51925万元。农林牧渔业增加值为84025万元，其中农业38274万元、林业7619万元、牧业5963万元、渔业32169万元。渔业在总产值和增加值中均较突出，说明海洋捕捞、养殖、沿海渔业和热带农业是县域经济的重要底盘。
+2002年规模以上工业总产值为12118万元。公路货运量145万吨，客运量581万人，货物周转量6911万吨公里，客运周转量26908万人公里；客运中公路547万人、水运34万人，客运周转量中公路26889万人公里、水运19万人公里。2002年定点饭店接待游客84323人次，其中境外游客242人。陵水当时已出现旅游服务业，但旅游规模明显小于三亚；它更适合被描述为农业、渔业、沿海社区和旅游开发并存的地方，而不是单纯旅游城市。2002年GDP总量表存在扫描冲突，本文不列该总数。
+【族群和政治生态分析】
+陵水是民族自治县，黎族人口占比较高，苗族、汉族和其他群体共同生活。自治制度为民族事务、双语服务和区域发展提供了制度空间，但县内不同村落、沿海渔业社区、汉族城镇和黎族山地区域的利益并不完全相同。语言、宗族、村社、职业和宗教文化可能交叉影响公共参与，但不能由这些因素推导党派支持或政治阵营。
+在条件性情景中，如果旅游、港口、旅游地产或海水养殖继续扩张，政策重点会转向海域使用、岸线开发、生态保护、村民就业和收益分配；如果外部投资放缓，渔业、热带农业和传统村寨网络可能成为社会稳定的缓冲。陵水的政治生态应被表述为多民族共同治理下的发展协商问题，而不是“黎族占多数所以由黎族决定一切”，更不能套用台湾的族群分区或自治制度经验。
+【2020年七普人口补充】2020年11月1日零时，陵水黎族自治县常住人口为372511人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+2000年人口为五普常住人口，2001—2002年为户籍人口和户籍民族；2002年经济数据来自2003年鉴。GDP总量因OCR冲突不写，农业、渔业、增加值、工业、运输和旅游只使用已核对数值。交通运输表中的水运数据不表示全部水运活动，疍家话和水上社群也不转写为法定民族人数。
+来源：陵水黎族自治县人民政府《历史沿革——2024年亮点》 https://lingshui.hainan.gov.cn/mlls_57671/lsrw/lsyg_57680/202507/t20250709_3894251.html；海南省统计局《海南统计年鉴—2002》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2002/202306/P020250423537485183761.zip；海南省统计局《海南统计年鉴—2003》 https://stats.hainan.gov.cn/tjj/tjsu/ndsj/2003/202306/P020230607424596076923.zip；海南省人民政府《海南人口民族》 https://www.hainan.gov.cn/hainan/rkmz/list1_tt.shtml；国家民委《黎族—历史沿革》 https://www.neac.gov.cn/seac/ztzl/lz/lsyg.shtml；国家统计局《第五次全国人口普查》 https://www.stats.gov.cn/sj/pcsj/rkpc/5rp/index1.htm。</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>1411</v>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="360" customHeight="1">
+      <c r="A21" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县：黎苗文化重镇与观光经济转型中的原乡—游客关系
+【历史与空间】
+保亭黎族苗族自治县位于海南岛南部，东南接三亚、北联陵水与乐东、西靠五指山，境内以低山丘陵、河谷盆地与山间台地相间为基本地貌，七仙岭等山峰构成醒目的地标性山体。全县面积约一千五百平方公里上下，在五个自治县中面积居中，山地与缓坡台地比例高，具备热带经济作物种植的适宜条件，且在空间上距三亚这一全岛最大旅游客源地和空港门户最近，这是保亭全部县域经济逻辑的地理起点。
+历史沿革上，保亭一带在明清两代分属崖州、陵水等县管辖的黎峒地区，明代设土官制度管辖黎峒，清代延续土官与流官并置的格局，黎族村寨的世袭首领制度在海南南部保存相对完整，至清末民初仍有土官后裔在地方上具有影响力。保亭设县始于1935年，其划县范围大体依循传统黎峒与汉人聚落的分野，将原属崖县、陵水等地的黎峒地区整合为一个行政单位，县治初设于保亭（今县城一带），县城因位于山间河谷、周边村寨密集，逐渐成为黎苗山区的物资集散与行政中心。1962年国务院对全岛区划作出重大调整，将琼中、陵水、乐东等县的边远山区划归保亭管辖，使保亭一度成为海南中部与南部山区面积最大的行政单位，行政地位显著上升；此后随着1970年代以后相关县的恢复设置，保亭的辖区范围逐步回缩至当前的规模。这是一个“因民族区域自治需要而设立、其后因区划调整而扩张又回缩”的县份，其沿革本身即反映了海南山区县级建制与民族政策之间的紧密关联。
+交通方面，保亭境内无铁路，主要依靠公路与海南环岛高速公路的互通口连接。县城至三亚的公路距离较短，是全岛少数可实现当日往返三亚的山区县份，保亭因此长期承担三亚与南部山区的劳动力居住地、旅游集散地与农产品供应地三重角色；相对便利的通勤条件既造就了保亭的旅游接待业基础，也使大量保亭居民长期在三亚的酒店、餐饮、建筑、零售与家政行业就业，形成“人在三亚、家在保亭”的跨境通勤型生计结构。
+【人口与语言民系】
+人口数据方面，按第五次全国人口普查（2000年），保亭黎族苗族自治县常住人口为139506人；按2010年第六次全国人口普查，保亭黎族苗族自治县常住人口为146684人。十年增加约7178人，增幅约5.1%，略高于白沙、昌江、五指山等中部与西部山区县，但仍显著低于海南全省人口增长水平，在五个自治县中属人口增长最慢的县份之一。人口低增长的直接原因是本地产业提供的长期性岗位有限，且邻近的三亚市对劳动力的吸纳能力远大于保亭本县，形成持续的人口外流。
+2010年第六次全国人口普查数据显示，保亭黎族苗族自治县少数民族人口占比达到70%上下，五个自治县中密度最高，其中黎族为主体、苗族占据可观比例，两者构成本县社会的主体。需要指出的数据纠正是：本工作簿原“县市事实档案”表所载保亭“少数民族约64%（黎约59%、苗约4—5%）”系2000年前后估算值，精度明显低于普查口径，且与2010年普查结果存在较大偏差，本次核查予以纠正，以2010年普查的少数民族占比为准（保亭五个自治县中最高，接近七成）。
+语言与民系方面，保亭的语言结构与保亭的民族构成高度吻合。黎话是保亭最重要的方言，内部可分杞、哈等方言群，不同方言群之间的差异足以导致互相无法沟通；苗话在保亭的使用规模显著大于白沙、昌江，在多个苗族聚居的乡镇和村寨中作为日常交际语言；海南话在县城建成区、乡镇政府所在地、公路干线和学校周边通行；普通话在县城与景区服务行业、机关单位、年轻一代中通行率较高。民系层面，保亭是海南唯一黎苗两大民族合计占绝对多数、且苗族人口规模相对较大的县份，黎族村寨与苗族村寨在空间上或交错、或分区聚居，两族之间长期通婚，共居关系紧密；但两族之间并不存在统一的社会组织，黎族村寨多以血缘家族与头人体系为核心，苗族村寨则更多依托寨老、宗族与节庆组织，两套权威网络各有其运行逻辑。汉族人口在保亭县城、农场场部与交通沿线聚居，多为农垦职工后裔及外省迁入者后代。语言、族群与政治态度三者之间并不存在稳定的对应关系：同为黎族，不同方言群、不同村寨的政治取向可以完全不同；同为汉族，县城职工后代与场部农户的政治关注点也各异。任何以语言或民族为变量直接推断政治立场的做法，在保亭都会产生错误结论。
+【产业与交通】
+保亭的产业转型轨迹是海南县市中最为清晰的观光型转型案例之一。1980年代以前，保亭的经济以热带农业和林业为主，橡胶、槟榔、椰子等热带经济作物是主要收入来源，黎锦等传统手工艺为家庭副业。进入1990年代后，依托七仙岭的温泉与山岳景观、黎苗文化的独特性以及邻近三亚的客源优势，保亭逐步发展出以七仙岭温泉度假区为代表的山地康养与观光旅游产业；2000年代以后，以槟榔谷黎苗文化生态旅游区、呀诺达雨林景区等为代表的大型文化主题景区相继建成，保亭的旅游产业从单一温泉度假转向“文化展示＋生态观光＋休闲度假”的复合形态，景区门票、观光车、索道、演艺、餐饮、住宿及配套商业构成县域旅游收入的主体。
+转型带来的最显著变化是产业结构与人口结构的同步重组。一方面，传统农业在县域经济中的比重持续下降，但并未消失：槟榔、椰子、热带水果、南药（益智等）在缓坡与台地上仍有种植，橡胶在部分乡镇保留存量，主要由中老年人口经营，年轻人大多外出务工或进入景区服务业。另一方面，景区与配套服务业的从业人员结构发生根本变化：景区核心岗位员工以汉族为主，多来自外省或岛内其他县市；本地黎苗村民在景区中的角色更多是集体土地与资源股份的持有者、表演与民俗服务者、景区周边的小商户与民宿经营者，而非直接雇员。这一分工结构是理解保亭政治生态的关键：外来从业者与本地资源持有者之间的利益关系，在景区扩张的每一个阶段都会重新协商一次。
+交通方面，保亭的优势在于“近”：县城与高速公路互通口的距离短，至三亚的公路通勤便利，使得保亭既有条件承接三亚的溢出客流与劳动力市场，又具备承接三亚外溢游客的地理条件；缺点在于内部交通层次不足，山区公路等级偏低，台风与暴雨季常发生塌方与漫水，景区与偏远村寨之间的可达性不均衡。保亭还承担着服务三亚城市扩张与产业外溢的角色：部分三亚的房地产开发与旅游投资延伸至保亭境内，使土地价值、租金与生活成本在县城及部分乡镇显著上升，本地居民的生活空间受到挤压。就业方面，大量保亭人在三亚就业，形成了一种特殊的政治后果：他们的户籍与选举关系在保亭，而日常生计与生活成本在三亚，这种“经济生活在外、生活登记在内”的结构，使保亭的常住人口统计与实际社会现实之间产生偏差，也使本地公共议题常常处于“本地需求与外溢压力”的错位之中。
+【族群和政治生态分析】
+保亭是海南五个自治县中少数民族占比最高、黎苗两大民族合计占绝对多数的县份，因此有充分理由在此展开政治生态分析——但分析的焦点必须落在结构上，而非族群偏好上。
+第一，黎苗两大民族在保亭构成一个共同的“原乡社会”，但不是统一的政治主体。黎族与苗族虽然共居密度高、通婚频繁、共同节庆（如三月三）创造了跨族的公共文化空间，但两族的组织形态、权威来源与关注议题仍各成系统：黎族村寨的诉求多集中于土地、林地与集体收益分配；苗族村寨的诉求多集中于传统生计空间的存续与文化传承的现实条件。跨族共同利益确实存在（尤其是与土地、林权、生态补偿相关），但这种共同性是议题性的、条件性的，而非身份性的。把黎族与苗族合并为一个“少数民族投票板块”来预测选举结果，在保亭缺乏经验证据支撑。
+第二，语言分层在保亭被政治性地放大为一种象征资源。黎话、苗话在公共场合的仪式性使用（例如节庆发言、景区民族文化展示、民族政策宣传）具有强烈的身份确认功能，这种象征性有时会被利用来强调“本民族的独特性”与“政策的针对性”。但象征语言与投票行为之间缺乏稳定链条：日常政治决策中，居民更多依据具体的利益关联、亲族网络与对具体政策的效用判断，而非依据语言身份。
+第三，保亭政治生态的真正核心是“原乡—观光”关系。这是保亭区别于白沙、五指山、琼中的关键结构性特征。1980年代以来的三十年间，保亭经历了一次深度的社会再组织：原本以村寨土地和林权为根基的黎苗社会，被逐步嵌入由外来资本主导、以游客体验为目标的旅游产业之中。这一过程带来的政治议题集中在四个方向：（1）土地与集体收益的分配方式——景区门票收入、土地作价入股、集体分红机制如何设计、村民是否真正受益；（2）生态搬迁与生活方式变迁——为保护景观与水源，部分村寨被纳入搬迁或限制范围，原有生计（狩猎、采集、山地种植、黎锦）如何延续；（3）外来人口与地方空间的张力——外来经营者、置业者与季节性务工人员在县城和景区的集聚，抬高了生活成本，改变了村庄的人口结构；（4）文化展示化的边界——黎苗文化被转为舞台化、商品化的表演后，节庆的时间表、服饰的使用、仪式的场合与传统的内容之间出现张力，部分村民认为传统被消费而未被尊重。这些议题都不以“族群对党派”的形式出现，而是以“原乡社会能否在旅游经济中保有主体性”的形式出现，其具体立场在村与村之间、甚至同一村寨内部都存在分裂。
+第四，交通与就业的地理现实使保亭居民具有高度的“外出经验”。大量保亭人在三亚从事酒店、餐饮、建筑、家政、零售等工作，他们对三亚的产业波动、房地产政策、旅游景气度有直接体感，却要在保亭行使选举权与表达权。这种“经济在外、身份在内”的错位，产生了一种特殊的政治态度特征：他们倾向于支持能够改善本县就业机会与公共服务供给、同时又不必与三亚既得利益发生正面冲突的政策；他们对外来投资既欢迎（带来就业与税收）又警惕（抬高成本、挤占空间），态度是务实与条件性的，而非原则性的。
+第五，行政沿革与区划调整的余波仍存于保亭的政治记忆中。1962年区划调整大幅扩张保亭，1970年代后又逐步回缩，这一进一出在保亭的历史叙述中成为地方身份的一部分，也影响保亭对自身行政地位与资源分配位置的理解。保亭长期作为海南黎族苗族自治州首府所在地之一，其在民族事务上的政策代表性使其在争取专项资金与项目时被赋予特别的期待，一旦实际获得的资源与期待不匹配，“被代表”的不满就会沉淀为对行政系统的普遍性不信任。
+第六，保亭县域内部的中间地带较厚。县城居民、农场职工后代、外来商户、村寨干部、返乡创业者等多个群体，虽然在旅游收益分配与土地问题上的立场有差异，但都不构成稳定的党派化力量。这种“多元但未极化”的结构，使得保亭的政治动态在常态下呈现低烈度、议题型特征，只在土地分配、生态搬迁、景区扩张等具体节点上出现短期的高强度博弈。
+综合而言，保亭的政治生态是一个“原乡社会嵌入旅游产业”后的条件性结构：黎苗身份提供象征资源与文化正当性，景区与土地收益分配才是真实的分歧轴线；语言不是民族，民族不是政治立场；外出务工经验与外来资本压力共同塑造了居民的务实态度；而在所有议题中，交通、就业与公共服务的改善，始终是少数能跨越族群与阶层边界的共鸣点。
+【2020年七普人口补充】2020年11月1日零时，保亭黎族苗族自治县常住人口为156108人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+本文数据口径说明：人口采用国家统计局第五次（2000年）与第六次（2010年）全国人口普查常住人口口径，保亭2000年为139506人，2010年为146684人。少数民族人口占比采用2010年第六次全国人口普查数据，为70%上下（五个自治县中最高，黎族为主体、苗族占可观比例）。数据纠正是：原“县市事实档案”表所载保亭“少数民族约64%（黎约59%、苗约4—5%）”系2000年前后估算值，精度低于普查口径，且与2010年普查数据存在显著偏差，本次核查予以纠正，旧表数据不再作为引用依据；旧表所载“黎约15%、苗约0.8%”的全岛构成数据亦为估计值，与县级普查占比不可混用。历史沿革（1935年置县、土官制度、1962年区划调整、后续回缩）来自地方志与公开资料，为定性叙述，不含精确计量。语言与民系分区（黎话杞／哈方言群、苗话、海南话、城镇普通话）依据《海南话》《中国语言地图集》及海南省语言文字工作部门公布的方言点资料，方言边界存在交叉，不宜作精确界线使用；苗族内部支系与村寨分布数据不足，本文未作细分。产业部分（七仙岭温泉、槟榔谷、呀诺达、热带农业与南药、外出务工）依据公开统计年鉴、行业公开资料与地方政府工作报告，仅作结构性描述，未引用单一年份的确切数字。政治生态分析为基于公开选举、施政与政策资料的推断性框架，属条件性判断，不构成对任何政党支持率或族群投票倾向的实证测量，不预设族群、语言与政党之间的任何对应关系。</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>4493</v>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="360" customHeight="1">
+      <c r="A22" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县：海南岛分水岭上的黎苗腹地与绿橙山货经济
+【历史与空间】
+琼中黎族苗族自治县位于海南岛中部，恰好坐落在海南岛重要的地理分水岭上，境内山脉走向使水流南北分派，故琼中自明清以来即为黎族、苗族聚居的核心腹地之一。全县以山地、高原和河谷盆地相间为基本地貌，南部为山地与峡谷密布区，中部为山间盆地（营根、湾岭等），北部过渡至琼北丘陵台地。全县面积在一千五百平方公里上下，在五个自治县中面积居中，山地比例高，平地分散而零碎，耕地主要集中于河谷盆地的坡脚地带。松涛水库及其水系位于县域西北部，是全岛最大的水库与重要水利枢纽，其库区与集水区覆盖琼中大部及周边区域，构成了琼中县域地理与经济结构的决定性要素。
+历史沿革方面，琼中一带在明代属崖州、琼山等县辖下的黎峒地区，土官制度长期施行，明清两代朝廷多次推行改土归流但收效有限，黎族村寨在此保留较高的自治程度，寨落的血缘家族结构与头人体系延续到二十世纪。设县始于1952年，即在中华人民共和国成立后的区划调整中，从琼山、定安、乐会、白沙等县析出组建琼中县，县治设在营根，其划县依据与保亭类似，即依黎苗聚居与传统峒界的整体性，将原本分属不同县的山区腹地整合为一个行政单位。1953年海南黎族苗族自治区成立以及1987年海南黎族苗族自治州成立，琼中均为其核心辖区，州府曾一度设在通什。黎母山是琼中境内最具象征性的地名，位于县域南部，是黎族广泛流传的始祖传说与族群记忆的圣地，其文化意义在黎族社会内部远大于其地理与经济意义。
+交通方面，琼中境内无铁路，公路是唯一对外通道，环岛高速公路从县域边缘通过并设有互通点，但县域内部公路以山区国道、省道和县乡道为主，等级偏低，通行条件在雨季与台风季波动明显。琼中作为海南岛中部的地理中心与山区门户，长期承担着对白沙、保亭、屯昌、五指山等周边地区的部分客货转运与农资供应功能，这一“中部集散地”角色使县城营根在行政服务与商业上具有一定地位，但也使琼中的经济在很大程度上受周边县市产业波动与交通通道改造的影响，而非仅由本地产业决定。
+【人口与语言民系】
+人口数据方面，按第五次全国人口普查（2000年），琼中黎族苗族自治县常住人口为171598人；按2010年第六次全国人口普查，琼中黎族苗族自治县常住人口为174076人。十年增加仅约2478人，增幅约1.4%，是海南五个自治县中人口增长最慢的县份之一，在全岛人口普遍快速扩张的背景下属于典型的滞留型、净外流型县域。这一数据与保亭（+5.1%）、五指山（+3.2%）、白沙（+2.1%）、昌江（+2.0%）共同构成海南中部与西部山区“人口增长停滞带”的清晰轮廓，揭示了海南山区县市在两轮普查之间面临的共同人口困境：本地自然增长被外出务工、外出就学与婚姻迁移大量抵消，而本地产业无法提供足够的回流吸纳。
+2010年第六次全国人口普查数据显示，琼中黎族苗族自治县少数民族人口占比为66.44%，其中黎族为主体、苗族占据可观比例，另有少量其他民族成分。数据纠正是：原“县市事实档案”表所载琼中“少数民族约52%（黎约45%、苗约6—7%）”系2000年前后估算值，本次核查以2010年普查数据66.44%为准，旧表数据予以纠正，黎族内部构成数据为估计值，仅作参考。
+语言与民系方面，琼中是海南语言多样性较为突出的县份，其方言构成与人口构成呈现不同的层次。黎话是琼中最重要的方言，在南部山区与中部村寨广泛通行，内部方言差异显著。苗话在县域内多个苗族聚居点使用，但在整体语言格局中不占主导，传承也因人口分散而较为脆弱。海南话主要在县城营根、湾岭等城镇建成区、各乡镇政府所在地及公路干线沿线聚落通行。客家话局部见于黎母山—中平一带；其语言使用者按法定民族登记与语言身份并非一回事，其历史来源与明末清初及近现代的移民垦殖活动相关。
+民系层面，琼中的汉族人口来源多元：县城与交通干线的汉族多为农垦职工后裔与外省迁入者后代；黎母山—中平一带的客家话群体则是另一支移民谱系；黎族与苗族村寨则延续着各自的组织结构。琼中黎族村寨延续以血缘家族和头人为核心的组织形态，祭祀、山林、水源与婚丧互助在村寨内完成，苗族村寨依托寨老与宗族组织。琼中独特的地理特征——海南岛分水岭——使黎族文化在此呈现出更强的“腹地性”与象征性，黎母山作为始祖传说圣地，使琼中在黎族文化地理中占据特殊地位；这种象征地位强化了琼中的文化主体意识，但并不直接转化为统一的政治力量。
+【产业与交通】
+琼中的产业结构以山地农业、生态林业、旅游与水利相关产业为主。农业方面，琼中绿橙是海南最具品牌影响力的热带水果之一，种植集中于县域中部的河谷盆地与缓坡区域，果实以早熟、甜度高、皮薄著称，在国内外市场均有一定知名度，绿橙的采收季节集中在春季，是琼中果农全年最主要的现金收入来源，采收期需要大量季节性雇工，本地及周边乡村的劳动力普遍在绿橙采收季获得短期务工机会，是琼中乡村经济中少有的劳动密集型环节。除绿橙外，琼中还盛产热带水果（如香蕉、芒果、菠萝蜜）、南药（槟榔、益智）、橡胶以及热带经济林，绿橙产业的成功带动了相关仓储、分选、包装、运输与批发环节，但产业链仍主要停留在初级加工阶段，附加值与农民在终端收益中的分成比例有限。
+林业与生态方面，琼中地处海南岛中部山地，是海南重要热带雨林与水源涵养区域，黎母山与吊罗山一带被划为森林生态重点保护区域，森林覆盖率高，采伐受到严格限制。松涛水库的库区与集水区涉及琼中大部及周边县份，其水资源功能、库区移民遗留问题、生态保护责任与地方发展之间的平衡，构成琼中最重要的长期议题之一：库区保护限制了林地、坡地的农业与开发空间，而生态保护的收益（下游供水、水源涵养）主要外溢到全岛甚至岛外，本县难以独享其价值，这构成了“生态保护成本本地承担、生态受益外部共享”的结构性困境，是琼中在生态补偿诉求上持续发声的根本原因。
+旅游方面，琼中的旅游以黎母山、吊罗山一带山地生态观光、黎族苗族文化体验、山地民宿与漂流探险等为主，客源以海口、三亚和本岛中西部为主，接待规模中等偏小，主要依托海口—琼中、三亚—琼中两条公路干线串联，游客停留时间短、人均消费有限。交通是琼中产业发展的核心瓶颈：县城营根虽为中部集散地，但无铁路、无港口，主要公路在雨季与台风季通行不稳定，山区公路等级低，农产品外运半径受限、物流成本偏高。琼中在海南岛中部地理中心的地位使其在理论上具备“中部枢纽”的区位优势，但受地形与交通投资的滞后，其实际枢纽功能远未充分释放，这一“区位优势与实际地位落差”是琼中地方认同与公共讨论中反复出现的主题。
+【族群和政治生态分析】
+琼中是海南中部山区中黎族文化象征性最强、人口结构相对稳定、但经济机会最为稀缺的自治县之一，其政治生态呈现出“文化腹地—生态约束—外流压力”三力叠加的特征。
+第一，黎族在琼中的象征地位极高。黎母山作为黎族始祖传说圣地，赋予琼中在黎族文化地理中不可替代的意义，琼中在各类黎族文化活动、民族政策宣传与对外文化交往中都扮演着核心角色。这种象征地位带来了两方面效应：一是文化自信与主体意识较强，黎族群众对自身文化的价值有明确认知，不轻易被外部叙事覆盖；二是象征地位与现实条件之间存在落差——作为“黎族之家”，琼中的产业发展、基础设施与公共服务水平在海南各县市中并不领先，这种“名分高、实惠弱”的落差成为县域内政治不满的重要来源。
+第二，黎族与苗族在琼中共居密度高，但同样不构成统一的政治行动主体。黎族内部按村寨、宗族、方言分化，苗族村寨规模小、点状分布，两族之间有共同的节庆与文化空间，但各自的社会组织与关注议题仍各成系统。将琼中理解为“黎苗蓝盘”或“原乡政治板块”，在方法上是把象征资本误读为组织力量。苗族人口在琼中约占总人口的6%上下，绝对规模有限，缺乏独立组织化的政治与社会基础，更准确的描述是“黎苗共居的多民族山区社会”，而非“以民族为轴心的政治阵营”。
+第三，生态保护是琼中最核心的政治议题。松涛水库的库区与集水区、黎母山与吊罗山的森林生态重点保护区域，构成了琼中大部分国土的用途约束。这种约束带来三重政治后果：（1）本地发展权受限——林地、坡地无法转为农业或建设用地，农作物种植与建设空间受压缩；（2）生态保护成本本地承担而收益外溢——下游城市、农场与工业用水长期受益于琼中的水源涵养，而琼中自身难以将这一贡献转化为经济收益；（3）生态补偿机制不足引发的普遍不满——居民要求提高生态补偿标准、扩大补偿范围、完善“保护换取补偿”的制度安排，这是琼中各类公共讨论中最具共识性的议题之一。由于这一议题涉及全岛上下游各方的利益博弈，其解决路径高度依赖省级与国家层面的政策，而非县域内部的政治博弈，这也是琼中在政治议题上高度依赖外部政策资源的原因。
+第四，人口持续外流是最深的结构性约束。2000至2010年琼中人口仅增长1.4%，是五个自治县中最慢的，说明本地青年人口大量外流至沿海县市与岛外。人口外流的后果不仅是劳动力减少，更在于政治参与的稀释：外出务工者在选举中实际参与率低，其利益主要由家庭与村寨代理人代为表达；同时，外流导致村寨人口老化、留守群体集中，使基层公共议题的焦点集中在养老、教育、医疗与交通，而非发展与投资。琼中的政治生态因此带有强烈的“候鸟式参与”特征——重大议题的最终决策权更多掌握在外出人口手中，而村寨日常运行则由留守的中老年人与村寨权威维持。
+第五，移民群体叠加增加了社会构成的复杂性。琼中的汉族居民不仅来自岛内不同地区，还包含黎母山—中平一带的客家话移民群体，这一支语言与民系的存在使琼中的社会层次比保亭、五指山更为多元。不同的移民来源在产业选择（种植、养殖、务工、经商）、组织方式（宗族、协会、合作社）与利益关注上存在差异，构成了县域内潜在的社会分层。这一分层与民族身份的交叉，使得任何基于“民族”的政治归类都更加不可靠。
+第六，产业机会的稀缺使务实主义成为主导态度。琼中的绿橙等产业虽有一定品牌效应，但受制于产业链短、物流成本高、加工能力弱、市场波动大等问题，农民收入增长有限。在收入增长受限时，民众的政治关注点集中于具体的、可感知的民生事项——道路修建、饮水安全、学校与医疗、危房改造、低保与救助、移民与搬迁补偿——而非任何宏大的意识形态或族群叙事。琼中的政治动态因此在常态下呈现“低动员、高共识民生导向”的特征，只在生态补偿、土地征用、水库移民遗留等具体节点上出现阶段性张力。
+第七，需要严格避免的两类推论：第一，“黎族天然支持某党派”或“苗族因族群身份倾向某方”——在琼中的实际政治中，黎族与苗族内部的政治取向随村寨、宗族、议题与代际而变化，不存在可观察的以族群身份为轴心的稳定支持结构。第二，“语言等于民族”——黎话、苗话使用者与黎族、苗族身份高度对应，但客家话、海南话使用者均为汉族登记，且各语言片之间的通婚与混居已持续数代，方言分布不能直接作为政治立场的代理变量。
+综合而言，琼中的政治生态可以概括为：黎苗文化提供了强烈的象征认同与主体意识，但缺乏组织化的族群政治力量；生态保护约束是最具共识性的议题，但其解决依赖外部政策资源；持续的人口外流削弱了参与基础并使基层权力结构偏向留守者与村寨权威；稀疏的产业机会使政治议程高度务实化，围绕具体的民生与生态补偿事项展开。相较于台湾任何单一族群的政治结构，琼中的族群因素更像是文化景观与身份象征，而非可动员的政治资源；其县域政治的真正主轴，是生态约束与民生供给之间的平衡，而这恰恰是海南中部山区各县共同的、也最难化解的结构性难题。
+【2020年七普人口补充】2020年11月1日零时，琼中黎族苗族自治县常住人口为179586人。该值取自红黑人口库第三方人口汇编；页面所列2020乡镇分项合计与县级总数一致，具体链接见“县市资料来源”。正式引用仍以政府七普公报为最终依据。
+【资料口径】
+本文数据口径说明：人口采用国家统计局第五次（2000年）与第六次（2010年）全国人口普查常住人口口径，琼中2000年为171598人，2010年为174076人，十年增幅约1.4%，为五个自治县中最低。少数民族人口占比采用2010年第六次全国人口普查数据，为66.44%。数据纠正是：原“县市事实档案”表所载琼中“少数民族约52%（黎约45%、苗约6—7%）”系2000年前后估算值，本次核查以2010年普查数据66.44%为准，旧表数据予以纠正，旧表黎族内部构成数据为估计值，仅作参考，不作为引用依据。历史沿革（1952年析置琼中县、县治营根、黎母山始祖传说地、黎族苗族自治州成立等）来自地方志与公开资料，属定性叙述，不含精确计量。语言与民系分区（黎话、苗话、海南话、黎母山—中平一带客家话）依据《海南话》《中国语言地图集》及海南省语言文字工作部门公布的方言点资料，方言边界存在交叉，客家话在琼中的具体分布村委范围依据公开方言调查资料，属参考性描述，不宜作精确界线使用；需注意海南话与客家话使用者均登记为汉族。产业部分（绿橙、热带水果与南药、林业生态保护、松涛水库与生态补偿、旅游）依据公开统计年鉴、林业与水利部门公开资料、行业公开资料与地方政府工作报告，仅作结构性描述，未引用单一年份的确切产值或面积数字。政治生态分析为基于公开选举、施政、生态政策与规划资料的推断性框架，属条件性判断，不构成对任何政党支持率或族群投票倾向的实证测量，不预设族群、语言与政党之间的任何对应关系。</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>4734</v>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>查看来源</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E22"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId18"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C第 &amp;P 页 / 共 &amp;N 页&amp;R海南县市扩展简析</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>县市扩展简析官方资料来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>优先列示市县政府、国家统计局与海南省统计局资料；红黑人口库仅作七普县市分项补充来源。点击标题可打开网页；部分政府旧站页面可能改版或仅支持检索，通用入口仍保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>县市</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>历史/市情官方来源</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>人口普查官方来源</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>产业/文化补充来源</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>口径与纠错说明</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>2020七普补充来源（第三方）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>海口市</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>海口市人民政府（市情与历史入口）</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>海口市统计局《第七次全国人口普查公报》</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>2000年含琼山；2010、2020为现行海口市范围，人口增长主要反映城市吸纳与区划口径变化。</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="n"/>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>三亚市</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>三亚市人民政府《市情》</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>2000五普、2002户籍与2002经济数据分别标注，不混作同一时点。</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="n"/>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>五指山市</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>五指山市人民政府（原通什市历史、人口资料入口）</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>五指山市《2010年第六次全国人口普查主要数据公报》</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>2000年普查时名为通什市；2010六普可核对黎、苗人口。</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="n"/>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>琼海市</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>琼海市人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>国家统计局《海南省第六次全国人口普查主要数据》</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>2010、2020采用六普、七普常住人口；博鳌、潭门与侨乡网络分别分析。</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="n"/>
+    </row>
+    <row r="9" ht="72" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>儋州市</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>儋州市人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>2020人口含洋浦；儋州话不是海南话，客家仅在若干乡镇局部集中。</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="n"/>
+    </row>
+    <row r="10" ht="72" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>文昌市</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>文昌市人民政府英文市况（含历史沿革）</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>文昌市人民政府《2022年政府工作报告》</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>保留2000五普基线；后续普查数据须以市统计部门最终表为准，不虚构缺项。已补入2020年七普常住人口560894人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：文昌市七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>万宁市</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>万宁市人民政府《走进万宁》</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>万宁市统计局《2024年前三季度经济运行简况》</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>2010、2020采用六普、七普；兴隆侨乡、黎族山区与滨海旅游不混为一体。</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="n"/>
+    </row>
+    <row r="12" ht="72" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>东方市</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>东方市人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>2002户籍民族数据用于当时结构；村话、军话是语言群体，不等于法定民族。已补入2020年七普常住人口444458人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：东方市七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>定安县</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>定安县人民政府《历史沿革》</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>定安县人民政府《城镇史》</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>不以客家县解释定安；文教传统按琼北科举、宗族和知识网络理解。</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="n"/>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>屯昌县</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>屯昌县人民政府（市情与资源入口）</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>屯昌县人民政府《矿产资源》</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>1949后新设县，早期村落社会早于现行县界；农垦人口不等于1949后外省政治群体。</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="n"/>
+    </row>
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>澄迈县人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>澄迈县《第七次全国人口普查公报》</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>客家仅为加乐、文儒等局部聚居；临高话分类需保持学术谨慎。</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="n"/>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>临高县</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>临高县人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>海南省人民政府《海南人口民族》</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>临高话来源与分类仍有争议，本文不作单一语系定论；和舍客家不构成全县主体。</t>
+        </is>
+      </c>
+      <c r="F16" s="34" t="n"/>
+    </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>白沙黎族自治县</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>白沙黎族自治县人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>国家统计局《海南省第六次全国人口普查主要数据》</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>2010六普少数民族67.43%，替代旧表约65%的估算。已补入2020年七普常住人口164699人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：白沙黎族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县《第七次全国人口普查公报》</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>2010六普少数民族38.65%；工矿、黎乡、渔农按职业与空间结构分析。已补入2020年七普常住人口232124人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：昌江黎族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>乐东黎族自治县</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>乐东黎族自治县人民政府（市情与历史沿革入口）</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>2002户籍民族38.06%；沿海海南话与内陆黎族社区不套用台湾南北族群结构。已补入2020年七普常住人口464435人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：乐东黎族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>陵水黎族自治县</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>陵水黎族自治县人民政府《历史沿革》</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>2002户籍少数民族55.98%；疍家是渔业社群/生活称谓，不直接等同法定民族。已补入2020年七普常住人口372511人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：陵水黎族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县人民政府（市情与统计入口）</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县《第七次全国人口普查公报》</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>旧表64%为粗略估算；2010分民族资料约69%，辅助数据注明需以普查年鉴最终表复核。已补入2020年七普常住人口156108人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：保亭黎族苗族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县人民政府（市情与统计入口）</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县第六次人口普查主要数据公报</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>2010六普少数民族66.44%，替代旧表约52%的估算。已补入2020年七普常住人口179586人；红黑人口库为第三方汇编，分项合计已作一致性校验，正式引用以政府公报为准。</t>
+        </is>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <t>红黑人口库：琼中黎族苗族自治县七普人口（第三方补充）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>全省通用人口、民族与语言口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>全省通用</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>国家统计局《海南省第五次全国人口普查主要数据》</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33" t="n"/>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>普查人口须按年份与常住/户籍口径分别解释；语言分类不等同法定民族。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>全省通用</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>国家统计局《海南省第六次全国人口普查主要数据》</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="29" t="inlineStr">
+        <is>
+          <t>普查人口须按年份与常住/户籍口径分别解释；语言分类不等同法定民族。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>全省通用</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南省第七次全国人口普查公报（第二号）》</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>普查人口须按年份与常住/户籍口径分别解释；语言分类不等同法定民族。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>全省通用</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>海南省人民政府《海南人口民族》</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="29" t="inlineStr">
+        <is>
+          <t>普查人口须按年份与常住/户籍口径分别解释；语言分类不等同法定民族。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>全省通用</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>海南省统计局《海南统计年鉴—2002》</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33" t="n"/>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>普查人口须按年份与常住/户籍口径分别解释；语言分类不等同法定民族。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F22"/>
+  <mergeCells count="8">
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B25:D25"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId67"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -563,9 +2394,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>① 1950 年海南岛战役未发生，ROC 海南特别行政区（1949 年成立，首府海口，1949 年辖 1 市 16 县：海口、琼山、澄迈、定安、文昌、琼东、乐会、临高、儋县、崖县、万宁、陵水、感恩、昌江、乐东、保亭、白沙；1950 年 1 月曾设榆林行署）延续治理并与台湾并行，1988 年后随台湾一同完成解严与民主化，采县市长、立委、总统直选。
-② 岛内族群格局大致沿袭现实：汉（海南话/儋州话/临高话/客家话/军话/迈话/疍家话等）、黎、苗、回等世居民族比例不变；1949–1950 年间国府军公教与大陆外省族裔大量迁入海口、榆林等要地（类比台湾眷村），形成外省族裔蓝盘。
-③ 分析单元沿用 2002 年乡镇界线并对回 ROC 时期行政归属；光只评估蓝营/绿营两党结构，民众党等第三势力并入中间选民。</t>
+          <t>以2000年五普为可比基线；2010、2020仅在标注年份和常住/户籍口径后作后续参照，2002年鉴用于补充产业、交通、教育及社团史。行政区划、农场职工、跨海移民与城市化已改变人口结构，不把2000年比例机械外推至今。</t>
         </is>
       </c>
     </row>
@@ -583,7 +2412,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1">
+    <row r="6" ht="430" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>族群/社会类比对表</t>
@@ -591,27 +2420,61 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>海南群体 → 台湾参照（推论蓝绿倾向）：
-海南话（闽南语文脉，几百万人，东北部/沿海）→ 台湾闽南族群（泛绿约 6:4）
-客家（约 40 万人，儋州那大—南丰—兰洋—和庆、临高和舍、澄迈、琼中松涛带）→ 桃竹苗「北客」（泛蓝约 7:3，深蓝底色）
-军话居民（约 10 万人，东方、昌江、儋州、三亚沿海，明代军户后裔操北方方言）→ 外省眷村族群（压倒性泛蓝）
-临高话民系（约 50 万人，壮傣语支）→ 福佬化/独特民系，农渔业阶级（中间偏绿）
-黎族（约 160 万人，中部南部山地）→ 台湾原住民（传统泛蓝 3:1，青年转绿）
-苗族（约 5 万，五指山—保亭—琼中一带）→ 山地原住民（泛蓝偏深）
-回族（三亚回辉/回新约 6000 人）→ 少數族群（中间，择人而投）
-疍家/水上人（三亚、陵水、潭门渔港）→ 高雄港区/南方澳渔民（泛绿）
-归侨（兴隆等华侨农场，印尼/马来/越南侨眷）→ 侨生/外省二代（蓝底）
-军公教与公职体系（首府海口及各县治）→ 台湾军公教（泛蓝）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>【海南人口文化结构与条件性情景推演】
+① 海南话使用者（闽语海南片，沿海及部分内陆为最大汉语方言群）→ 仅作语言文化参照，不直接等同台湾闽南族群。
+　修正：海南话已独立成系，海南汉族并无台湾「本省/外省」二元断痕；其投票随农渔/都会职业与世代变化，不作台湾式 6:4 绿盘预设。
+② 客家话使用者（局部聚居，无统一近期全岛统计；儋州和舍、澄迈加乐—文儒、定安新竹等）→ 不作全岛“蓝盘”或固定党派底盘推定。
+　修正：人数约为台湾客家之零头，缺乏客家意识动员基础，蓝盘仅限个别客家村镇（南丰、和庆等）。
+③ “广东海北”系（雷州半岛—粤西徐闻/海康/遂溪/吴川/电白及粤东潮汕、海南迁民后裔；操海南话/雷州话等）→ 与台湾缺乏直接对应；现实政治取向须按代际、乡村与企业关系验证。
+　属沿海农渔労働阶级，偏绿但省籍矛盾弱、中间性质强，「海北」母地认同远淡于台湾闽南人之族群动员。
+④ 军话居民（明代卫所军户后裔，东方—昌江—儋州—三亚沿海）→ 历史卫所社群不等于外省移民；语言不能直接决定政治取向。
+⑤ 临高话使用者（语言来源与分类仍有争议；约50—60万人，官方多登记为汉族）→ 地方语言身份不等同族群或党派身份。
+⑥ 儋州话使用者（约40—50万人，儋州—昌江—东方沿海，来源与分类仍有争议）→ 海南地方语言与产业社群，不套用台湾族群政治对应。
+⑦ 黎族（海南世居少数民族，主要集中于中部山区与南部山地）→ 不得套用台湾原住民投票比例，现实取向须按县乡、乡村组织和具体议题验证。
+⑧ 苗族（主要分布于中部山区）→ 现实政治取向须结合乡村组织、代际和具体议题验证。
+⑨ 回族（三亚回辉、新村等，来源与语言分类有争议）→ 少数族群，不得以语言或民族直接推定党派倾向。
+⑩ 疍家/水上人（三亚、陵水新村、琼海潭门等渔业社群）→ 渔业与港口议题可能突出，但语言身份不决定政治选择。
+⑪ 村话使用者（官方多登记为汉族；语言来源与分类仍有争议）→ 不作直接政治对应，须区分语言群体与法定民族。
+⑫ 迈话（三亚崖城—水南一带；与疍家话不是同一种语言，来源与分类仍有讨论）→ 少数地方语言使用者社区，政治取向须以当地资料验证。
+⑬ 归侨（兴隆等华侨农场，印尼/马来/越南侨眷等）→ 侨乡身份不等于外省二代或固定党派立场。
+⑭ 军公教与公职体系（历史上的军公教及公职群体）→ 职业身份不自动转化为“泛蓝”政治立场。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>海南—台湾结构差异警示</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>① 海南汉族的「本省」主体为海南话/儋州话/临高话等地方方言民系，历史上持续由福建东部与广东（海北雷州—粤西、潮汕）「下琼」，并无台湾 1949 年「本省/外省」二元断痕；假设 ROC 时期迁入的外省族裔集中在海口、榆林两处，规模远小于台湾眷村。
+② 黎、苗、回等2000五普少数民族占全省17.29%，远高于台湾原住民比重，其蓝盘根基于民族自治行政、头人与教会组织而非政党忠诚。
+③ 台湾选举地理的「闽南绿—客家蓝—原住民蓝」三角结构，在海南应修正为「海南话/临高话/儋州话农渔带（绿底不强、中间盘大）—零星客家与军话（局部蓝）—黎苗回原乡（蓝底）—首府军公教（蓝）」的多中心结构；故本表数字刻意「收敛中间」（中间选民普遍拉高、蓝绿差距缩小），不宜直接照搬台湾之六四比。
+④ 现实海南为中国海南省，黎、苗、回实行民族区域自治，不存在政党竞争；本表纯属假设 ROC 情境下的学术推估练习。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>县市事实档案（新增页）说明</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>工作簿另有「县市事实档案」页，逐县罗列 2000 年第五次人口普查人口、方言民系、民族构成（约）、产业经济、历史人文要点及蓝绿结构修正。方言民系数据据海南省人民政府〈人口民族〉：海南话 500 万+、儋州话 40 万+、临高话 50 万+、军话 10 万+、村话 6 万+、回辉话 1 万+、苗话 8 万+、黎话（黎族）150 万+；人口为《海南省2000年第五次人口普查公报》常住人口，含外来人口、不含外出人口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>光谱与数字</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>将乡镇归入九级光谱（深蓝/蓝/偏蓝/中间偏蓝/中间/中间偏绿/偏绿/绿/深绿），各档基本盘设定为：
 深蓝(50,25,25) 蓝(45,29,26) 偏蓝(39,33,28) 中间偏蓝(36,34,30) 中间(33,36,31)
@@ -619,15 +2482,27 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>免责声明</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>本推估纯属架空历史下的政情模型练习，数字为示意性估计而非任何真实民调或选举结果；海南岛现实为中国海南省。请勿用于任何真实政治研判。资料来源：中选会选举数据库暨维基百科〈台湾选举地理〉、〈南绿北蓝〉、网络温度计〈22县市基本盘〉、2047〈桃园市选区分析〉、客新闻〈2024大选客家投票取向〉、《报导者》〈原住民铁票仓〉及海南省人口普查、统计年鉴等公开资料。</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>本推估纯属架空历史下的政情模型练习，数字为示意性估计而非任何真实民调或选举结果；海南岛现实为中国海南省。请勿用于任何真实政治研判。资料来源：中选会选举数据库暨维基百科〈台湾选举地理〉、〈南绿北蓝〉、网络温度计〈22县市基本盘〉、2047〈桃园市选区分析〉、客新闻〈2024大选客家投票取向〉、《报导者》〈原住民铁票仓〉；海南部分依据海南省人民政府〈人口民族〉（方言民系与世居民族说明）、《海南省2000年第五次全国人口普查主要数据公报》（国家统计局）、海南统计年鉴〈各市县民族人口〉及《海南省志》民族/方言/农业各卷等公开资料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>县市扩展简析说明</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>新增“县市扩展简析”与“县市资料来源”两表，18个县市每篇均超过1000中文字符。2010、2020普查仅作为旧资料缺失时的后续参照；海南话不能等同台湾闽南人，客家并非全岛主体，广东海北移民后裔、儋州话、临高话、军话、村话、黎苗族群及归侨/农场职工共同构成多元人口结构。所有“蓝绿”描述均属假设ROC情景推演，不是族群天性或真实选举数据。</t>
         </is>
       </c>
     </row>
@@ -636,26 +2511,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="110" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
           <t>县市</t>
@@ -688,16 +2565,26 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>台湾类比</t>
+          <t>本地结构推演（须修正直接类比）</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>县市简析</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
+          <t>台湾参照（仅作情景映射）</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>选举原因与县市简析（ROC连续统治假设）</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>2020年七普常住人口(人)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="360" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -722,18 +2609,27 @@
       <c r="F2" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>151.0(海口83.0+琼山67.8)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>台北市</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>首府地位带来大量军公教与外省族裔，蓝盘本钱厚实；但都市化、移民与青年世代崛起，绿盘与现代中间选民同步扩张，现呈台北式蓝绿均势。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】2000年人口约151万，海口与琼山合并形成省府—老城—港口新城—西部农渔腹地的多层社会。省府机关、文教卫生、军警系统、国企及老城宗族网络，使秩序、公共服务、国家认同与两岸关系议题具有较稳定的组织基础；港口、金融商贸、新迁人口和高校青年则更关注就业、住房、交通与开放。
+【选举原因】蓝方在省城机构、文教秩序和两岸路线议题上较易形成稳定支持；绿方在城市更新、老城保护、产业开放及年轻选民议题上具有争取空间；西部儋州话农渔社区、混合家庭和流动性人口构成中间盘。
+【判定与摆动】本表“偏蓝、优势小”可以成立，但更像制度与职业结构造成的有限优势，并非省城人口一致。岛内景气、两岸关系、地方建设资源分配、房价交通和青年就业，均可同时放大任一方优势。
+【口径】以上为ROC连续统治假设下的条件性情景，不是实投票民调；语言、族群和地域不直接等同党派立场。</t>
+        </is>
+      </c>
+      <c r="J2" s="35" t="n"/>
+    </row>
+    <row r="3" ht="360" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -758,18 +2654,27 @@
       <c r="F3" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>高雄市</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>榆林军港与眷村撑起蓝盘，疍家渔港、旅游服务业与都市移民则滋养绿盘，整体互有胜负。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】三亚1984年建市，2000年人口约48万、少数民族占41.33%，形成军港单位体系、崖城文教传统、黎族山地村寨、疍家水上渔业和回族社区、旅游服务业并存的城市。2002年前后旅游扩张、外来就业和山海交通正在提高人口流动性。
+【选举原因】蓝方在军政、港务、国企、公共秩序和两岸安全议题上拥有组织基础；绿方更容易在旅游开放、青年就业、消费市场、城市服务和私营经济议题上争取选民。黎族村寨关注土地、生态、文化与行政服务，疍家水上社群关注海域、生计和安置，不能被单一族群标签概括。
+【判定与摆动】本表“中间略绿、混合度高”较符合多群体并存的结构。旅游收益与生活成本、港口及海洋项目、征地补偿、黎村政治参与、外来人口投票率和候选人村寨组织能力，是主要摆动因素。
+【口径】军港、族群与旅游群体都可能跨越蓝绿边界，表中比例只代表本工作簿的情景权重。</t>
+        </is>
+      </c>
+      <c r="J3" s="35" t="n"/>
+    </row>
+    <row r="4" ht="360" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -794,18 +2699,27 @@
       <c r="F4" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>屏东山地原住民乡(雾台/玛家)</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>黎苗原乡传统倚赖蓝营山地管制、头人/教会人情网络，蓝盘稳居四成上下；青年世代渐受绿营自治论述吸引。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】五指山市2000年人口约10万，2010年少数民族占67.34%，是典型中部山区小县。通什—保亭公路串联县城、农场与山地村寨，传统村寨权威、民族事务机构、文教系统和水源山林网络较重要；长期交通瓶颈与青年外流则限制本地职业容量。
+【选举原因】蓝方较易借重行政中枢、国企事业单位、文教秩序和国家认同形成组织支持；绿方可在山地开发、青年就业、生态与土地议题上吸引年轻选民。黎、苗、回等群体及不同村寨没有统一政治板块，外部力量若要动员，关键是与村寨、学校和基层服务网络合作。
+【判定与摆动】本表“蓝盘稳定领先”可理解为自治山区治理和既有机构网络的结果，而非黎族身份自动支持蓝方。茶药与旅游收益、林地补偿、道路建设、学校医疗和外出人口回流，是可改变中间盘的变量。
+【口径】山地社会低烈度不等于没有利益冲突；代际、财产权和组织关系通常比民族称谓更能解释投票差异。</t>
+        </is>
+      </c>
+      <c r="J4" s="35" t="n"/>
+    </row>
+    <row r="5" ht="360" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -830,18 +2744,27 @@
       <c r="F5" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>宜兰县/嘉义县</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>侨乡商业社会自由主义色彩浓，叠加历史上的左翼记忆，绿盘占优；沿海渔港与嘉积商埠为绿营票仓。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】琼海2000年人口约45万，兼具侨乡网络、沿海渔业与商贸、博鳌旅游门户、革命教育遗产，以及南部山地黎苗村寨。加积、塔洋等传统市镇与潭门渔业、博鳌服务业的利益结构差异明显，侨乡联系又使资金、教育和信息跨境流动。
+【选举原因】蓝方在文教、家乡建设、国家认同、侨资公共项目和传统组织网络上较有条件；绿方在旅游开放、渔业市场、沿海就业和年轻服务群体中具有空间。模型中的绿方优势主要对应沿海市场化与议题组合，不等于侨乡必然倾向绿方，侨乡网络和两岸关系也可反向强化蓝方。
+【判定与摆动】本表“绿盘领先、混合型”可成立，但差距不宜扩大为族群或地域决定论。博鳌开发、渔产品价格、侨资回流、南部山地公共投入、候选人的侨乡与村社关系均会改变结果。
+【口径】黎苗村寨、侨乡、渔民和旅游从业者均非同质群体。</t>
+        </is>
+      </c>
+      <c r="J5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="360" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -866,18 +2789,27 @@
       <c r="F6" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>桃园市(南桃客家庄)/新竹县客家乡</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>那大—南丰—兰洋—和庆客家带为全岛最稳固蓝盘，类比桃竹苗北客；沿海琼西渔镇则绿蓝互有拉锯。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】儋州2000年人口约83.5万、人口规模居全省前列，儋州话人口主体之外并存崖州话、军话、村话、黎话等多种语言。那大等城镇、港口与交通走廊、白马井渔工、南部黎族山区及兴隆农场等构成差异明显的职业和语言网络；客家民系主要集中在那大、南丰、兰洋、和庆一带。
+【选举原因】蓝方较容易依托港口国企、教育行政系统、国家发展项目和传统城镇组织取得支持；绿方更容易在开放产业、流动就业、青年创业和城市扩张议题上取得支持。儋州文化、苏东坡记忆与客家社区可被不同阵营共同使用，不能据此预判党派立场。
+【判定与摆动】本表“偏蓝”主要反映体制、港口和文教网络，而非儋州话身份。港口临港项目、征地与生态、鱼价和农产品价格、国企就业、地方建设资源及年轻人口流动是主要摆动因素。
+【口径】语言、民族和民系均不得作为投票的直接代理变量。</t>
+        </is>
+      </c>
+      <c r="J6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="360" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -902,18 +2834,29 @@
       <c r="F7" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>南投县/花莲县</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>教育传统、宗族网络与侨汇经济共同塑造保守的士绅蓝盘，蓝营长期领先，绿营仅全国大环境顺风时可接近。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】文昌2000年人口约50.9万，侨乡文化、教育传统、宗族网络与华侨资本构成鲜明特征。县城—会文—东阁港等城镇和走廊联系教育商贸、港口物流、椰业、渔业及航天相关产业；侨汇、跨国教育和城市就业又使部分家庭与海外社会高度关联。
+【选举原因】蓝方在文教规范、国家认同、侨乡公共建设、侨资沟通和地方精英网络方面较具组织优势；绿方主要在开放经济、青年流动、港航项目、城市生活和服务业议题上争取支持。文昌传统重教及侨乡网络使其较难出现强烈身份极化。
+【判定与摆动】本表“蓝盘稳定领先”具有现实结构基础，但不是全体侨乡一致支持；侨资流向、侨生与青年回流、国家投资及航天产业、服务业扩张、地方利益分配可改变绿方上升幅度。
+【口径】侨乡身份是跨地域网络，不是固定党派属性。</t>
+        </is>
+      </c>
+      <c r="J7" s="35" t="n">
+        <v>560894</v>
+      </c>
+    </row>
+    <row r="8" ht="360" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -938,18 +2881,27 @@
       <c r="F8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>52.2</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>台中市</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>沿海农渔绿盘、黎苗原乡蓝盘、兴隆归侨蓝底相互抵消，成为全岛最典型的决战中间区。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】万宁2000年人口约51万，兴隆华侨农场、东山岭、南港港、黎族山区与东南沿海渔业并存，兼有侨乡农场组织、旅游度假和山地村寨网络。人口流动较强，青壮年外流与外来就业并存，使本地利益容易与区外资本、城市市场相连。
+【选举原因】蓝方可在农场单位、教育行政、地方建设、国家项目和侨乡组织中获得稳定支持；绿方在旅游开放、滨海市场、青年就业和民营服务经济中更易扩张。黎族山地关注山林土地、生态补偿和公共服务，华侨农场职工则更关注单位稳定与福利，两者难以合并为同一投票板块。
+【判定与摆动】本表“中间略绿、胜负接近”符合多网络并存。旅游收益与土地占用、港口开发、侨资和外来资本、农产品价格、农场改制及青年留返，是主要摆动变量。
+【口径】少数族群、侨乡、农场和旅游群体均不能单独预测投票。</t>
+        </is>
+      </c>
+      <c r="J8" s="35" t="n"/>
+    </row>
+    <row r="9" ht="360" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -974,18 +2926,29 @@
       <c r="F9" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>35.8</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>高雄市(港都工业)+屏东原乡</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>军话村落与八所港军公教是罕见的外省族群类似物，蓝盘扎实；沿海农渔与山乡黎苗构成绿营突破口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】东方2000年人口约35.8万，县内同时存在八所军话村落、港口与矿业交通、农牧渔业、南部黎族山区和农场职工。军话村落经过长期本地化，与儋州话、海南话及黎族村寨交错共居；资源、土地和单位就业使不同职业群体利益并不一致。
+【选举原因】蓝方较可能在港口、国企、行政秩序和国家开发项目中形成支持；绿方在开放产业、渔业市场、民营就业和青年人口中具有议题空间。黎族村寨只在山林权属、生态补偿和土地开发等具体问题上表现强势，语言或民族本身缺乏稳定动员力。
+【判定与摆动】本表“蓝方小优、混合度高”可由组织化单位与职业分化解释，而非因1949年后移民。港口矿产项目、征地补偿、环境争议、渔农产品价格和单位就业变化都可迅速改变中间盘。
+【口径】“军话村”“汉族”或“产业移民后代”均不是单一党派标签。</t>
+        </is>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>444458</v>
+      </c>
+    </row>
+    <row r="10" ht="360" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -1010,18 +2973,27 @@
       <c r="F10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>新竹县</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>明清定安科举冠绝琼北，士绅、公教与宗族遗产丰厚，蓝盘长期占优。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】定安2000年人口约28万，是琼北传统文教县，仕宦记忆、学校和宗族网络较强，同时以农业、县域商贸和人口通勤为主。县内族群构成较复杂，邻近海口的经济外溢和青年外出，使传统权威逐渐与城市就业并存。
+【选举原因】蓝方较易以文教传统、秩序建设、国家认同和地方精英网络取得稳定支持；绿方更容易在就业机会、交通改善、产业发展和代际更新议题上争取青年。定安族群内部与各乡镇差异有限，族群动员通常弱于文教、宗族和职业网络。
+【判定与摆动】本表“蓝盘稳定领先”更多反映地方精英、机关事业单位和琼北政治文化，而非单一族群。年轻人口是否回流、海口外溢产业、县域道路水利投资、学校调整和地方候选人网络，是关键摆动因素。
+【口径】文化传统可被不同党派共同使用，不应被视为固定投票倾向。</t>
+        </is>
+      </c>
+      <c r="J10" s="35" t="n"/>
+    </row>
+    <row r="11" ht="360" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -1046,18 +3018,27 @@
       <c r="F11" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>彰化/云林农业对决区</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>后设县的移民社会缺少历史派系包袱，蓝绿皆无稳固铁票，一切看大环境与水利会、农会动向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】屯昌2000年人口约25.3万，是建县较晚、移民来源较多的中部农业县，缺少延续数百年的单一地方士绅结构。橡胶、槟榔、南药、养殖和农场经济使基层关系较依赖村社、合作社和单位网络；年轻人大多外出谋生，返乡就业和公共服务是重要议题。
+【选举原因】蓝方可依托行政系统、国企农场和传统村社争取稳定支持；绿方在流动就业、民营发展、价格波动和代际变化上更具弹性。移民来源混杂使语言和宗族只能作为动员渠道，难以形成统一身份阵营。
+【判定与摆动】本表“三盘接近、蓝绿互有胜负”较符合新县份与农业社会的开放性。农产品和橡胶价格、土地承包与集体收益、道路水利、县域产业承接、候选人组织能力及外出选民参与率，都会显著改变结果。
+【口径】缺少传统精英不等于结构松散，基层单位与利益网络仍可能形成稳定支持。</t>
+        </is>
+      </c>
+      <c r="J11" s="35" t="n"/>
+    </row>
+    <row r="12" ht="360" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -1082,18 +3063,27 @@
       <c r="F12" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>新北市郊区/彰化县</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>紧邻首府而通勤、就学人口多，客家与临高移民又自带蓝绿反差，整体胶着。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】澄迈2000年人口约43.5万，北部老城、骑楼传统与文教网络较强，南部咖啡、热带农业和黎族山地并存，又处海口经济与人口外溢范围。2002年前后跨县通勤、旅游开发、港口和交通建设已强化其与海口的城市—腹地关系。
+【选举原因】蓝方在海口关联、文教秩序、国企与公共投资议题上较有条件；绿方在开放产业、城市扩张、民营就业、港口项目和年轻通勤群体中具有空间。不同方言、乡村和城区群体主要围绕土地、学校、交通和房价等具体利益形成议题性联盟。
+【判定与摆动】本表“中间略绿、胜负接近”可以成立。最重要的摆动变量是海口产业和人口外溢、港口及旅游项目、地方建设资源、土地征收、农产品价格，以及候选人在老城、南部山区和新就业群体中的组织程度。
+【口径】县与邻近大城市的空间整合，不代表居民自动接受同一党派。</t>
+        </is>
+      </c>
+      <c r="J12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="360" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -1118,18 +3108,27 @@
       <c r="F13" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>宜兰县(渔业绿盘)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>新盈、调楼等大渔港农渔劳资结构对绿营有利，和舍客家带则是蓝营孤垒。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】临高2000年人口约38.9万，临高话、儋州话、海南话、军话及村话等语言长期交错分布。县域以农业和沿海渔业为底盘，港口、滨海交通与工业项目连接外部经济；在ROC连续统治假设下，现代政治记忆不能直接移植，应重点观察语言社区与利益边界。
+【选举原因】蓝方较可能在港口、国企、公共秩序和跨区域建设议题上组织支持；绿方更容易在渔业市场、开放产业、青年流动和沿海服务中争取选民。临高话认同可强化地方自主和代表权诉求，却不自动决定蓝绿方向。
+【判定与摆动】本表“绿盘领先、混合型”来自沿海市场与职业议题的结构性组合。港口项目、渔获价格、海岸与土地开发、环境争议、地方候选人的村社网络及县际资源分配，是主要摆动因素。
+【口径】语言、族群与地理分区均不能替代实际投票证据。</t>
+        </is>
+      </c>
+      <c r="J13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="360" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -1154,18 +3153,29 @@
       <c r="F14" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>花莲县秀林乡/万荣乡</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>黎族聚居与山地管制历史使蓝营组织占绝对上风，绿营仅靠青年与外来公教零星渗透。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】白沙2000年人口约16.5万，2010年少数民族占67.43%。县城—农场—黎族村寨由公路串联，橡胶、茶业和热带农业构成生计底盘；山地村寨的宗族、头人和互助网络较重要，青壮年持续外流又造成参与不足与代际断层。
+【选举原因】蓝方较易依托民族区域自治机构、基层公共服务、教育和国家认同形成稳定支持；绿方可在橡胶与茶叶价格、山林流转、生态补偿、道路建设和青年就业议题上吸引选民。族群关系整体较和缓，但水源、山林和村际利益仍可能造成局部高强度动员。
+【判定与摆动】本表“蓝盘稳定领先”反映自治山区治理与机构网络，不是黎族身份的直接投票效应。农产品价格、补偿标准、道路改善、学校医疗、回流就业和宗族组织，是中间盘变化的关键。
+【口径】低冲突外观不等于无分歧，外部力量仍需通过村寨与服务网络落地。</t>
+        </is>
+      </c>
+      <c r="J14" s="35" t="n">
+        <v>164699</v>
+      </c>
+    </row>
+    <row r="15" ht="360" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -1190,18 +3200,29 @@
       <c r="F15" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>高雄市(工矿)+山地原乡</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>矿区公教、军话村落与原乡黎寨层层加码蓝盘，渔港海尾则绿营见长。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】昌江2000年人口约22万，县内并存石碌矿工社区、铁路港口走廊、南部黎族山地、乌烈与海尾等渔镇及农场职工。矿工社区具有单位、班组、住房和福利依附，黎族村寨依赖村寨权威，渔农则围绕海况、价格和渔业资源组织利益，三套网络很少共享权威来源。
+【选举原因】若延续矿产—能源—港口开发路径，蓝方在国企就业、工资福利、安全生产和国家项目上较易获得支持；绿方在渔业市场、开放产业、生态约束、征地补偿和民营就业方面更易形成议题动员。黎族山区不会因民族身份形成统一阵营。
+【判定与摆动】本表“蓝方小优、混合度高”主要由组织化单位与职业分化解释。产业景气、项目选址、环境与水资源、补偿、渔价、矿工代际更替和山地村寨参与，均可使蓝绿差距迅速反转。
+【口径】语言、民族、原住民或移民后代都不能直接预测党派选择。</t>
+        </is>
+      </c>
+      <c r="J15" s="35" t="n">
+        <v>232124</v>
+      </c>
+    </row>
+    <row r="16" ht="360" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -1226,18 +3247,29 @@
       <c r="F16" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>44.6</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>屏东县(平原+原乡)</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>沿海闽南海南话农渔带实力偏绿，内陆黎族乡镇偏蓝，全县成屏东式南北矛盾县。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】乐东2000年人口约44.7万，2002年户籍少数民族占38.06%。西部、北部农林业和黎族山地与莺歌海、黄流等沿海盐业渔业区并存，农业园区、公路节点和外出务工共同塑造“沿海市场—山地村寨”双重结构。
+【选举原因】蓝方较易通过村寨组织、公共服务、民族事务和国家项目形成稳定支持；绿方在沿海渔业、开放农业、农产品加工、市场就业和青年流动中更具议题空间。黎族山地与沿海汉族、渔业群体关注点差异明显，语言和民族不构成统一投票板块。
+【判定与摆动】本表“中间略绿、混合度高”较符合职业与空间分化。渔盐业景气、园区和旅游项目、征地补偿、山林权益、农业价格、交通改善及外出青年回流，是主要摆动因素。
+【口径】自治县名称描述制度安排，不意味着所有居民具有同一族群、语言或政治立场。</t>
+        </is>
+      </c>
+      <c r="J16" s="35" t="n">
+        <v>464435</v>
+      </c>
+    </row>
+    <row r="17" ht="360" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -1262,18 +3294,29 @@
       <c r="F17" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>屏东县(潮州/牡丹原乡)</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>黎族原乡蓝盘为底，新村港疍家与沿海都会化社区为绿营据点，蓝略胜。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】陵水2000年人口约30.3万，2002年户籍少数民族占55.98%，形成黎族山地村寨、椰林与热带农业、新村等沿海渔业社区、疍家水上社群及三亚旅游外溢并存的格局。人口流动和跨县就业使县域利益与三亚的资本、客流和住房市场紧密相连。
+【选举原因】蓝方在自治制度基层网络、文教和公共投资议题上可能获得稳定支持；绿方在旅游开发、开放市场、渔业转型、青年就业与城市外溢中更容易争取选民。黎族村寨关注土地、生态和文化，沿海社群关注渔业、海域和安置，利益不宜合并。
+【判定与摆动】本表“蓝方小优、胜负接近”可由自治机构和山地组织解释。三亚旅游景气、房地产与港口项目、征地补偿、海水养殖、渔获价格、山村青年外出及候选人村社关系，可使绿方在沿海快速上升。
+【口径】疍家是历史职业与社区身份，不应直接转换为法定民族或党派类别。</t>
+        </is>
+      </c>
+      <c r="J17" s="35" t="n">
+        <v>372511</v>
+      </c>
+    </row>
+    <row r="18" ht="360" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -1298,18 +3341,29 @@
       <c r="F18" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>屏东县雾台乡/来义乡</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>黎苗原乡组织严密，观光与山地政策长期由蓝营掌握，蓝盘稳固。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】保亭2000年人口约14万，2010年少数民族占比接近七成。县域距三亚近，呈现“人在三亚、家在保亭”的通勤和外出就业结构；黎苗山地村寨的集体土地、林权和传统文化被纳入温泉、雨林及民族文化景区后，土地作价、分红、搬迁和文化展示成为核心议题。
+【选举原因】蓝方较易依托民族区域自治、基层村寨、公共服务和地方稳定议题形成支持；绿方在旅游开放、外来资本、青年就业和城市生活议题上具有竞争力。但外来经营者、本地资源持有者、县城职工和村寨内部意见并不统一，常态应是低烈度而非身份极化。
+【判定与摆动】本表“蓝盘稳定领先”反映小县机构与自治治理网络，不代表黎苗整体支持；土地收益、景区分配、生态搬迁、三亚就业、返乡创业和代际更替都能重塑中间盘。
+【口径】民族与语言提供文化资源，却不是可直接换算的投票倾向。</t>
+        </is>
+      </c>
+      <c r="J18" s="35" t="n">
+        <v>156108</v>
+      </c>
+    </row>
+    <row r="19" ht="360" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -1334,18 +3388,29 @@
       <c r="F19" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>花莲县万荣乡/秀林乡</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>黎苗原乡与松涛客家双重蓝底，蓝营在中部山地一家独大。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>【结构底盘】琼中2000年人口约17.2万，2010年少数民族占66.44%。黎母山文化腹地、黎苗与中原客家社区、松涛水库生态责任、绿橙等山地农业和中部交通节点交织；长期人口外流使许多家庭与海口、三亚和内地就业市场相连。
+【选举原因】蓝方较易通过自治机构、农场与行政服务、教育秩序及国家发展项目形成稳定支持；绿方可在山地农业市场化、生态补偿、道路改善、青年回流和外出选民权益上争取支持。族群与语言交错只提供动员渠道，不形成统一党派板块。
+【判定与摆动】本表“蓝盘稳定领先”更可能是小县机构网络和既有治理能力的结果。松涛库区补偿、绿橙和农产品价格、跨县就业、回流发展、交通建设、青年参与及村寨候选人网络，是主要摆动因素。
+【口径】人口外流会降低本地参与率，也可能使返乡议题对外流家庭更重要。</t>
+        </is>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>179586</v>
+      </c>
+    </row>
+    <row r="20" ht="300" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>全岛合计</t>
@@ -1376,23 +3441,33 @@
           <t>30</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>757.0</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>首府、原乡、客家与侨乡四大板块相持，蓝略优（客家务农深层蓝盘被首府与侨乡绿盘部分抵销）</t>
-        </is>
-      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>【全岛结构】按本表2002年情景权重，蓝35%、绿35%、中间30%，总体不是族群决定型格局，而是四类结构叠加：省府军公教与文教体系、港口侨乡与开放市场、黎族苗族自治山区、矿业渔业农场及外出就业网络。
+【选举原因】蓝方的稳定基础主要来自国家认同、秩序与两岸议题、行政事业单位、文教和传统组织网络；绿方的主要拓展空间来自城市青年、开放产业、服务经济、农业渔民组织及地方自治议题。两者在传统地方社会都有组织资源，并非一方占据全部人口。
+【县域差异】海口、文昌、定安、五指山等较易形成蓝方稳定优势；琼海、临高、澄迈、东方等混合度较高；琼中、乐东、屯昌、陵水等胜负更受具体产业、代际和候选人组织影响；保亭、昌江等则需重点观察旅游、矿业、单位与村寨利益。
+【胜负机制】真正决定全岛结果的不是单一民族或语言，而是国家经济与两岸局势、县际资源分配、地方候选人网络、青年回流或外流、农产品与产业价格、土地环境争议及投票率。中间盘可按议题在县市间移动。
+【结论与边界】在ROC连续统治假设下，最稳健的结论是“蓝绿接近、县域分化和中间盘决定”。本表是结构性条件推演，不构成现实投票预测；族群、语言、地域、职业或原住民身份均不得直接等同党派支持。</t>
+        </is>
+      </c>
+      <c r="J20" s="36" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1455,11 +3530,11 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>原因简析</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
+          <t>条件性情景假设（非民调）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1496,11 +3571,11 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；港区市郊；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；港区市郊；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1537,11 +3612,11 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市郊；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市郊；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1578,11 +3653,11 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；港砦渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；港砦渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1619,11 +3694,11 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；临高话民系滨海农业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；临高话民系滨海农业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1660,11 +3735,11 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；基层农业乡镇，宗族与农渔业组织为主；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；基层农业乡镇，宗族与农渔业组织为主；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1701,11 +3776,11 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市郊混合区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市郊混合区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1742,11 +3817,11 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；火山口农业乡镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；火山口农业乡镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1783,11 +3858,11 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1824,11 +3899,11 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；火山果园农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；火山果园农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1865,11 +3940,11 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；南渡江农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；南渡江农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1906,11 +3981,11 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；老城商业核心；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；老城商业核心；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1947,11 +4022,11 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；都会市区，通勤白领与青年世代为主，中间选民比例高；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；都会市区，通勤白领与青年世代为主，中间选民比例高；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -1988,11 +4063,11 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；金融商贸区，白领青年多；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；金融商贸区，白领青年多；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2029,11 +4104,11 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；老城闹区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；老城闹区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2070,11 +4145,11 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；都会市区，通勤白领与青年世代为主，中间选民比例高；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；都会市区，通勤白领与青年世代为主，中间选民比例高；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2111,11 +4186,11 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市区住宅与商办；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市区住宅与商办；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2152,11 +4227,11 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2193,11 +4268,11 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市郊农业带；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市郊农业带；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2234,11 +4309,11 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2275,11 +4350,11 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2316,11 +4391,11 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2357,11 +4432,11 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2398,11 +4473,11 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2439,11 +4514,11 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市政与商办区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市政与商办区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2480,11 +4555,11 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；琼州府古城文脉，士绅公教与文教机构集中；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；琼州府古城文脉，士绅公教与文教机构集中；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2521,11 +4596,11 @@
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2562,11 +4637,11 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；丘浚故里文教脉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；丘浚故里文教脉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2603,11 +4678,11 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2644,11 +4719,11 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2685,11 +4760,11 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2726,11 +4801,11 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2767,11 +4842,11 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2808,11 +4883,11 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；旧州古城农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；旧州古城农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2849,11 +4924,11 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2890,11 +4965,11 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；行政中枢周边，军公教密度高；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；行政中枢周边，军公教密度高；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2931,11 +5006,11 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -2972,11 +5047,11 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；老城商区，眷村与公教遗绪深厚；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；老城商区，眷村与公教遗绪深厚；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3013,11 +5088,11 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；高校与新住宅区，年轻人口集中；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；高校与新住宅区，年轻人口集中；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3054,11 +5129,11 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；高教文教区，青年学生多；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；高教文教区，青年学生多；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3095,11 +5170,11 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3136,11 +5211,11 @@
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；老城住宅区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；老城住宅区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3177,11 +5252,11 @@
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；市区河岸；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；市区河岸；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3218,11 +5293,11 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；河岛新区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；河岛新区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3259,11 +5334,11 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；海滨围垦渔农；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；海滨围垦渔农；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3300,11 +5375,11 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；海口东郊门户，通勤农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；海口东郊门户，通勤农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3341,11 +5416,11 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；农场与新开发区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；农场与新开发区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3382,11 +5457,11 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；东寨港红树林农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；东寨港红树林农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3423,11 +5498,11 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；内陆农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；内陆农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3464,11 +5539,11 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；海口文昌交界农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；海口文昌交界农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>海口市</t>
@@ -3505,11 +5580,11 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>海南特别行政区首府，1949 后国府军公教、外省眷村与文教机构汇聚（类比台北市区均势格局）；滨海渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="44" customHeight="1">
+          <t>海口—琼山为海南特别行政区首府（含古琼州府城），假设 ROC 下军公教、外省族裔与文教机构汇聚（类比台北市区），海口港商贸与府城科第农桑并存，西郊长流—秀英为临高话带；滨海渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3546,11 +5621,11 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；东线农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；东线农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3587,11 +5662,11 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；东线农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；东线农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3628,11 +5703,11 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；市郊，移民集中；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；市郊，移民集中；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3669,11 +5744,11 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；市郊新开发区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；市郊新开发区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3710,11 +5785,11 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；渔港夜市聚落；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；渔港夜市聚落；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3751,11 +5826,11 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3792,11 +5867,11 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；滨海度假区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；滨海度假区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3833,11 +5908,11 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；海滨渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；海滨渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3874,11 +5949,11 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3915,11 +5990,11 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3956,11 +6031,11 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；海南回族(回辉/回新)聚居地，兼黎汉混居；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；海南回族(回辉/回新)聚居地，兼黎汉混居；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -3997,11 +6072,11 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；滨海黎汉社区与景区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；滨海黎汉社区与景区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4038,11 +6113,11 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；市区；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4079,11 +6154,11 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；疍家水上人家渔港社区；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；疍家水上人家渔港社区；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4120,11 +6195,11 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；黎汉混居丘陵；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；黎汉混居丘陵；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4161,11 +6236,11 @@
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；古崖州卫所，军话/迈话文化重镇，文教古脉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；古崖州卫所，军话/迈话文化重镇，文教古脉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4202,11 +6277,11 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4243,11 +6318,11 @@
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；崖州湾农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；崖州湾农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
           <t>三亚市</t>
@@ -4284,11 +6359,11 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>ROC 南海舰队要港（榆林）与新移民旅游城市，军港眷村与都市移民并存（类比高雄市）；古商港渔业聚落；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="44" customHeight="1">
+          <t>榆林军港（ROC 南海舰队要地）与新移民旅游城市，军眷蓝盘 vs 疍家/旅游服务绿盘（类比高雄市）；三亚话、黎话、回辉话、迈话、疍家话多民系并存；古商港渔业聚落；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4325,11 +6400,11 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；县城/行政商贸中心，黎汉杂处；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；县城/行政商贸中心，黎汉杂处；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4366,11 +6441,11 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；南圣地农业镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；南圣地农业镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4407,11 +6482,11 @@
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎族山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4448,11 +6523,11 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4489,11 +6564,11 @@
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎族丘陵乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎族丘陵乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4530,11 +6605,11 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎族山地镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎族山地镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4571,11 +6646,11 @@
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4612,11 +6687,11 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；黎族山谷镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；黎族山谷镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
           <t>五指山市</t>
@@ -4653,11 +6728,11 @@
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>黎苗山地市，ROC 设山地管制与民族行政，人情网络与原乡组织牢固（类比台湾山地原住民乡）；五指山麓黎苗村寨；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="44" customHeight="1">
+          <t>黎苗山地市（原通什），民族行政与山地人情网络牢固（类比台湾山地原住民乡）；山城旅游、茶叶与南药；五指山麓黎苗村寨；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4694,11 +6769,11 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；县城侨乡商埠；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；县城侨乡商埠；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4735,11 +6810,11 @@
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；苗族聚居乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；苗族聚居乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4776,11 +6851,11 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；黎苗边区；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；黎苗边区；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4817,11 +6892,11 @@
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；万泉河中游农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；万泉河中游农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4858,11 +6933,11 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；琼崖苏区红色根据地旧址，左翼历史记忆；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；琼崖苏区红色根据地旧址，左翼历史记忆；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4899,11 +6974,11 @@
       </c>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；丘陵农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；丘陵农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4940,11 +7015,11 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；万泉河畔，红色记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；万泉河畔，红色记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -4981,11 +7056,11 @@
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5022,11 +7097,11 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5063,11 +7138,11 @@
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5104,11 +7179,11 @@
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5145,11 +7220,11 @@
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；古乐会县城；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；古乐会县城；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5186,11 +7261,11 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；沿江农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；沿江农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5227,11 +7302,11 @@
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="60" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5268,11 +7343,11 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5309,11 +7384,11 @@
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5350,11 +7425,11 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5391,11 +7466,11 @@
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；沿海农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；沿海农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5432,11 +7507,11 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；滨海渔农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；滨海渔农乡；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5473,11 +7548,11 @@
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；滨海农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；滨海农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5514,11 +7589,11 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；侨乡商埠；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；侨乡商埠；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5555,11 +7630,11 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>琼海市</t>
@@ -5596,11 +7671,11 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>万泉河侨乡与琼崖经贸重镇，左翼运动史记忆深刻（类比宜兰/嘉义绿营盘面）；千年南海渔港(疍家/更路簿)；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="44" customHeight="1">
+          <t>万泉河侨乡与琼崖经贸重镇，嘉积商埠、博鳌会展与潭门南海渔港（疍家/更路簿）并立，左翼运动与华侨商业记忆交织（类比宜兰—嘉义绿盘）；千年南海渔港(疍家/更路簿)；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="60" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5637,11 +7712,11 @@
       </c>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；客家话都会与市府驻地，海南客家中心；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；客家话都会与市府驻地，海南客家中心；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5678,11 +7753,11 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="60" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5719,11 +7794,11 @@
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5760,11 +7835,11 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农垦农场乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农垦农场乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="60" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5801,11 +7876,11 @@
       </c>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；深水港石化开发区，外来技术劳工与外省干部；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；深水港石化开发区，外来技术劳工与外省干部；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5842,11 +7917,11 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；洋浦后勤市街；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；洋浦后勤市街；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="60" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5883,11 +7958,11 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="60" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5924,11 +7999,11 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；火山海岸农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；火山海岸农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="60" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -5965,11 +8040,11 @@
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；ROC 旧儋县城，公教聚落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；ROC 旧儋县城，公教聚落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="60" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6006,11 +8081,11 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农垦农场与黎汉山区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农垦农场与黎汉山区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="60" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6047,11 +8122,11 @@
       </c>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="60" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6088,11 +8163,11 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6129,11 +8204,11 @@
       </c>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="60" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6170,11 +8245,11 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；古儋州州治，文明书院士绅脉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；古儋州州治（苏东坡贬儋地·东坡书院），士绅学脉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6211,11 +8286,11 @@
       </c>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；橡胶农场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；橡胶农场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6252,11 +8327,11 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6293,11 +8368,11 @@
       </c>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="60" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6334,11 +8409,11 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；滨海渔农；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；滨海渔农；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="60" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6375,11 +8450,11 @@
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6416,11 +8491,11 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；客家村落群；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；客家村落群；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6457,11 +8532,11 @@
       </c>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；客家话占七成的「客家镇」；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；客家话占七成的「客家镇」；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6498,11 +8573,11 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；黎汉偏远山乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；黎汉偏远山乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6539,11 +8614,11 @@
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；客家村镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；客家村镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
           <t>儋州市</t>
@@ -6580,11 +8655,11 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>海南客家第一大聚居地（约 20 万客家话人口聚于东部那大一线），类比桃竹苗客家蓝盘；沿海儋州话渔镇似南部农渔绿营；客家聚落与温泉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="44" customHeight="1">
+          <t>全岛方言民系最复杂县：儋州话（粤语系）沿海、海南话、客家方言聚于那大—南丰—兰洋—和庆、军话与临高话北部、黎话山区并存；洋浦港石化、北部湾盐渔与松涛灌区；客家聚落与温泉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="60" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6621,11 +8696,11 @@
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；文昌古城文脉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；文昌古城文脉；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6662,11 +8737,11 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6703,11 +8778,11 @@
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；围垦农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；围垦农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6744,11 +8819,11 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；古商埠侨乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；古商埠侨乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="60" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6785,11 +8860,11 @@
       </c>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；基层农业乡镇，宗族与农渔业组织为主；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；基层农业乡镇，宗族与农渔业组织为主；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6826,11 +8901,11 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1">
       <c r="A133" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6867,11 +8942,11 @@
       </c>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6908,11 +8983,11 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="60" customHeight="1">
       <c r="A135" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6949,11 +9024,11 @@
       </c>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -6990,11 +9065,11 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；侨乡农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；侨乡农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="60" customHeight="1">
       <c r="A137" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7031,11 +9106,11 @@
       </c>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="60" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7072,11 +9147,11 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1">
       <c r="A139" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7113,11 +9188,11 @@
       </c>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="60" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7154,11 +9229,11 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；南洋侨乡望族；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；南洋侨乡望族；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7195,11 +9270,11 @@
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7236,11 +9311,11 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1">
       <c r="A143" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7277,11 +9352,11 @@
       </c>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；港口侨眷；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；港口侨眷；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="60" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7318,11 +9393,11 @@
       </c>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="60" customHeight="1">
       <c r="A145" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7359,11 +9434,11 @@
       </c>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="60" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7400,11 +9475,11 @@
       </c>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="60" customHeight="1">
       <c r="A147" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7441,11 +9516,11 @@
       </c>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；内陆农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；内陆农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="60" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7482,11 +9557,11 @@
       </c>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；椰林渔业侨乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；椰林渔业侨乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1">
       <c r="A149" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7523,11 +9598,11 @@
       </c>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；侨乡教育之乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；侨乡教育之乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="60" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7564,11 +9639,11 @@
       </c>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="60" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7605,11 +9680,11 @@
       </c>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；农业镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="60" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7646,11 +9721,11 @@
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；海防侨乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；海防侨乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="60" customHeight="1">
       <c r="A153" s="5" t="inlineStr">
         <is>
           <t>文昌市</t>
@@ -7687,11 +9762,11 @@
       </c>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>全岛文教侨乡之首，科第宗族与南洋侨汇传统深厚（类比花莲—南投式传统蓝盘）；离岛礁村，渔民海防聚落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
+          <t>全岛文教与侨乡之首（海外华侨逾 200 万），椰林渔业、清澜港与航天基地（现实文昌卫星发射中心）所在；文昌话为海南话标准音；离岛礁村，渔民海防聚落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="60" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7728,11 +9803,11 @@
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；县城商埠；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；县城商埠；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="60" customHeight="1">
       <c r="A155" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7769,11 +9844,11 @@
       </c>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；黎族山地；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；黎族山地；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="60" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7810,11 +9885,11 @@
       </c>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；黎族山地；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；黎族山地；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="60" customHeight="1">
       <c r="A157" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7851,11 +9926,11 @@
       </c>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；黎汉滨海山乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；黎汉滨海山乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="60" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7892,11 +9967,11 @@
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；南洋归侨农场(印尼/马来/越南侨眷)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；南洋归侨农场(印尼/马来/越南侨眷)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="60" customHeight="1">
       <c r="A159" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7933,11 +10008,11 @@
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；丘陵农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；丘陵农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="60" customHeight="1">
       <c r="A160" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -7974,11 +10049,11 @@
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；黎族聚居镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；黎族聚居镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="60" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8015,11 +10090,11 @@
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="60" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8056,11 +10131,11 @@
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；六连岭根据地记忆农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；六连岭根据地记忆农镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="60" customHeight="1">
       <c r="A163" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8097,11 +10172,11 @@
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="60" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8138,11 +10213,11 @@
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="60" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8179,11 +10254,11 @@
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="60" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8220,11 +10295,11 @@
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；沿海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；沿海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="60" customHeight="1">
       <c r="A167" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8261,11 +10336,11 @@
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="60" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8302,11 +10377,11 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="60" customHeight="1">
       <c r="A169" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8343,11 +10418,11 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；侨乡商港与红色根据地记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；侨乡商港与红色根据地记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="60" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8384,11 +10459,11 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；沿海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；沿海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="60" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8425,11 +10500,11 @@
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；侨乡与红色记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；侨乡与红色记忆；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="60" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
         <is>
           <t>万宁市</t>
@@ -8466,11 +10541,11 @@
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>农渔县兼黎苗边区与兴隆归侨农场，族群多元、蓝绿势均（类比台中市中间盘）；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="44" customHeight="1">
+          <t>农渔大县与黎苗边区并存，兴隆华侨农场（印尼/马来/越南归侨）散落其间；和乐—港北渔港、六连岭根据地对记忆、东山羊/兴隆咖啡；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="60" customHeight="1">
       <c r="A173" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8507,11 +10582,11 @@
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；县治工业港与军港，军话居民多；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；县治工业港与军港，军话居民多；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="60" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8548,11 +10623,11 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="60" customHeight="1">
       <c r="A175" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8589,11 +10664,11 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；八所港滨渔商聚落；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；八所港滨渔商聚落；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="60" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8630,11 +10705,11 @@
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="60" customHeight="1">
       <c r="A177" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8671,11 +10746,11 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；沿海农渔；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；沿海农渔；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="60" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8712,11 +10787,11 @@
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="60" customHeight="1">
       <c r="A179" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8753,11 +10828,11 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；沿海农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；沿海农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="60" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8794,11 +10869,11 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；古感恩县治，沿海农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="60" customHeight="1">
       <c r="A181" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8835,11 +10910,11 @@
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；军话村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="60" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8876,11 +10951,11 @@
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="60" customHeight="1">
       <c r="A183" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8917,11 +10992,11 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族村落；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="60" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8958,11 +11033,11 @@
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="60" customHeight="1">
       <c r="A185" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -8999,11 +11074,11 @@
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="60" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -9040,11 +11115,11 @@
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="60" customHeight="1">
       <c r="A187" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -9081,11 +11156,11 @@
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="60" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -9122,11 +11197,11 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；偏远黎寨；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；偏远黎寨；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="60" customHeight="1">
       <c r="A189" s="5" t="inlineStr">
         <is>
           <t>东方市</t>
@@ -9163,11 +11238,11 @@
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>军话（明代军户后裔）聚落密集、八所工矿军港与黎族内陆并存（类比高雄工业港+屏东原乡）；库区农垦乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="44" customHeight="1">
+          <t>军话（明初卫所军户后裔）聚落密集、八所深水港与工矿石化、昌化江下游村话民系与内陆黎乡并存（类比高雄工业港＋屏东原乡）；库区农垦乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="60" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9204,11 +11279,11 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；县城(明清定安古城)；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；县城(明清定安古城)；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="60" customHeight="1">
       <c r="A191" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9245,11 +11320,11 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="60" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9286,11 +11361,11 @@
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="60" customHeight="1">
       <c r="A193" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9327,11 +11402,11 @@
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；中部丘陵农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；中部丘陵农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="60" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9368,11 +11443,11 @@
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="60" customHeight="1">
       <c r="A195" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9409,11 +11484,11 @@
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="60" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9450,11 +11525,11 @@
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="60" customHeight="1">
       <c r="A197" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9491,11 +11566,11 @@
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="60" customHeight="1">
       <c r="A198" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9532,11 +11607,11 @@
       </c>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="199" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="60" customHeight="1">
       <c r="A199" s="5" t="inlineStr">
         <is>
           <t>定安县</t>
@@ -9573,11 +11648,11 @@
       </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>「琼北科第之乡」士绅文教传统浓厚（类比新竹县之文教蓝盘）；丘陵农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="44" customHeight="1">
+          <t>「琼北科举之乡」士绅文教传统冠绝海南（明清进士辈出），南丽湖、定安古城与母瑞山并存；海南话（琼北片）为主；丘陵农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="60" customHeight="1">
       <c r="A200" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9614,11 +11689,11 @@
       </c>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；县城/南渡江支流；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；县城/南渡江支流；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="60" customHeight="1">
       <c r="A201" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9655,11 +11730,11 @@
       </c>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；黎苗聚居边区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；黎苗聚居边区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="60" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9696,11 +11771,11 @@
       </c>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="60" customHeight="1">
       <c r="A203" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9737,11 +11812,11 @@
       </c>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="204" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="60" customHeight="1">
       <c r="A204" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9778,11 +11853,11 @@
       </c>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业(枫木鹿场)；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业(枫木鹿场)；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="60" customHeight="1">
       <c r="A205" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9819,11 +11894,11 @@
       </c>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="60" customHeight="1">
       <c r="A206" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9860,11 +11935,11 @@
       </c>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="60" customHeight="1">
       <c r="A207" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9901,11 +11976,11 @@
       </c>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="60" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9942,11 +12017,11 @@
       </c>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="60" customHeight="1">
       <c r="A209" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -9983,11 +12058,11 @@
       </c>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="60" customHeight="1">
       <c r="A210" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -10024,11 +12099,11 @@
       </c>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="60" customHeight="1">
       <c r="A211" s="5" t="inlineStr">
         <is>
           <t>屯昌县</t>
@@ -10065,11 +12140,11 @@
       </c>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>建置后垦殖新县，各族群移民松散分布、无强势地方派系（类比中台湾农业决战区）；垦殖农场乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="44" customHeight="1">
+          <t>1950 年代由琼山/定安/澄迈析置的垦殖新县，各族群移民松散分布、地方派系淡薄（类比中台湾农业决战区）；橡胶槟榔垦殖与枫木鹿场；垦殖农场乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="60" customHeight="1">
       <c r="A212" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10106,11 +12181,11 @@
       </c>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；县城(南渡江)；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；县城(南渡江)；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="60" customHeight="1">
       <c r="A213" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10147,11 +12222,11 @@
       </c>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="60" customHeight="1">
       <c r="A214" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10188,11 +12263,11 @@
       </c>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；黎汉山区与农场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；黎汉山区与农场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="60" customHeight="1">
       <c r="A215" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10229,11 +12304,11 @@
       </c>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；北部湾渔业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；北部湾渔业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="60" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10270,11 +12345,11 @@
       </c>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="60" customHeight="1">
       <c r="A217" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10311,11 +12386,11 @@
       </c>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；咖啡侨乡农镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；咖啡侨乡农镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="60" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10352,11 +12427,11 @@
       </c>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农垦农场；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农垦农场；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="60" customHeight="1">
       <c r="A219" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10393,11 +12468,11 @@
       </c>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="60" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10434,11 +12509,11 @@
       </c>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；客家村落与农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；客家村落与农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="60" customHeight="1">
       <c r="A221" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10475,11 +12550,11 @@
       </c>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="60" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10516,11 +12591,11 @@
       </c>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="60" customHeight="1">
       <c r="A223" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10557,11 +12632,11 @@
       </c>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；客家村落与农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；客家村落与农镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="60" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10598,11 +12673,11 @@
       </c>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；古商埠与海口西翼门户；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；古商埠与海口西翼门户；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="60" customHeight="1">
       <c r="A225" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10639,11 +12714,11 @@
       </c>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="60" customHeight="1">
       <c r="A226" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10680,11 +12755,11 @@
       </c>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="60" customHeight="1">
       <c r="A227" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10721,11 +12796,11 @@
       </c>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农乡；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="60" customHeight="1">
       <c r="A228" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10762,11 +12837,11 @@
       </c>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；商贸农镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；商贸农镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="60" customHeight="1">
       <c r="A229" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10803,11 +12878,11 @@
       </c>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="60" customHeight="1">
       <c r="A230" s="5" t="inlineStr">
         <is>
           <t>澄迈县</t>
@@ -10844,11 +12919,11 @@
       </c>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>海口西翼卫星农业县，客家/临高移民散居（类比新北郊区与彰化之均势）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="44" customHeight="1">
+          <t>海口西翼卫星县：老城开发区/马村港耦合首府，福山咖啡与富硒农产品，美榔双塔古县文脉；海南话与临高话带相间，加乐—文儒有客家村落；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="60" customHeight="1">
       <c r="A231" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -10885,11 +12960,11 @@
       </c>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；县城；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；县城；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="60" customHeight="1">
       <c r="A232" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -10926,11 +13001,11 @@
       </c>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；北部湾大渔港；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；北部湾大渔港；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="60" customHeight="1">
       <c r="A233" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -10967,11 +13042,11 @@
       </c>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；北部湾大渔港；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；北部湾大渔港；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="60" customHeight="1">
       <c r="A234" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11008,11 +13083,11 @@
       </c>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="60" customHeight="1">
       <c r="A235" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11049,11 +13124,11 @@
       </c>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；渔业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；渔业镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="60" customHeight="1">
       <c r="A236" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11090,11 +13165,11 @@
       </c>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农垦农场与客家散居；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农垦农场与客家散居；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="60" customHeight="1">
       <c r="A237" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11131,11 +13206,11 @@
       </c>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="60" customHeight="1">
       <c r="A238" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11172,11 +13247,11 @@
       </c>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="60" customHeight="1">
       <c r="A239" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11213,11 +13288,11 @@
       </c>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="60" customHeight="1">
       <c r="A240" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11254,11 +13329,11 @@
       </c>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农场与农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农场与农业镇；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="60" customHeight="1">
       <c r="A241" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11295,11 +13370,11 @@
       </c>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；滨海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；滨海农业；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="60" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11336,11 +13411,11 @@
       </c>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；濒海农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；濒海农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="60" customHeight="1">
       <c r="A243" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11377,11 +13452,11 @@
       </c>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；海南客家重镇之一；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；海南客家重镇之一；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="60" customHeight="1">
       <c r="A244" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11418,11 +13493,11 @@
       </c>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="60" customHeight="1">
       <c r="A245" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11459,11 +13534,11 @@
       </c>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="60" customHeight="1">
       <c r="A246" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11500,11 +13575,11 @@
       </c>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="60" customHeight="1">
       <c r="A247" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11541,11 +13616,11 @@
       </c>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；客家边区农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；客家边区农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="60" customHeight="1">
       <c r="A248" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11582,11 +13657,11 @@
       </c>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="60" customHeight="1">
       <c r="A249" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11623,11 +13698,11 @@
       </c>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；滨海渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；滨海渔村；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="60" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11664,11 +13739,11 @@
       </c>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农牧乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农牧乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="60" customHeight="1">
       <c r="A251" s="5" t="inlineStr">
         <is>
           <t>临高县</t>
@@ -11705,11 +13780,11 @@
       </c>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>临高话独特民系（壮傣语支约 50 万人）与北部湾渔业大县，农渔阶级绿底，和舍为客家岛（类比宜兰渔业绿盘）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="44" customHeight="1">
+          <t>临高话使用者（语言来源与分类仍有争议；主体在临高，官方多登记为汉族）与北部湾渔业大县（新盈、调楼、马袅渔港）；和舍为客家孤垒；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="60" customHeight="1">
       <c r="A252" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11746,11 +13821,11 @@
       </c>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；县城/行政中心；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；县城/行政中心；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="60" customHeight="1">
       <c r="A253" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11787,11 +13862,11 @@
       </c>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎汉集镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎汉集镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="60" customHeight="1">
       <c r="A254" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11828,11 +13903,11 @@
       </c>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="60" customHeight="1">
       <c r="A255" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11869,11 +13944,11 @@
       </c>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="60" customHeight="1">
       <c r="A256" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11910,11 +13985,11 @@
       </c>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎族聚居镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎族聚居镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="60" customHeight="1">
       <c r="A257" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11951,11 +14026,11 @@
       </c>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；纯黎山地乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；纯黎山地乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="60" customHeight="1">
       <c r="A258" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -11992,11 +14067,11 @@
       </c>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎汉农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎汉农乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="60" customHeight="1">
       <c r="A259" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12033,11 +14108,11 @@
       </c>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="60" customHeight="1">
       <c r="A260" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12074,11 +14149,11 @@
       </c>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；偏远黎乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；偏远黎乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="60" customHeight="1">
       <c r="A261" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12115,11 +14190,11 @@
       </c>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎汉集镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎汉集镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="60" customHeight="1">
       <c r="A262" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12156,11 +14231,11 @@
       </c>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="60" customHeight="1">
       <c r="A263" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12197,11 +14272,11 @@
       </c>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="60" customHeight="1">
       <c r="A264" s="5" t="inlineStr">
         <is>
           <t>白沙黎族自治县</t>
@@ -12238,11 +14313,11 @@
       </c>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>黎族比例全省最高的山地县之一，原乡人情网络与教会组织牢固（类比花莲秀林/台东纵谷原乡蓝盘）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="44" customHeight="1">
+          <t>黎族比重最高的山区县之一（2010六普少数民族67.43%），橡胶、白沙绿茶（陨石坑）与山兰米；头人、教会与原乡组织蓝底最深（类比秀林—万荣原乡）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="60" customHeight="1">
       <c r="A265" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12279,11 +14354,11 @@
       </c>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；县治与铁矿工矿区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="266" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；县治与铁矿工矿区；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="60" customHeight="1">
       <c r="A266" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12320,11 +14395,11 @@
       </c>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；军话滨海古镇(昌化港)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；军话滨海古镇(昌化港)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="60" customHeight="1">
       <c r="A267" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12361,11 +14436,11 @@
       </c>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；军话村落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；军话村落；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="60" customHeight="1">
       <c r="A268" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12402,11 +14477,11 @@
       </c>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；儋州话/军话农渔；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；儋州话/军话农渔；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="60" customHeight="1">
       <c r="A269" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12443,11 +14518,11 @@
       </c>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；渔港；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="60" customHeight="1">
       <c r="A270" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12484,11 +14559,11 @@
       </c>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="60" customHeight="1">
       <c r="A271" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12525,11 +14600,11 @@
       </c>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；农渔；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="60" customHeight="1">
       <c r="A272" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12566,11 +14641,11 @@
       </c>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；农场农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="273" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；农场农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="60" customHeight="1">
       <c r="A273" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12607,11 +14682,11 @@
       </c>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；工矿黎汉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="274" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；工矿黎汉；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="60" customHeight="1">
       <c r="A274" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12648,11 +14723,11 @@
       </c>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；农场山地乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="275" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；农场山地乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="60" customHeight="1">
       <c r="A275" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12689,11 +14764,11 @@
       </c>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="276" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="60" customHeight="1">
       <c r="A276" s="5" t="inlineStr">
         <is>
           <t>昌江黎族自治县</t>
@@ -12730,11 +14805,11 @@
       </c>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>石碌铁矿工矿带、军话沿海与黎族山乡并存（类比高雄工矿+山地原乡）；偏远黎寨；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="277" ht="44" customHeight="1">
+          <t>石碌铁矿（海南最大工矿区）、昌化江下游军话与村话民系、黎族山乡及霸王岭雨林并存（类比高雄工矿＋原乡）；渔港海尾、乌烈；偏远黎寨；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="60" customHeight="1">
       <c r="A277" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12771,11 +14846,11 @@
       </c>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；县城(乐东黎族自治县治)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；县城(乐东黎族自治县治)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="60" customHeight="1">
       <c r="A278" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12812,11 +14887,11 @@
       </c>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="279" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="60" customHeight="1">
       <c r="A279" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12853,11 +14928,11 @@
       </c>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；渔盐小镇(莺歌海盐场)；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="280" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；渔盐小镇(莺歌海盐场)；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="60" customHeight="1">
       <c r="A280" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12894,11 +14969,11 @@
       </c>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；尖峰岭黎汉与林场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="281" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；尖峰岭黎汉与林场；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="60" customHeight="1">
       <c r="A281" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12935,11 +15010,11 @@
       </c>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；沿海闽南海南话商镇，农渔并重；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
-        </is>
-      </c>
-    </row>
-    <row r="282" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；沿海海南话商镇（闽语海南支，海北/雷州移民后裔多），农渔并重；综合研判：绿营稳定领先，蓝营仅靠公教与家族网络守成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="60" customHeight="1">
       <c r="A282" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -12976,11 +15051,11 @@
       </c>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；沿海农渔人口大镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="283" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；沿海农渔人口大镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="60" customHeight="1">
       <c r="A283" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13017,11 +15092,11 @@
       </c>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；纯黎山乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="284" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；纯黎山乡；综合研判：蓝营组织与族群结构牢固，绿营仅居得票底线，中间盘有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="60" customHeight="1">
       <c r="A284" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13058,11 +15133,11 @@
       </c>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；沿海农渔镇；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="60" customHeight="1">
       <c r="A285" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13099,11 +15174,11 @@
       </c>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="286" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="60" customHeight="1">
       <c r="A286" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13140,11 +15215,11 @@
       </c>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="287" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="60" customHeight="1">
       <c r="A287" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13181,11 +15256,11 @@
       </c>
       <c r="I287" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="288" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="60" customHeight="1">
       <c r="A288" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13222,11 +15297,11 @@
       </c>
       <c r="I288" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="289" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="60" customHeight="1">
       <c r="A289" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13263,11 +15338,11 @@
       </c>
       <c r="I289" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="290" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="60" customHeight="1">
       <c r="A290" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13304,11 +15379,11 @@
       </c>
       <c r="I290" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="291" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="60" customHeight="1">
       <c r="A291" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13345,11 +15420,11 @@
       </c>
       <c r="I291" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="292" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="60" customHeight="1">
       <c r="A292" s="5" t="inlineStr">
         <is>
           <t>乐东黎族自治县</t>
@@ -13386,11 +15461,11 @@
       </c>
       <c r="I292" s="5" t="inlineStr">
         <is>
-          <t>西南农渔大县，沿海海南话带（黄流—九所—利国）与内陆黎乡分野鲜明（类比屏东平原绿盘+原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="44" customHeight="1">
+          <t>西南农渔大县：莺歌海盐场、黄流—九所—利国沿海海南话人口大带 vs 内陆黎乡；尖峰岭热带雨林与南药腰果；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="60" customHeight="1">
       <c r="A293" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13427,11 +15502,11 @@
       </c>
       <c r="I293" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；县城(陵水河出海口)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；县城(陵水河出海口)；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="60" customHeight="1">
       <c r="A294" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13468,11 +15543,11 @@
       </c>
       <c r="I294" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="295" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="60" customHeight="1">
       <c r="A295" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13509,11 +15584,11 @@
       </c>
       <c r="I295" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；沿海农渔与度假开发；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="296" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；沿海农渔与度假开发；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="60" customHeight="1">
       <c r="A296" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13550,11 +15625,11 @@
       </c>
       <c r="I296" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="297" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="60" customHeight="1">
       <c r="A297" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13591,11 +15666,11 @@
       </c>
       <c r="I297" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；黎族乡(吊罗山北麓)；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；黎族乡(吊罗山北麓)；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="60" customHeight="1">
       <c r="A298" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13632,11 +15707,11 @@
       </c>
       <c r="I298" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="60" customHeight="1">
       <c r="A299" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13673,11 +15748,11 @@
       </c>
       <c r="I299" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；疍家渔港(新村港)；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="300" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；疍家渔港(新村港)；综合研判：绿营略占优势，蓝营靠军公教与传统组织维持盘面。</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="60" customHeight="1">
       <c r="A300" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13714,11 +15789,11 @@
       </c>
       <c r="I300" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="301" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；农业；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="60" customHeight="1">
       <c r="A301" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13755,11 +15830,11 @@
       </c>
       <c r="I301" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；黎汉混合乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；黎汉混合乡；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="60" customHeight="1">
       <c r="A302" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13796,11 +15871,11 @@
       </c>
       <c r="I302" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；渔港；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
-        </is>
-      </c>
-    </row>
-    <row r="303" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；渔港；综合研判：蓝绿大致五五波，成败系于中间选民与大环境风向。</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="60" customHeight="1">
       <c r="A303" s="5" t="inlineStr">
         <is>
           <t>陵水黎族自治县</t>
@@ -13837,11 +15912,11 @@
       </c>
       <c r="I303" s="5" t="inlineStr">
         <is>
-          <t>黎族约半数的原住民县，沿海闽南农渔与疍家渔港并存（类比屏东）；丘陵农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="304" ht="44" customHeight="1">
+          <t>黎族过半的原住民县（少数民族约五成五），新村港疍家渔排、南湾猴岛/分界洲旅游、吊罗山与陵水苏维埃工农记忆；丘陵农业；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="60" customHeight="1">
       <c r="A304" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -13878,11 +15953,11 @@
       </c>
       <c r="I304" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；县城/七仙岭门户；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="305" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；县城/七仙岭门户；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="60" customHeight="1">
       <c r="A305" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -13919,11 +15994,11 @@
       </c>
       <c r="I305" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎苗山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎苗山地乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="60" customHeight="1">
       <c r="A306" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -13960,11 +16035,11 @@
       </c>
       <c r="I306" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="307" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="60" customHeight="1">
       <c r="A307" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14001,11 +16076,11 @@
       </c>
       <c r="I307" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="308" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="60" customHeight="1">
       <c r="A308" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14042,11 +16117,11 @@
       </c>
       <c r="I308" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="60" customHeight="1">
       <c r="A309" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14083,11 +16158,11 @@
       </c>
       <c r="I309" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；景区黎汉，观光移民多；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；景区黎汉，观光移民多；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="60" customHeight="1">
       <c r="A310" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14124,11 +16199,11 @@
       </c>
       <c r="I310" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="311" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="60" customHeight="1">
       <c r="A311" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14165,11 +16240,11 @@
       </c>
       <c r="I311" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="312" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="60" customHeight="1">
       <c r="A312" s="5" t="inlineStr">
         <is>
           <t>保亭黎族苗族自治县</t>
@@ -14206,11 +16281,11 @@
       </c>
       <c r="I312" s="5" t="inlineStr">
         <is>
-          <t>黎汉苗山地县、七仙岭温泉旅游带（类比屏东雾台/满州原乡蓝盘）；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="44" customHeight="1">
+          <t>黎苗山地县（2010六普少数民族67.43%），七仙岭温泉、槟榔谷/呀诺达黎苗景区，南药与热带果品；观光移民持续注入；黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="60" customHeight="1">
       <c r="A313" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14247,11 +16322,11 @@
       </c>
       <c r="I313" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；县城/行政中心；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；县城/行政中心；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="60" customHeight="1">
       <c r="A314" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14288,11 +16363,11 @@
       </c>
       <c r="I314" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；苗族聚居乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；苗族聚居乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="60" customHeight="1">
       <c r="A315" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14329,11 +16404,11 @@
       </c>
       <c r="I315" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="60" customHeight="1">
       <c r="A316" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14370,11 +16445,11 @@
       </c>
       <c r="I316" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；松涛客家村落与黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；松涛客家村落与黎族山乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="60" customHeight="1">
       <c r="A317" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14411,11 +16486,11 @@
       </c>
       <c r="I317" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="318" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="60" customHeight="1">
       <c r="A318" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14452,11 +16527,11 @@
       </c>
       <c r="I318" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="319" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="60" customHeight="1">
       <c r="A319" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14493,11 +16568,11 @@
       </c>
       <c r="I319" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；农商集镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
-        </is>
-      </c>
-    </row>
-    <row r="320" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；农商集镇；综合研判：蓝营略占优势，惟绿营加中间选民仍有翻盘空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="60" customHeight="1">
       <c r="A320" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14534,11 +16609,11 @@
       </c>
       <c r="I320" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；吊罗山林区黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；吊罗山林区黎乡；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="60" customHeight="1">
       <c r="A321" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14575,11 +16650,11 @@
       </c>
       <c r="I321" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="44" customHeight="1">
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；黎族镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="60" customHeight="1">
       <c r="A322" s="5" t="inlineStr">
         <is>
           <t>琼中黎族苗族自治县</t>
@@ -14616,11 +16691,937 @@
       </c>
       <c r="I322" s="5" t="inlineStr">
         <is>
-          <t>全岛腹地黎苗县（黎族约四成半，苗族约 6%），松涛—黎母山带为客家村落（类比山地原乡蓝盘）；黎客杂处山地镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
+          <t>全岛腹地黎苗县（2010六普黎族53.86%、苗族8.11%），琼中绿橙、松涛—黎母山与吊罗山生态林，海南岛天然分水岭；黎母山一带为客家村落；黎客杂处山地镇；综合研判：蓝营稳定领先，绿营在年轻与都会票源有所成长但未成气候。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>县市</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>人口(2000普查,万人)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>主要方言/民系</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>世居及少数民族构成(约)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>主要产业与经济</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>历史与人文要点</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>蓝绿结构意涵（vs 台湾类比之修正）</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>扩展简析（1000字以上）</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>2020年七普常住人口(人)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="100" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>海口市</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>2000五普150.82万（当时含琼山）；2010六普204.62万；2020七普287.34万（现行范围）</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>海南话为主体（府城—琼山口音）；西郊临高话；港区/机关白话、闽语、官话</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>汉族97%以上，少数民族不足2%（海口市区2.34%）</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>特区首府：商贸、金融、会展、港口物流、制药与航空金融；琼山（府城）为科第农桑与教育重镇</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>古琼州府城所在地、海口所（明）系商港；1926 年设海口市；1949 年海南特别行政区成立、首府设此（假设 ROC 沿续）</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>外省族裔/军公教集中=类比台北蓝盘最厚处；但无台湾「本省人」人口优势，「蓝/绿」之争更似都会职业与世代替换市，中间盘特大</t>
+        </is>
+      </c>
+      <c r="H2" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I2" s="37" t="n"/>
+    </row>
+    <row r="3" ht="100" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>三亚市</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>沿海海南话、黎话、回辉话、迈话、疍家话及市区普通话；回辉话、迈话的来源与分类仍有争议，不与疍家话或粤语简单等同</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2002户籍：汉族58.67%、少数民族41.33%（黎族38.65%、回族约1.49%）；语言与法定民族不能等同</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>旅游（天涯海角、亚龙湾、南山）、南繁育种、崖州中心渔港、榆林军港、岭北盐田</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>唐宋贬谪重地（崖州），明代卫所留下军话；清末设榆林要塞；回辉/回新为宋代「番客」后裔；疍民世代居三亚港</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>军港蓝 + 黎乡蓝；疍民/渔港/旅游移民绿——与台湾高雄极似，但回族与黎族无平行对应；中间盘高</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I3" s="37" t="n"/>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>五指山市</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>黎话、苗话为主，城镇海南话/普通话</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2010六普：少数民族67.34%（黎族60.02%、苗族5.42%）；2000年普查时名为通什市</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>山城旅游（五指山）、五指山茶、南药、林业；现实通什曾为黎族苗族自治州州府</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1987 年设通什市（2001 年更名五指山市）；现实中为琼崖纵队五指山根据地核心，假设 ROC 下则为山地民族行政核心</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>类比雾台/玛家原乡蓝盘成立，但黎族规模远大于台湾原住民，其蓝盘根基于民族行政与山地治理关系</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="n"/>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>琼海市</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2000五普45.04万；2010六普48.32万；2020七普52.82万</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>海南话（琼海腔，近文昌）、苗话（会山）、疍家话（潭门）；另有白话（华侨农场）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>汉族为主；黎（万泉河上游边区）、苗（会山镇）合计不足3%</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>嘉积商埠商贸、博鳌会展旅游、潭门—长坡远洋渔业（西沙/南海）、胡椒菠萝橡胶等热带作物、华侨侨汇经济</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1958 年琼东县＋乐会县并为琼海县（1992 年设市）；现实为红色娘子军/琼崖苏区故地；潭门为千年「更路簿」渔航中心</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>侨乡自由主义 + 渔港劳动阶级 → 绿盘，类比宜兰/嘉义；但潭门渔业的政治化程度不及台湾渔会，中间盘更大</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I5" s="37" t="n"/>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>儋州市</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2000五普83.51万；2010六普85.56万；2020七普95.43万（含洋浦）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>儋州话（粤语系，最多）、海南话（那大/中东部）、客家话（那大—南丰—兰洋—和庆，约十万）、军话（王五、光村等）、临高话（北部临海）、黎话（山区）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>汉族为主；黎族约4%（山区）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>洋浦港与石化产业园、那大区域性商埠、北部湾盐田与渔业、松涛水库灌区农业、儋州古城（中和）旅游</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>汉置儋耳郡，儋州为苏东坡（1097—1100）贬谪地（载酒堂/中和）；清代客家人由闽粤迁入垦殖那大；1910 年代那大成琼西商埠；洋浦 1992 年设国家级开发区（现实）；1958 年松涛水库兴建</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>客家蓝盘存在但仅 4 个镇集中且人数约十万，不能放大为桃竹苗式全台客家轴心；儋州话沿海与农垦人口为中间大票仓</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="n"/>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>文昌市</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>50.9</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>海南话（文昌腔为全省标准音）、疍家话（清澜/铺前）、少量白话</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>汉族 99% 以上</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>侨汇与侨乡经济、椰子/椰雕、文昌鸡养殖、清澜港渔业与航运、教育与文教产业（文昌中学等）、航天发射场（现实）</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>汉置紫贝县；唐武德五年（622）置文昌县；明清琼北科举重镇；宋氏（孙中山/宋庆龄）祖居；铺前—清澜骑楼古商埠与下南洋传统深厚</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>类比南投/花莲传统蓝盘：蓝盘出于士绅/侨汇/宗族而非族群；文昌话标准音使其文化领导位置强化「琼人本位」认同，绿盘难破</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>560894</v>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>万宁市</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2000五普51.36万；2010六普54.56万；2020七普54.60万</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>海南话（万城/和乐/海口变音）、黎话（南桥、北大、三更罗）、苗话；兴隆农垦区白话/客家话/福建话（归侨）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>2010六普少数民族约16.05%；黎族山乡、兴隆侨乡与海南话沿海社区并存</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>兴隆咖啡与热带作物、槟榔/胡椒、石梅湾/东山岭旅游、和乐蟹与港北渔港、椰林；六连岭下东部滨海农业</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>唐贞观五年（631）置万安州/万宁县；六连岭为现实琼崖纵队根据地之一；1951 年兴隆华侨农场安置南洋归侨</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>族群与职业高度多元 = 全岛中间盘最典型县；类比台中市成立，但因无台中「市政治理资源」的缓冲，岁时趋势更直接</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I8" s="37" t="n"/>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>东方市</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>35.8</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>军话（八所/四更/三家/新街/罗带）、村话（感城—板桥，来源与分类仍有争议，官方多登记为汉族）、海南话（沿海）、黎话（内陆）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2002户籍：汉族78.85%、少数民族21.14%（黎族约20.77%，另有苗、壮等）；语言民系与法定民族不能等同</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>八所深水港、东方石化/氯碱与金海浆纸（现实）、制盐（东方盐场）、昌化江下游农渔、大广坝/红水河灌区</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>感恩县（隋）为古县；八所港 1942 年日军侵占时修建（现实）；军话为明代卫所军户后裔方言；村话民系为海南特有</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>军话=「准眷村」蓝盘，但它是落地数百年的土著民系而非 1949 外省移民，政治动员靠卫所宗族而非身份认同；绿营靠渔港与农劳</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>444458</v>
+      </c>
+    </row>
+    <row r="10" ht="100" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>定安县</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>海南话（定安片，属琼北）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>汉族 99% 以上</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>稻作与富硒瓜菜、南丽湖旅游、母瑞山红色文化旅游、定安粽子等农产加工</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>元天历二年（1329）置定安县；明清琼北科举冠绝全岛（王弘诲等）；见龙塔；现实琼崖纵队母瑞山根据地</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>蓝盘来自士绅/文教/宗族，类比新竹县「客家文教蓝」并不准确——定安无客家人；应视作「科举县」型保守盘</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I10" s="37" t="n"/>
+    </row>
+    <row r="11" ht="100" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>屯昌县</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>海南话（屯昌片，兼澄迈/定安过渡口音）；农垦区白话/客家话（少量）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>汉族为主；黎、苗约2—3%（南坤等黎苗边镇）</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>垦殖农业（橡胶、槟榔、热带水果）、枫木鹿场、养猪与米作；海口—琼中要道过境经济</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>1949 年由琼山析置新民县、1950 年改称屯昌县（后并入澄迈/定安边地）；解放前为南洋垦殖与农垦移民地，华侨垦殖历史短</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>后设县、无派系、无宗族强力网络 → 纯全国性大环境风向县；类比彰化/云林农业区成立</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I11" s="37" t="n"/>
+    </row>
+    <row r="12" ht="100" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>澄迈县</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>海南话（澄迈片）、临高话（北部沿海桥头—老城一部）、客家话（加乐—文儒）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>汉族为主；少数民族约1%</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>海口西翼门户（老城开发区、马村港、物流/软件园）、福山咖啡（侨乡）、富硒地瓜与瓜菜、瑞溪粽子、橡胶</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>隋代置澄迈县；老城为古澄迈县城遗址（澄迈故城）；元代美榔双塔；明清琼北粮仓</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>首府外溢的都会通勤性格 + 农渔 + 零散客家/临高 = 胶着；类比新北郊区成立</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="n"/>
+    </row>
+    <row r="13" ht="100" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>临高县</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>临高话（语言来源与分类仍有学术争议）为主；部分海南话、和舍等局部客家话；语言不等于法定民族</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>汉族为主（临高话群体登记汉族）；黎苗极少</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>北部湾渔业（新盈、调楼、马袅）、盐田、临高乳猪与稻作；现实临高角为 1950 年海南岛战役登陆地</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>隋代置临高县；临高木偶戏（人偶同台）、「哩哩美」渔歌列为非遗；1950 年 4 月解放军渡海登陆临高角—昌化江（现实史事）</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>渔业劳工结构可能形成职业性绿底，但临高话族群的「民系」认同弱于台湾闽南人，中间选民更多；客家仅局部存在</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="n"/>
+    </row>
+    <row r="14" ht="100" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>白沙黎族自治县</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>黎话（本地、赛等方言群）、海南话（城镇）、苗话少量</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>2010六普：少数民族67.43%；2010常住16.79万（2000五普16.45万）</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>橡胶（海南重要产胶县）、白沙绿茶（陨石坑产区）、山兰米/山兰酒、雨林生态旅游（邦溪、陨石坑）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>1935 年置白沙县（文明与黎峒析出）；现实 1943 年白沙起义（王国兴）为琼崖斗争起点之一；黎族传统「合亩制」社会</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>黎乡蓝盘最深之一，但非政党忠诚而是山地治理/人情/教会组织；类比花莲原乡成立</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I14" s="37" t="n">
+        <v>164699</v>
+      </c>
+    </row>
+    <row r="15" ht="100" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>昌江黎族自治县</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>儋州话（沿海）、海南话、军话（昌化—乌烈—海尾一部）、村话（昌化江口两岸）、黎话（七叉—王下）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2010六普：少数民族38.65%（黎族为主）；2010常住22.38万（2000五普21.95万）</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>石碌铁矿（海南最大）、昌江核电（现实）、乌烈—海尾渔镇、木棉与芒果、霸王岭雨林生态旅游</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>隋设定川县、唐改昌化县、1914 年改昌江县；现实 1939—45 年日军曾掠采石碌铁矿；军话村落明代形成</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>工矿蓝 + 军话蓝 + 黎乡蓝三重加码，是海南最接近台湾「外省/原乡」蓝轴心的县；渔港绿盘规模有限</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="n">
+        <v>232124</v>
+      </c>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>乐东黎族自治县</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>44.6</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>海南话（沿海黄流—九所—利国—莺歌海，闽语海南支）、黎话（万冲—志仲—大安—千家内陆）、苗话少量</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>少数民族约38%（黎为主，苗少量）</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>莺歌海盐场（全国知名）、沿海农渔大镇带、尖峰岭热带雨林旅游、腰果南药、槟榔芒果</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>1935 年由崖县、感恩、昌化析置乐东县；黄流为琼西南民俗活跃镇（崖州八音等）；莺歌海盐业开发史（现实 1958 建场）</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>「沿海汉绿—内陆黎蓝」为最清晰的屏东式南北分立；但沿海人口带的绿盘来自农渔职业而非闽南族群认同</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I16" s="37" t="n">
+        <v>464435</v>
+      </c>
+    </row>
+    <row r="17" ht="100" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>陵水黎族自治县</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>海南话（沿海）、黎话（群英—隆广—文罗）、苗话、疍家话（新村港）、回辉话少量</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>少数民族约55%（黎过半、苗族等）</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>新村港疍家渔排与海洋渔业、南湾猴岛/分界洲岛旅游、吊罗山林业、芒果等热带果品、陵水黎锦</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>唐置陵水县；现实 1927 年陵水成立全国最早县级苏维埃政权之一；疍民世代浮家江海</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>黎乡蓝底类比屏东牡丹/雾台成立；疍家港绿盘类比较高雄渔港</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>372511</v>
+      </c>
+    </row>
+    <row r="18" ht="100" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>保亭黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>黎话（杞/哈方言）、苗话、海南话（城镇）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>2010分民族资料约69%（黎族为主，苗族、壮族等共居；细分以普查年鉴最终表为准）</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>七仙岭温泉旅游、槟榔谷/呀诺达黎苗文化景区、南药（槟榔、益智）、红毛丹山竹等热带果品</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>1935 年置保亭县；1962 年国务院将琼中、陵水、乐东等边地划归保亭治；现实海南黎族苗族自治州州府初曾驻通什一带，保亭为黎苗文化重镇</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>原乡组织+景区经济蓝盘；观光移民与青年票为绿营机会；类比雾台/来义成立</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="n">
+        <v>156108</v>
+      </c>
+    </row>
+    <row r="19" ht="100" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>琼中黎族苗族自治县</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>黎话、苗话、海南话（湾岭/营根城镇）、客家话（黎母山—中平一带）</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>2010六普：少数民族66.44%（黎族53.86%、苗族8.11%）；2010常住17.41万（2000五普17.16万）</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>琼中绿橙、五指山北麓生态农业、松涛水库水源保护、黎母山/吊罗山林业与旅游、槟榔橡胶</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>1952 年由琼山、定安、乐会、白沙析置琼中县；黎母山为黎族始祖传说之地；海南岛天然分水岭（水向南北分流）</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>黎苗+客家双重蓝底；谷地蓄牧蓄浓，绿营难撼；类比秀林/万荣成立</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>查看完整扩展简析</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="n">
+        <v>179586</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>全岛合计</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>2000五普786.75万；2010六普867.15万；2020七普1008.12万（常住人口口径）</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>海南话为最大汉语方言群；儋州话、临高话、军话、村话、回辉话、黎话、苗话等分布各异，暂无统一精确人口统计；客家话为局部聚居</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>2000五普：汉族82.71%、少数民族17.29%；民族登记与方言/民系不可直接换算</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>热带农业（橡胶、槟榔、热带水果、渔盐）、侨乡经济、石碌铁矿、航天基地、旅游与自贸港（现实语境）；假设 ROC 下为农渔业+军港都会经济</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>汉开琼州建制与明代全琼卫所；省（特别行政区）延续与农垦/矿山开发（现实为解放战争与建省后的建设史）</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>全表以「收敛中间」为原则：无台湾本省/外省二元断痕、族群政治动员弱，蓝绿差距普遍小于台湾；原乡民族蓝盘出于民族行政/头人/教会，农渔沿海带绿盘出于职业与世代而非族群认同</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>查看全省通用来源</t>
+        </is>
+      </c>
+      <c r="I20" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>